--- a/outputs/atlas/rtl_di_atlas_un_members_2026.xlsx
+++ b/outputs/atlas/rtl_di_atlas_un_members_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RTLDI ATLAS 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTLDI ATLAS 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,14 +515,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source equation: ΔG = η × (1 − R) × G₀   |   η = 0.05 (Hubbard, Causality and Attraction v3, DOI 10.5281/zenodo.19468550)   |   R = R from 8 V-Dem components (crosswalk, year=2024) + real WB socio #9 + 2026-fresh G0 (GDP is the more dynamic variable). See docs/indicator_crosswalk.md</t>
+          <t>Source equation: ΔG = η × (1 − R) × G₀   |   η = 0.3 (Hubbard, Causality and Attraction v3, DOI 10.5281/zenodo.19468550)   |   R = R from 8 V-Dem components (crosswalk, year=2024) + real WB socio #9 + 2026-fresh G0 (GDP is the more dynamic variable). See docs/indicator_crosswalk.md</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Countries: 193 | With GDP: 187 | Est. global deficit: $2,887,963,265,996 | Avg R: 0.346</t>
+          <t>Countries: 193 | With GDP: 187 | Est. global deficit: $18,762,377,508,353 | Avg R: 0.326</t>
         </is>
       </c>
     </row>
@@ -635,10 +635,10 @@
         <v>2024</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>665.15740771934</v>
+        <v>3990.94444631604</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>937190158541.3571</v>
+        <v>5623140951248.143</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>1</v>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.667</v>
+        <v>0.556</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>84534.0407841548</v>
@@ -694,16 +694,16 @@
         <v>2024</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1408.900679735913</v>
+        <v>11271.20543788731</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>479182602178.8529</v>
+        <v>3833460817430.825</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>2694.73780859961</v>
@@ -753,16 +753,16 @@
         <v>2024</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>134.7368904299805</v>
+        <v>718.596748959896</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>195494576692.9041</v>
+        <v>1042637742362.155</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>3</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         <v>2024</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>661.7341579861111</v>
+        <v>3970.404947916667</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>94981252033.98892</v>
+        <v>569887512203.9336</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>4</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -841,28 +841,28 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>130861007</v>
+        <v>123975371</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.222</v>
+        <v>0.556</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>14185.7812248529</v>
+        <v>32487.0778047567</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>2026</v>
@@ -871,16 +871,16 @@
         <v>2024</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>551.6692698553906</v>
+        <v>4331.61037396756</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>72191996184.23116</v>
+        <v>537013003140.077</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>5</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -900,28 +900,28 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>123975371</v>
+        <v>69226000</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.667</v>
+        <v>0.556</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>32487.0778047567</v>
+        <v>53246.3676145108</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>2026</v>
@@ -930,16 +930,16 @@
         <v>2024</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>541.4512967459451</v>
+        <v>7099.515681934773</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>67126625392.50964</v>
+        <v>491471072597.6166</v>
       </c>
       <c r="K12" s="10" t="n">
         <v>6</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -959,28 +959,28 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>51751065</v>
+        <v>130861007</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>36238.639908315</v>
+        <v>14185.7812248529</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>2026</v>
@@ -989,16 +989,16 @@
         <v>2024</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1207.9546636105</v>
+        <v>3310.015619132344</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>62512940313.56013</v>
+        <v>433151977105.387</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>7</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1018,28 +1018,28 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>35300280</v>
+        <v>51751065</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>SAU</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>35121.6628687742</v>
+        <v>36238.639908315</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>2026</v>
@@ -1048,16 +1048,16 @@
         <v>2024</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1756.08314343871</v>
+        <v>7247.727981663001</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>61990226666.66663</v>
+        <v>375077641881.3608</v>
       </c>
       <c r="K14" s="10" t="n">
         <v>8</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -1077,28 +1077,28 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>69226000</v>
+        <v>35300280</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>SAU</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>53246.3676145108</v>
+        <v>35121.6628687742</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>2026</v>
@@ -1107,16 +1107,16 @@
         <v>2024</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>887.4394602418467</v>
+        <v>10536.49886063226</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>61433884074.70208</v>
+        <v>371941359999.9997</v>
       </c>
       <c r="K15" s="10" t="n">
         <v>9</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
         <v>2024</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>286.4041354949056</v>
+        <v>1718.424812969433</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>60717268026.21863</v>
+        <v>364303608157.3118</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>10</v>
@@ -1195,28 +1195,28 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>85518661</v>
+        <v>58952704</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.111</v>
+        <v>0.556</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>15892.7157287241</v>
+        <v>40385.3413957669</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>2026</v>
@@ -1225,16 +1225,16 @@
         <v>2024</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>706.3429212766267</v>
+        <v>5384.712186102253</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>60405500834.40553</v>
+        <v>317443343632.4791</v>
       </c>
       <c r="K17" s="10" t="n">
         <v>11</v>
       </c>
       <c r="L17" s="10" t="n">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1254,28 +1254,28 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>283487931</v>
+        <v>85518661</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>4925.43048751861</v>
+        <v>15892.7157287241</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>2026</v>
@@ -1284,16 +1284,16 @@
         <v>2024</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>164.1810162506204</v>
+        <v>3708.30033670229</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>46543336606.36575</v>
+        <v>317128879380.629</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>12</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1313,28 +1313,28 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>58952704</v>
+        <v>283487931</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>40385.3413957669</v>
+        <v>4925.43048751861</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>2026</v>
@@ -1343,16 +1343,16 @@
         <v>2024</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>673.0890232627816</v>
+        <v>985.086097503722</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>39680417954.05988</v>
+        <v>279260019638.1944</v>
       </c>
       <c r="K19" s="10" t="n">
         <v>13</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>156</v>
+        <v>91</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1372,28 +1372,28 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>68551653</v>
+        <v>41288599</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Northern America</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>46103.0840855884</v>
+        <v>54340.3477224733</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>2026</v>
@@ -1402,16 +1402,16 @@
         <v>2024</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>512.2564898398714</v>
+        <v>5434.034772247331</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>35116029138.50089</v>
+        <v>224363682663.3764</v>
       </c>
       <c r="K20" s="10" t="n">
         <v>14</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -1431,28 +1431,28 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>10986400</v>
+        <v>68551653</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>0.778</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>50273.5060469837</v>
+        <v>46103.0840855884</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>2026</v>
@@ -1461,16 +1461,16 @@
         <v>2024</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>2513.675302349185</v>
+        <v>3073.538939039228</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>27616242341.72909</v>
+        <v>210696174831.0053</v>
       </c>
       <c r="K21" s="10" t="n">
         <v>15</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1490,28 +1490,28 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>83516593</v>
+        <v>48848840</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.889</v>
+        <v>0.667</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>56103.7323182554</v>
+        <v>35326.7683069278</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>2026</v>
@@ -1520,16 +1520,16 @@
         <v>2024</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>311.6874017680857</v>
+        <v>3532.676830692779</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>26031069876.6927</v>
+        <v>172567165274.2187</v>
       </c>
       <c r="K22" s="10" t="n">
         <v>16</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1549,28 +1549,28 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>41288599</v>
+        <v>83516593</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Northern America</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.778</v>
+        <v>0.889</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>54340.3477224733</v>
+        <v>56103.7323182554</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>2026</v>
@@ -1579,16 +1579,16 @@
         <v>2024</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>603.7816413608148</v>
+        <v>1870.124410608514</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>24929298073.7085</v>
+        <v>156186419260.1562</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>17</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1608,28 +1608,28 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>100987686</v>
+        <v>10986400</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>4717.29028732449</v>
+        <v>50273.5060469837</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>2026</v>
@@ -1638,16 +1638,16 @@
         <v>2024</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>235.8645143662245</v>
+        <v>13406.26827919565</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>23819411515.35877</v>
+        <v>147286625822.5551</v>
       </c>
       <c r="K24" s="10" t="n">
         <v>18</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -1697,10 +1697,10 @@
         <v>2024</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>259.5084795124105</v>
+        <v>1557.050877074463</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>23762604460.77077</v>
+        <v>142575626764.6246</v>
       </c>
       <c r="K25" s="10" t="n">
         <v>19</v>
@@ -1756,16 +1756,16 @@
         <v>2024</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>326.5164542854156</v>
+        <v>1959.098725712493</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>23400784837.40816</v>
+        <v>140404709024.449</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>20</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -1815,10 +1815,10 @@
         <v>2024</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>129.670805840387</v>
+        <v>778.0248350423219</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>22505971603.44257</v>
+        <v>135035829620.6554</v>
       </c>
       <c r="K27" s="10" t="n">
         <v>21</v>
@@ -1844,28 +1844,28 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>27196812</v>
+        <v>100987686</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Australia and New Zealand</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.778</v>
+        <v>0.111</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>64603.9856308464</v>
+        <v>4717.29028732449</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>2026</v>
@@ -1874,16 +1874,16 @@
         <v>2024</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>717.8220625649603</v>
+        <v>1257.944076619864</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>19522471685.03146</v>
+        <v>127036861415.2468</v>
       </c>
       <c r="K28" s="10" t="n">
         <v>22</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -1903,28 +1903,28 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>48848840</v>
+        <v>36559233</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.778</v>
+        <v>0.556</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>35326.7683069278</v>
+        <v>25103.565661423</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>2026</v>
@@ -1933,16 +1933,16 @@
         <v>2024</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>392.5196478547535</v>
+        <v>3347.142088189733</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>19174129474.9132</v>
+        <v>122368947486.235</v>
       </c>
       <c r="K29" s="10" t="n">
         <v>23</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -1962,28 +1962,28 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>251269164</v>
+        <v>27196812</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>PAK</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Australia and New Zealand</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>0.778</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1478.77277977996</v>
+        <v>64603.9856308464</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>2026</v>
@@ -1992,16 +1992,16 @@
         <v>2024</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>73.93863898899801</v>
+        <v>4306.932375389762</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>18578500006.06334</v>
+        <v>117134830110.1888</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>24</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2021,28 +2021,28 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>9974400</v>
+        <v>251269164</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>PAK</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>54176.6844383302</v>
+        <v>1478.77277977996</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>2026</v>
@@ -2051,16 +2051,16 @@
         <v>2024</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1805.889481277674</v>
+        <v>443.631833933988</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>18012664042.05603</v>
+        <v>111471000036.38</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>25</v>
       </c>
       <c r="L31" s="10" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2080,28 +2080,28 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45696159</v>
+        <v>9974400</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.444</v>
+        <v>0.333</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>13969.7836603737</v>
+        <v>54176.6844383302</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>2026</v>
@@ -2110,16 +2110,16 @@
         <v>2024</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>388.0495461214917</v>
+        <v>10835.33688766604</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>17732373759.44552</v>
+        <v>108075984252.3362</v>
       </c>
       <c r="K32" s="10" t="n">
         <v>26</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2139,28 +2139,28 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>36559233</v>
+        <v>45696159</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.667</v>
+        <v>0.444</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>25103.565661423</v>
+        <v>13969.7836603737</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>2026</v>
@@ -2169,16 +2169,16 @@
         <v>2024</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>418.3927610237166</v>
+        <v>2328.29727672895</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>15296118435.77937</v>
+        <v>106394242556.6731</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>27</v>
       </c>
       <c r="L33" s="10" t="n">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.222</v>
+        <v>0.111</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>3338.47371395895</v>
@@ -2228,16 +2228,16 @@
         <v>2024</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>129.8295333206258</v>
+        <v>890.25965705572</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>15130107650.13869</v>
+        <v>103749309600.951</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>28</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2257,28 +2257,28 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>20592571</v>
+        <v>115843670</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>14154.6324958076</v>
+        <v>3984.8315387656</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>2026</v>
@@ -2287,16 +2287,16 @@
         <v>2024</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>707.73162479038</v>
+        <v>796.96630775312</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>14574013732.44126</v>
+        <v>92323501956.47087</v>
       </c>
       <c r="K35" s="10" t="n">
         <v>29</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2346,10 +2346,10 @@
         <v>2024</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>303.680516171354</v>
+        <v>1822.083097028124</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>13982062880.76923</v>
+        <v>83892377284.61534</v>
       </c>
       <c r="K36" s="10" t="n">
         <v>30</v>
@@ -2375,28 +2375,28 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>115843670</v>
+        <v>17993485</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.444</v>
+        <v>0.778</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>3984.8315387656</v>
+        <v>67520.4218956281</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>2026</v>
@@ -2405,16 +2405,16 @@
         <v>2024</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>110.6897649657111</v>
+        <v>4501.361459708542</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>12822708605.0654</v>
+        <v>80995179904.84375</v>
       </c>
       <c r="K37" s="10" t="n">
         <v>31</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2434,28 +2434,28 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>52886363</v>
+        <v>20592571</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.444</v>
+        <v>0.111</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>7919.20886825345</v>
+        <v>14154.6324958076</v>
       </c>
       <c r="G38" s="8" t="n">
         <v>2026</v>
@@ -2464,16 +2464,16 @@
         <v>2024</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>219.9780241181514</v>
+        <v>3774.568665548693</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>11633837635.53531</v>
+        <v>77728073239.68672</v>
       </c>
       <c r="K38" s="10" t="n">
         <v>32</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2493,28 +2493,28 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>64007187</v>
+        <v>46814308</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.444</v>
+        <v>0.111</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>6267.186814093</v>
+        <v>5752.99076651465</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>2026</v>
@@ -2523,16 +2523,16 @@
         <v>2024</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>174.0885226136945</v>
+        <v>1534.130871070573</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>11142916621.48847</v>
+        <v>71819275110.60611</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>33</v>
       </c>
       <c r="L39" s="10" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2552,28 +2552,28 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>46814308</v>
+        <v>35557673</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.222</v>
+        <v>0.444</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>5752.99076651465</v>
+        <v>11874.4273684245</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>2026</v>
@@ -2582,16 +2582,16 @@
         <v>2024</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>223.727418697792</v>
+        <v>1979.07122807075</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>10473644286.96339</v>
+        <v>70371167571.44815</v>
       </c>
       <c r="K40" s="10" t="n">
         <v>34</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2611,16 +2611,16 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>34217848</v>
+        <v>52886363</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>8452.37167056621</v>
+        <v>7919.20886825345</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>2026</v>
@@ -2641,16 +2641,16 @@
         <v>2024</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>281.7457223522071</v>
+        <v>1319.868144708908</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>9640732302.098024</v>
+        <v>69803025813.21185</v>
       </c>
       <c r="K41" s="10" t="n">
         <v>35</v>
       </c>
       <c r="L41" s="10" t="n">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2670,28 +2670,28 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
-        <v>35557673</v>
+        <v>64007187</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.556</v>
+        <v>0.444</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>11874.4273684245</v>
+        <v>6267.186814093</v>
       </c>
       <c r="G42" s="8" t="n">
         <v>2026</v>
@@ -2700,16 +2700,16 @@
         <v>2024</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>263.8761637427667</v>
+        <v>1044.531135682167</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>9382822342.859753</v>
+        <v>66857499728.93082</v>
       </c>
       <c r="K42" s="10" t="n">
         <v>36</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -2729,28 +2729,28 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>6036860</v>
+        <v>232679478</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.667</v>
+        <v>0.222</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>90674.066632628</v>
+        <v>1084.16041805436</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>2026</v>
@@ -2759,16 +2759,16 @@
         <v>2024</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1511.234443877134</v>
+        <v>252.970764212684</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>9123110764.864115</v>
+        <v>58861105366.26839</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>37</v>
       </c>
       <c r="L43" s="10" t="n">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2788,28 +2788,28 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
-        <v>2857822</v>
+        <v>34217848</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>QAT</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.222</v>
+        <v>0.333</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>76688.6941743178</v>
+        <v>8452.37167056621</v>
       </c>
       <c r="G44" s="8" t="n">
         <v>2026</v>
@@ -2818,16 +2818,16 @@
         <v>2024</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>2982.338106779026</v>
+        <v>1690.474334113242</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>8522991452.991448</v>
+        <v>57844393812.58813</v>
       </c>
       <c r="K44" s="10" t="n">
         <v>38</v>
       </c>
       <c r="L44" s="10" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -2847,28 +2847,28 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>232679478</v>
+        <v>6036860</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>1084.16041805436</v>
+        <v>90674.066632628</v>
       </c>
       <c r="G45" s="8" t="n">
         <v>2026</v>
@@ -2877,16 +2877,16 @@
         <v>2024</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>36.13868060181201</v>
+        <v>9067.4066632628</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>8408729338.038343</v>
+        <v>54738664589.18467</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>39</v>
       </c>
       <c r="L45" s="10" t="n">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
@@ -2906,28 +2906,28 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>37860221</v>
+        <v>9177982</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.222</v>
+        <v>0.667</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>5389.47314453125</v>
+        <v>58268.8787651601</v>
       </c>
       <c r="G46" s="8" t="n">
         <v>2026</v>
@@ -2936,16 +2936,16 @@
         <v>2024</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>209.5906222873264</v>
+        <v>5826.887876516009</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>7935147279.325703</v>
+        <v>53479072046.68215</v>
       </c>
       <c r="K46" s="10" t="n">
         <v>40</v>
       </c>
       <c r="L46" s="10" t="n">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -2965,28 +2965,28 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>17993485</v>
+        <v>2857822</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>QAT</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.889</v>
+        <v>0.222</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>67520.4218956281</v>
+        <v>76688.6941743178</v>
       </c>
       <c r="G47" s="8" t="n">
         <v>2026</v>
@@ -2995,16 +2995,16 @@
         <v>2024</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>375.1134549757118</v>
+        <v>17894.02864067415</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>6749598325.403646</v>
+        <v>51137948717.94869</v>
       </c>
       <c r="K47" s="10" t="n">
         <v>41</v>
       </c>
       <c r="L47" s="10" t="n">
-        <v>174</v>
+        <v>75</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.667</v>
+        <v>0.556</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>20080.2096215595</v>
@@ -3054,16 +3054,16 @@
         <v>2024</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>334.6701603593249</v>
+        <v>2677.3612828746</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>6376070299.814428</v>
+        <v>51008562398.51543</v>
       </c>
       <c r="K48" s="10" t="n">
         <v>42</v>
       </c>
       <c r="L48" s="10" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3083,28 +3083,28 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>28405543</v>
+        <v>37860221</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>4217.59102643391</v>
+        <v>5389.47314453125</v>
       </c>
       <c r="G49" s="8" t="n">
         <v>2026</v>
@@ -3113,16 +3113,16 @@
         <v>2024</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>210.8795513216955</v>
+        <v>1257.543733723958</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>5990148162.889129</v>
+        <v>47610883675.95422</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>43</v>
       </c>
       <c r="L49" s="10" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3142,28 +3142,28 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
-        <v>9177982</v>
+        <v>132059767</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.778</v>
+        <v>0.111</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>58268.8787651601</v>
+        <v>1133.88279681719</v>
       </c>
       <c r="G50" s="8" t="n">
         <v>2026</v>
@@ -3172,16 +3172,16 @@
         <v>2024</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>647.431986279557</v>
+        <v>302.3687458179173</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>5942119116.298021</v>
+        <v>39930746120.79639</v>
       </c>
       <c r="K50" s="10" t="n">
         <v>44</v>
       </c>
       <c r="L50" s="10" t="n">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3201,28 +3201,28 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>132059767</v>
+        <v>28405543</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>1133.88279681719</v>
+        <v>4217.59102643391</v>
       </c>
       <c r="G51" s="8" t="n">
         <v>2026</v>
@@ -3231,16 +3231,16 @@
         <v>2024</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>44.09544209844628</v>
+        <v>1265.277307930173</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>5823233809.282806</v>
+        <v>35940888977.33477</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>45</v>
       </c>
       <c r="L51" s="10" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3260,28 +3260,28 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
-        <v>4897263</v>
+        <v>10405134</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>KWT</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.333</v>
+        <v>0.556</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>32717.7186631255</v>
+        <v>24626.1481858973</v>
       </c>
       <c r="G52" s="8" t="n">
         <v>2026</v>
@@ -3290,16 +3290,16 @@
         <v>2024</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>1090.590622104183</v>
+        <v>3283.486424786307</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>5340909101.7778</v>
+        <v>34165116237.08244</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>46</v>
       </c>
       <c r="L52" s="10" t="n">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3319,28 +3319,28 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>9005582</v>
+        <v>4897263</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>KWT</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.889</v>
+        <v>0.333</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>103998.186685604</v>
+        <v>32717.7186631255</v>
       </c>
       <c r="G53" s="8" t="n">
         <v>2026</v>
@@ -3349,16 +3349,16 @@
         <v>2024</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>577.7677038089114</v>
+        <v>6543.5437326251</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>5203134433.602864</v>
+        <v>32045454610.6668</v>
       </c>
       <c r="K53" s="10" t="n">
         <v>47</v>
       </c>
       <c r="L53" s="10" t="n">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3378,28 +3378,28 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
-        <v>36361859</v>
+        <v>9005582</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.111</v>
+        <v>0.889</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>3161.70010632875</v>
+        <v>103998.186685604</v>
       </c>
       <c r="G54" s="8" t="n">
         <v>2026</v>
@@ -3408,16 +3408,16 @@
         <v>2024</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>140.5200047257222</v>
+        <v>3466.606222853468</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>5109568598.516046</v>
+        <v>31218806601.61718</v>
       </c>
       <c r="K54" s="10" t="n">
         <v>48</v>
       </c>
       <c r="L54" s="10" t="n">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3437,28 +3437,28 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>18406359</v>
+        <v>9562065</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.111</v>
+        <v>0.556</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>6150.02571438505</v>
+        <v>23292.3263882478</v>
       </c>
       <c r="G55" s="8" t="n">
         <v>2026</v>
@@ -3467,16 +3467,16 @@
         <v>2024</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>273.3344761948911</v>
+        <v>3105.64351843304</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>5031092495.92012</v>
+        <v>29696365190.08543</v>
       </c>
       <c r="K55" s="10" t="n">
         <v>49</v>
       </c>
       <c r="L55" s="10" t="n">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3496,28 +3496,28 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
-        <v>38081173</v>
+        <v>36361859</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.444</v>
+        <v>0.222</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>4153.1943359375</v>
+        <v>3161.70010632875</v>
       </c>
       <c r="G56" s="8" t="n">
         <v>2026</v>
@@ -3526,16 +3526,16 @@
         <v>2024</v>
       </c>
       <c r="I56" s="7" t="n">
-        <v>115.3665093315972</v>
+        <v>737.7300248100416</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>4393292000.262669</v>
+        <v>26825235142.20924</v>
       </c>
       <c r="K56" s="10" t="n">
         <v>50</v>
       </c>
       <c r="L56" s="10" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3555,28 +3555,28 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>10405134</v>
+        <v>18406359</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0.667</v>
+        <v>0.222</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>24626.1481858973</v>
+        <v>6150.02571438505</v>
       </c>
       <c r="G57" s="8" t="n">
         <v>2026</v>
@@ -3585,16 +3585,16 @@
         <v>2024</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>410.4358030982882</v>
+        <v>1435.006000023179</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>4270639529.635304</v>
+        <v>26413235603.58063</v>
       </c>
       <c r="K57" s="10" t="n">
         <v>51</v>
       </c>
       <c r="L57" s="10" t="n">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3614,28 +3614,28 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
-        <v>5281538</v>
+        <v>38081173</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>OMN</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.222</v>
+        <v>0.444</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>20285.2272897377</v>
+        <v>4153.1943359375</v>
       </c>
       <c r="G58" s="8" t="n">
         <v>2026</v>
@@ -3644,16 +3644,16 @@
         <v>2024</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>788.8699501564662</v>
+        <v>692.1990559895833</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>4166446618.809482</v>
+        <v>26359752001.57601</v>
       </c>
       <c r="K58" s="10" t="n">
         <v>52</v>
       </c>
       <c r="L58" s="10" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3673,28 +3673,28 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>18135478</v>
+        <v>5281538</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>OMN</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>6874.705739766</v>
+        <v>20285.2272897377</v>
       </c>
       <c r="G59" s="8" t="n">
         <v>2026</v>
@@ -3703,16 +3703,16 @@
         <v>2024</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>229.1568579922001</v>
+        <v>4733.219700938796</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>4155869156.666668</v>
+        <v>24998679712.85689</v>
       </c>
       <c r="K59" s="10" t="n">
         <v>53</v>
       </c>
       <c r="L59" s="10" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
@@ -3732,28 +3732,28 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
-        <v>56432944</v>
+        <v>18135478</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
         <v>0.333</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>2132.43452097647</v>
+        <v>6874.705739766</v>
       </c>
       <c r="G60" s="8" t="n">
         <v>2026</v>
@@ -3762,16 +3762,16 @@
         <v>2024</v>
       </c>
       <c r="I60" s="7" t="n">
-        <v>71.08115069921568</v>
+        <v>1374.9411479532</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>4011318596.864399</v>
+        <v>24935214940</v>
       </c>
       <c r="K60" s="10" t="n">
         <v>54</v>
       </c>
       <c r="L60" s="10" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3791,28 +3791,28 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>9132629</v>
+        <v>56432944</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>8317.633999137919</v>
+        <v>2132.43452097647</v>
       </c>
       <c r="G61" s="8" t="n">
         <v>2026</v>
@@ -3821,16 +3821,16 @@
         <v>2024</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>415.881699956896</v>
+        <v>426.4869041952941</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>3798093273.595647</v>
+        <v>24067911581.18639</v>
       </c>
       <c r="K61" s="10" t="n">
         <v>55</v>
       </c>
       <c r="L61" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -3850,28 +3850,28 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
-        <v>10202830</v>
+        <v>9132629</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>AZE</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>7283.8499076179</v>
+        <v>8317.633999137919</v>
       </c>
       <c r="G62" s="8" t="n">
         <v>2026</v>
@@ -3880,10 +3880,10 @@
         <v>2024</v>
       </c>
       <c r="I62" s="7" t="n">
-        <v>364.192495380895</v>
+        <v>2495.290199741376</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>3715794117.647057</v>
+        <v>22788559641.57388</v>
       </c>
       <c r="K62" s="10" t="n">
         <v>56</v>
@@ -3909,28 +3909,28 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>9562065</v>
+        <v>10202830</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>23292.3263882478</v>
+        <v>7283.8499076179</v>
       </c>
       <c r="G63" s="8" t="n">
         <v>2026</v>
@@ -3939,16 +3939,16 @@
         <v>2024</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>388.20543980413</v>
+        <v>2185.15497228537</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>3712045648.760679</v>
+        <v>22294764705.88234</v>
       </c>
       <c r="K63" s="10" t="n">
         <v>57</v>
       </c>
       <c r="L63" s="10" t="n">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -3998,10 +3998,10 @@
         <v>2024</v>
       </c>
       <c r="I64" s="7" t="n">
-        <v>67.95250078005351</v>
+        <v>407.715004680321</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>3703417476.190487</v>
+        <v>22220504857.14292</v>
       </c>
       <c r="K64" s="10" t="n">
         <v>58</v>
@@ -4027,28 +4027,28 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>11427557</v>
+        <v>10694681</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0.444</v>
+        <v>0.778</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>10875.6618443092</v>
+        <v>29292.242104753</v>
       </c>
       <c r="G65" s="8" t="n">
         <v>2026</v>
@@ -4057,16 +4057,16 @@
         <v>2024</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>302.1017178974778</v>
+        <v>1952.816140316867</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>3452284601.071348</v>
+        <v>20884745672.34014</v>
       </c>
       <c r="K65" s="10" t="n">
         <v>59</v>
       </c>
       <c r="L65" s="10" t="n">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4086,28 +4086,28 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>37885849</v>
+        <v>11427557</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>DOM</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>2665.87444776753</v>
+        <v>10875.6618443092</v>
       </c>
       <c r="G66" s="8" t="n">
         <v>2026</v>
@@ -4116,16 +4116,16 @@
         <v>2024</v>
       </c>
       <c r="I66" s="7" t="n">
-        <v>88.86248159225102</v>
+        <v>1812.610307384866</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>3366630559.369301</v>
+        <v>20713707606.42808</v>
       </c>
       <c r="K66" s="10" t="n">
         <v>60</v>
       </c>
       <c r="L66" s="10" t="n">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4145,28 +4145,28 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>21916000</v>
+        <v>37885849</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>LKA</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
         <v>0.333</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>4515.56787322732</v>
+        <v>2665.87444776753</v>
       </c>
       <c r="G67" s="8" t="n">
         <v>2026</v>
@@ -4175,16 +4175,16 @@
         <v>2024</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>150.5189291075773</v>
+        <v>533.174889553506</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>3298772850.321665</v>
+        <v>20199783356.21581</v>
       </c>
       <c r="K67" s="10" t="n">
         <v>61</v>
       </c>
       <c r="L67" s="10" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4204,28 +4204,28 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
-        <v>109276265</v>
+        <v>21916000</v>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>LKA</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>649.383338556725</v>
+        <v>4515.56787322732</v>
       </c>
       <c r="G68" s="8" t="n">
         <v>2026</v>
@@ -4234,16 +4234,16 @@
         <v>2024</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>28.86148171363222</v>
+        <v>903.113574645464</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>3153874924.031529</v>
+        <v>19792637101.92999</v>
       </c>
       <c r="K68" s="10" t="n">
         <v>62</v>
       </c>
       <c r="L68" s="10" t="n">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4263,28 +4263,28 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>6441421</v>
+        <v>109276265</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0.444</v>
+        <v>0.111</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>17596.0173663521</v>
+        <v>649.383338556725</v>
       </c>
       <c r="G69" s="8" t="n">
         <v>2026</v>
@@ -4293,16 +4293,16 @@
         <v>2024</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>488.7782601764473</v>
+        <v>173.1688902817933</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>3148426549.444031</v>
+        <v>18923249544.18917</v>
       </c>
       <c r="K69" s="10" t="n">
         <v>63</v>
       </c>
       <c r="L69" s="10" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4322,28 +4322,28 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
-        <v>31934230</v>
+        <v>6441421</v>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>2727.8935220697</v>
+        <v>17596.0173663521</v>
       </c>
       <c r="G70" s="8" t="n">
         <v>2026</v>
@@ -4352,16 +4352,16 @@
         <v>2024</v>
       </c>
       <c r="I70" s="7" t="n">
-        <v>90.92978406899002</v>
+        <v>2932.669561058683</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>2903772638.309463</v>
+        <v>18890559296.66418</v>
       </c>
       <c r="K70" s="10" t="n">
         <v>64</v>
       </c>
       <c r="L70" s="10" t="n">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4381,28 +4381,28 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>7494498</v>
+        <v>5422069</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>TKM</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>6856.65802730208</v>
+        <v>25992.6748502048</v>
       </c>
       <c r="G71" s="8" t="n">
         <v>2026</v>
@@ -4411,16 +4411,16 @@
         <v>2024</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>342.832901365104</v>
+        <v>3465.689980027306</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>2569360493.614969</v>
+        <v>18791210204.31668</v>
       </c>
       <c r="K71" s="10" t="n">
         <v>65</v>
       </c>
       <c r="L71" s="10" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4440,28 +4440,28 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
-        <v>6586476</v>
+        <v>31934230</v>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>SRB</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0.444</v>
+        <v>0.333</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>13679.2065983557</v>
+        <v>2727.8935220697</v>
       </c>
       <c r="G72" s="8" t="n">
         <v>2026</v>
@@ -4470,16 +4470,16 @@
         <v>2024</v>
       </c>
       <c r="I72" s="7" t="n">
-        <v>379.9779610654361</v>
+        <v>545.57870441394</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>2502715721.08643</v>
+        <v>17422635829.85678</v>
       </c>
       <c r="K72" s="10" t="n">
         <v>66</v>
       </c>
       <c r="L72" s="10" t="n">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4499,28 +4499,28 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>50448963</v>
+        <v>7494498</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>TKM</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>984.607666015625</v>
+        <v>6856.65802730208</v>
       </c>
       <c r="G73" s="8" t="n">
         <v>2026</v>
@@ -4529,10 +4529,10 @@
         <v>2024</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>49.23038330078126</v>
+        <v>2056.997408190624</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>2483621785.616931</v>
+        <v>15416162961.68981</v>
       </c>
       <c r="K73" s="10" t="n">
         <v>67</v>
@@ -4558,28 +4558,28 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
-        <v>12413315</v>
+        <v>6586476</v>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>SRB</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.111</v>
+        <v>0.444</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>4421.16609889999</v>
+        <v>13679.2065983557</v>
       </c>
       <c r="G74" s="8" t="n">
         <v>2026</v>
@@ -4588,16 +4588,16 @@
         <v>2024</v>
       </c>
       <c r="I74" s="7" t="n">
-        <v>196.4962710622218</v>
+        <v>2279.867766392616</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>2439170109.020743</v>
+        <v>15016294326.51857</v>
       </c>
       <c r="K74" s="10" t="n">
         <v>68</v>
       </c>
       <c r="L74" s="10" t="n">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -4617,16 +4617,16 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>7381023</v>
+        <v>50448963</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>6569.16408678648</v>
+        <v>984.607666015625</v>
       </c>
       <c r="G75" s="8" t="n">
         <v>2026</v>
@@ -4647,10 +4647,10 @@
         <v>2024</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>328.458204339324</v>
+        <v>295.3822998046875</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>2424357560.767251</v>
+        <v>14901730713.70159</v>
       </c>
       <c r="K75" s="10" t="n">
         <v>69</v>
@@ -4676,28 +4676,28 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
-        <v>29123744</v>
+        <v>7381023</v>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>1830.00833684727</v>
+        <v>6569.16408678648</v>
       </c>
       <c r="G76" s="8" t="n">
         <v>2026</v>
@@ -4706,16 +4706,16 @@
         <v>2024</v>
       </c>
       <c r="I76" s="7" t="n">
-        <v>81.33370385987867</v>
+        <v>1970.749226035944</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>2368741969.786918</v>
+        <v>14546145364.6035</v>
       </c>
       <c r="K76" s="10" t="n">
         <v>70</v>
       </c>
       <c r="L76" s="10" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4735,28 +4735,28 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>1588670</v>
+        <v>50015092</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>BHR</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>29653.5682731534</v>
+        <v>1077.91278452817</v>
       </c>
       <c r="G77" s="8" t="n">
         <v>2026</v>
@@ -4765,16 +4765,16 @@
         <v>2024</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>1482.67841365767</v>
+        <v>287.443409207512</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>2355486715.42553</v>
+        <v>14376508556.30736</v>
       </c>
       <c r="K77" s="10" t="n">
         <v>71</v>
       </c>
       <c r="L77" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -4794,28 +4794,28 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
-        <v>5422069</v>
+        <v>29123744</v>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0.667</v>
+        <v>0.111</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>25992.6748502048</v>
+        <v>1830.00833684727</v>
       </c>
       <c r="G78" s="8" t="n">
         <v>2026</v>
@@ -4824,16 +4824,16 @@
         <v>2024</v>
       </c>
       <c r="I78" s="7" t="n">
-        <v>433.2112475034132</v>
+        <v>488.002223159272</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>2348901275.539584</v>
+        <v>14212451818.72151</v>
       </c>
       <c r="K78" s="10" t="n">
         <v>72</v>
       </c>
       <c r="L78" s="10" t="n">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -4853,28 +4853,28 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>17638801</v>
+        <v>1588670</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>KHM</t>
+          <t>BHR</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>2627.87969756224</v>
+        <v>29653.5682731534</v>
       </c>
       <c r="G79" s="8" t="n">
         <v>2026</v>
@@ -4883,10 +4883,10 @@
         <v>2024</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>131.393984878112</v>
+        <v>8896.070481946019</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>2317632351.862027</v>
+        <v>14132920292.55318</v>
       </c>
       <c r="K79" s="10" t="n">
         <v>73</v>
@@ -4912,28 +4912,28 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
-        <v>50015092</v>
+        <v>17638801</v>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>KHM</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>1077.91278452817</v>
+        <v>2627.87969756224</v>
       </c>
       <c r="G80" s="8" t="n">
         <v>2026</v>
@@ -4942,16 +4942,16 @@
         <v>2024</v>
       </c>
       <c r="I80" s="7" t="n">
-        <v>41.91883050942884</v>
+        <v>788.3639092686719</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>2096574164.46149</v>
+        <v>13905794111.17216</v>
       </c>
       <c r="K80" s="10" t="n">
         <v>74</v>
       </c>
       <c r="L80" s="10" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4971,28 +4971,28 @@
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>10905028</v>
+        <v>68560157</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0.889</v>
+        <v>0.444</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>31823.3078290564</v>
+        <v>1186.71691894531</v>
       </c>
       <c r="G81" s="8" t="n">
         <v>2026</v>
@@ -5001,16 +5001,16 @@
         <v>2024</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>176.796154605869</v>
+        <v>197.7861531575517</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>1927967016.26933</v>
+        <v>13560249712.90779</v>
       </c>
       <c r="K81" s="10" t="n">
         <v>75</v>
       </c>
       <c r="L81" s="10" t="n">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="N81" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O81" s="6" t="inlineStr">
@@ -5030,28 +5030,28 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>34427414</v>
+        <v>12413315</v>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.556</v>
+        <v>0.222</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>2390.77237652715</v>
+        <v>4421.16609889999</v>
       </c>
       <c r="G82" s="8" t="n">
         <v>2026</v>
@@ -5060,16 +5060,16 @@
         <v>2024</v>
       </c>
       <c r="I82" s="7" t="n">
-        <v>53.12827503393667</v>
+        <v>1031.605423076664</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>1829069119.699202</v>
+        <v>12805643072.35891</v>
       </c>
       <c r="K82" s="10" t="n">
         <v>76</v>
       </c>
       <c r="L82" s="10" t="n">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5089,28 +5089,28 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>68560157</v>
+        <v>10905028</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0.556</v>
+        <v>0.889</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>1186.71691894531</v>
+        <v>31823.3078290564</v>
       </c>
       <c r="G83" s="8" t="n">
         <v>2026</v>
@@ -5119,16 +5119,16 @@
         <v>2024</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>26.37148708767356</v>
+        <v>1060.776927635214</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>1808033295.054372</v>
+        <v>11567802097.61598</v>
       </c>
       <c r="K83" s="10" t="n">
         <v>77</v>
       </c>
       <c r="L83" s="10" t="n">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="N83" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O83" s="6" t="inlineStr">
@@ -5148,28 +5148,28 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>11552876</v>
+        <v>4515577</v>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>JOR</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0.333</v>
+        <v>0.556</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>4618.09592498567</v>
+        <v>19161.2188501596</v>
       </c>
       <c r="G84" s="8" t="n">
         <v>2026</v>
@@ -5178,16 +5178,16 @@
         <v>2024</v>
       </c>
       <c r="I84" s="7" t="n">
-        <v>153.9365308328557</v>
+        <v>2554.82918002128</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>1778409652.582158</v>
+        <v>11536527884.23295</v>
       </c>
       <c r="K84" s="10" t="n">
         <v>78</v>
       </c>
       <c r="L84" s="10" t="n">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
@@ -5207,28 +5207,28 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>6338193</v>
+        <v>16634373</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>5579.65969165029</v>
+        <v>2497.20332208763</v>
       </c>
       <c r="G85" s="8" t="n">
         <v>2026</v>
@@ -5237,16 +5237,16 @@
         <v>2024</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>278.9829845825145</v>
+        <v>665.9208858900347</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>1768248000.000001</v>
+        <v>11077176404.38527</v>
       </c>
       <c r="K85" s="10" t="n">
         <v>79</v>
       </c>
       <c r="L85" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5266,28 +5266,28 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
-        <v>10694681</v>
+        <v>19764771</v>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
         <v>0.889</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>29292.242104753</v>
+        <v>16709.8893972307</v>
       </c>
       <c r="G86" s="8" t="n">
         <v>2026</v>
@@ -5296,16 +5296,16 @@
         <v>2024</v>
       </c>
       <c r="I86" s="7" t="n">
-        <v>162.734678359739</v>
+        <v>556.9963132410236</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>1740395472.695012</v>
+        <v>11008904579.0531</v>
       </c>
       <c r="K86" s="10" t="n">
         <v>80</v>
       </c>
       <c r="L86" s="10" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5325,28 +5325,28 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>10825703</v>
+        <v>34427414</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>HND</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0.111</v>
+        <v>0.556</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>3426.43483328923</v>
+        <v>2390.77237652715</v>
       </c>
       <c r="G87" s="8" t="n">
         <v>2026</v>
@@ -5355,16 +5355,16 @@
         <v>2024</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>152.2859925906324</v>
+        <v>318.76965020362</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>1648602926.846387</v>
+        <v>10974414718.19521</v>
       </c>
       <c r="K87" s="10" t="n">
         <v>81</v>
       </c>
       <c r="L87" s="10" t="n">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
@@ -5384,28 +5384,28 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
-        <v>16634373</v>
+        <v>11552876</v>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>ZWE</t>
+          <t>JOR</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0.222</v>
+        <v>0.333</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>2497.20332208763</v>
+        <v>4618.09592498567</v>
       </c>
       <c r="G88" s="8" t="n">
         <v>2026</v>
@@ -5414,16 +5414,16 @@
         <v>2024</v>
       </c>
       <c r="I88" s="7" t="n">
-        <v>97.11346252563006</v>
+        <v>923.619184997134</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>1615421558.972852</v>
+        <v>10670457915.49295</v>
       </c>
       <c r="K88" s="10" t="n">
         <v>82</v>
       </c>
       <c r="L88" s="10" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -5443,28 +5443,28 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>6929153</v>
+        <v>6338193</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>6416.09708970845</v>
+        <v>5579.65969165029</v>
       </c>
       <c r="G89" s="8" t="n">
         <v>2026</v>
@@ -5473,16 +5473,16 @@
         <v>2024</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>213.8699029902817</v>
+        <v>1673.897907495087</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>1481937279.914819</v>
+        <v>10609488000.00001</v>
       </c>
       <c r="K89" s="10" t="n">
         <v>83</v>
       </c>
       <c r="L89" s="10" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
@@ -5502,28 +5502,28 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
-        <v>5287500</v>
+        <v>3866200</v>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Australia and New Zealand</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.889</v>
+        <v>0.667</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>49205.1792146792</v>
+        <v>24050.4397933135</v>
       </c>
       <c r="G90" s="8" t="n">
         <v>2026</v>
@@ -5532,16 +5532,16 @@
         <v>2024</v>
       </c>
       <c r="I90" s="7" t="n">
-        <v>273.3621067482179</v>
+        <v>2405.043979331349</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>1445402139.431202</v>
+        <v>9298381032.890863</v>
       </c>
       <c r="K90" s="10" t="n">
         <v>84</v>
       </c>
       <c r="L90" s="10" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
@@ -5561,28 +5561,28 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>4515577</v>
+        <v>6929153</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>19161.2188501596</v>
+        <v>6416.09708970845</v>
       </c>
       <c r="G91" s="8" t="n">
         <v>2026</v>
@@ -5591,16 +5591,16 @@
         <v>2024</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>319.3536475026601</v>
+        <v>1283.21941794169</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>1442065985.529119</v>
+        <v>8891623679.488916</v>
       </c>
       <c r="K91" s="10" t="n">
         <v>85</v>
       </c>
       <c r="L91" s="10" t="n">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -5620,28 +5620,28 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
-        <v>29651054</v>
+        <v>5287500</v>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Australia and New Zealand</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0.333</v>
+        <v>0.889</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>1447.31004458428</v>
+        <v>49205.1792146792</v>
       </c>
       <c r="G92" s="8" t="n">
         <v>2026</v>
@@ -5650,16 +5650,16 @@
         <v>2024</v>
       </c>
       <c r="I92" s="7" t="n">
-        <v>48.24366815280934</v>
+        <v>1640.172640489307</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>1430475609.55703</v>
+        <v>8672412836.587212</v>
       </c>
       <c r="K92" s="10" t="n">
         <v>86</v>
       </c>
       <c r="L92" s="10" t="n">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
@@ -5679,28 +5679,28 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>14754785</v>
+        <v>10825703</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>HND</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>1694.95375862193</v>
+        <v>3426.43483328923</v>
       </c>
       <c r="G93" s="8" t="n">
         <v>2026</v>
@@ -5709,16 +5709,16 @@
         <v>2024</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>84.74768793109651</v>
+        <v>799.5014611008204</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>1250433914.670424</v>
+        <v>8655165365.943535</v>
       </c>
       <c r="K93" s="10" t="n">
         <v>87</v>
       </c>
       <c r="L93" s="10" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5738,28 +5738,28 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
-        <v>12277109</v>
+        <v>29651054</v>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.556</v>
+        <v>0.333</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>4181.13789301228</v>
+        <v>1447.31004458428</v>
       </c>
       <c r="G94" s="8" t="n">
         <v>2026</v>
@@ -5768,16 +5768,16 @@
         <v>2024</v>
       </c>
       <c r="I94" s="7" t="n">
-        <v>92.9141754002729</v>
+        <v>289.462008916856</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>1140717459.034269</v>
+        <v>8582853657.342179</v>
       </c>
       <c r="K94" s="10" t="n">
         <v>88</v>
       </c>
       <c r="L94" s="10" t="n">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
@@ -5797,28 +5797,28 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>34631766</v>
+        <v>12277109</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>656.776824637306</v>
+        <v>4181.13789301228</v>
       </c>
       <c r="G95" s="8" t="n">
         <v>2026</v>
@@ -5827,16 +5827,16 @@
         <v>2024</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>32.8388412318653</v>
+        <v>696.8563155020466</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>1137267065.253111</v>
+        <v>8555380942.757016</v>
       </c>
       <c r="K95" s="10" t="n">
         <v>89</v>
       </c>
       <c r="L95" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -5856,28 +5856,28 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
-        <v>11772557</v>
+        <v>2888278</v>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>HTI</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0.111</v>
+        <v>0.667</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>2142.62330526788</v>
+        <v>29384.0189598663</v>
       </c>
       <c r="G96" s="8" t="n">
         <v>2026</v>
@@ -5886,16 +5886,16 @@
         <v>2024</v>
       </c>
       <c r="I96" s="7" t="n">
-        <v>95.22770245635022</v>
+        <v>2938.401895986629</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>1121073555.146423</v>
+        <v>8486921551.33647</v>
       </c>
       <c r="K96" s="10" t="n">
         <v>90</v>
       </c>
       <c r="L96" s="10" t="n">
-        <v>59</v>
+        <v>164</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -5915,28 +5915,28 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>10576502</v>
+        <v>14754785</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>3006.70564478923</v>
+        <v>1694.95375862193</v>
       </c>
       <c r="G97" s="8" t="n">
         <v>2026</v>
@@ -5945,16 +5945,16 @@
         <v>2024</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>100.2235214929744</v>
+        <v>508.486127586579</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>1060014275.517486</v>
+        <v>7502603488.022542</v>
       </c>
       <c r="K97" s="10" t="n">
         <v>91</v>
       </c>
       <c r="L97" s="10" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -5974,16 +5974,16 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
-        <v>3866200</v>
+        <v>2127400</v>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>24050.4397933135</v>
+        <v>34301.0318686594</v>
       </c>
       <c r="G98" s="8" t="n">
         <v>2026</v>
@@ -6004,16 +6004,16 @@
         <v>2024</v>
       </c>
       <c r="I98" s="7" t="n">
-        <v>267.2271088145946</v>
+        <v>3430.103186865939</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>1033153448.098986</v>
+        <v>7297201519.738598</v>
       </c>
       <c r="K98" s="10" t="n">
         <v>92</v>
       </c>
       <c r="L98" s="10" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="N98" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O98" s="6" t="inlineStr">
@@ -6033,28 +6033,28 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>6916140</v>
+        <v>34631766</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>NIC</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>2847.53966339498</v>
+        <v>656.776824637306</v>
       </c>
       <c r="G99" s="8" t="n">
         <v>2026</v>
@@ -6063,10 +6063,10 @@
         <v>2024</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>142.376983169749</v>
+        <v>197.0330473911918</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>984699148.3796278</v>
+        <v>6823602391.518665</v>
       </c>
       <c r="K99" s="10" t="n">
         <v>93</v>
@@ -6092,28 +6092,28 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
-        <v>20299123</v>
+        <v>10576502</v>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>TCD</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Melanesia</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>961.55975562506</v>
+        <v>3006.70564478923</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>2026</v>
@@ -6122,16 +6122,16 @@
         <v>2024</v>
       </c>
       <c r="I100" s="7" t="n">
-        <v>48.077987781253</v>
+        <v>601.3411289578461</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>975940987.5641518</v>
+        <v>6360085653.104917</v>
       </c>
       <c r="K100" s="10" t="n">
         <v>94</v>
       </c>
       <c r="L100" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -6151,28 +6151,28 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>3699557</v>
+        <v>23548781</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0.444</v>
+        <v>0.111</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>9241.491223137131</v>
+        <v>981.992649769081</v>
       </c>
       <c r="G101" s="8" t="n">
         <v>2026</v>
@@ -6181,16 +6181,16 @@
         <v>2024</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>256.708089531587</v>
+        <v>261.8647066050883</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>949706209.5832094</v>
+        <v>6166594627.472477</v>
       </c>
       <c r="K101" s="10" t="n">
         <v>95</v>
       </c>
       <c r="L101" s="10" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6210,28 +6210,28 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
-        <v>2888278</v>
+        <v>6916140</v>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>NIC</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>29384.0189598663</v>
+        <v>2847.53966339498</v>
       </c>
       <c r="G102" s="8" t="n">
         <v>2026</v>
@@ -6240,16 +6240,16 @@
         <v>2024</v>
       </c>
       <c r="I102" s="7" t="n">
-        <v>326.4890995540702</v>
+        <v>854.261899018494</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>942991283.4818306</v>
+        <v>5908194890.277767</v>
       </c>
       <c r="K102" s="10" t="n">
         <v>96</v>
       </c>
       <c r="L102" s="10" t="n">
-        <v>162</v>
+        <v>1</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6269,28 +6269,28 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>18501984</v>
+        <v>11772557</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>HTI</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0.444</v>
+        <v>0.222</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>1773.21829923448</v>
+        <v>2142.62330526788</v>
       </c>
       <c r="G103" s="8" t="n">
         <v>2026</v>
@@ -6299,16 +6299,16 @@
         <v>2024</v>
       </c>
       <c r="I103" s="7" t="n">
-        <v>49.25606386762445</v>
+        <v>499.9454378958387</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>911334905.5817657</v>
+        <v>5885636164.518721</v>
       </c>
       <c r="K103" s="10" t="n">
         <v>97</v>
       </c>
       <c r="L103" s="10" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6328,28 +6328,28 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
-        <v>23548781</v>
+        <v>20299123</v>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>TCD</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>981.992649769081</v>
+        <v>961.55975562506</v>
       </c>
       <c r="G104" s="8" t="n">
         <v>2026</v>
@@ -6358,16 +6358,16 @@
         <v>2024</v>
       </c>
       <c r="I104" s="7" t="n">
-        <v>38.18860304657537</v>
+        <v>288.467926687518</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>899295049.8397362</v>
+        <v>5855645925.384911</v>
       </c>
       <c r="K104" s="10" t="n">
         <v>98</v>
       </c>
       <c r="L104" s="10" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
@@ -6387,28 +6387,28 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>24478595</v>
+        <v>3699557</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>1094.61949265799</v>
+        <v>9241.491223137131</v>
       </c>
       <c r="G105" s="8" t="n">
         <v>2026</v>
@@ -6417,16 +6417,16 @@
         <v>2024</v>
       </c>
       <c r="I105" s="7" t="n">
-        <v>36.487316421933</v>
+        <v>1540.248537189522</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>893158241.3293471</v>
+        <v>5698237257.499256</v>
       </c>
       <c r="K105" s="10" t="n">
         <v>99</v>
       </c>
       <c r="L105" s="10" t="n">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="M105" s="6" t="inlineStr">
         <is>
@@ -6446,28 +6446,28 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
-        <v>42647492</v>
+        <v>18501984</v>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>413.757894705303</v>
+        <v>1773.21829923448</v>
       </c>
       <c r="G106" s="8" t="n">
         <v>2026</v>
@@ -6476,16 +6476,16 @@
         <v>2024</v>
       </c>
       <c r="I106" s="7" t="n">
-        <v>20.68789473526515</v>
+        <v>295.5363832057466</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>882286825.2190626</v>
+        <v>5468009433.490593</v>
       </c>
       <c r="K106" s="10" t="n">
         <v>100</v>
       </c>
       <c r="L106" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M106" s="6" t="inlineStr">
         <is>
@@ -6505,28 +6505,28 @@
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>1368333</v>
+        <v>24478595</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>TTO</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
         <v>0.333</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>18733.4110406494</v>
+        <v>1094.61949265799</v>
       </c>
       <c r="G107" s="8" t="n">
         <v>2026</v>
@@ -6535,16 +6535,16 @@
         <v>2024</v>
       </c>
       <c r="I107" s="7" t="n">
-        <v>624.4470346883135</v>
+        <v>218.923898531598</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>854451484.316164</v>
+        <v>5358949447.976082</v>
       </c>
       <c r="K107" s="10" t="n">
         <v>101</v>
       </c>
       <c r="L107" s="10" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M107" s="6" t="inlineStr">
         <is>
@@ -6564,28 +6564,28 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
-        <v>21314956</v>
+        <v>42647492</v>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>1187.10943350064</v>
+        <v>413.757894705303</v>
       </c>
       <c r="G108" s="8" t="n">
         <v>2026</v>
@@ -6594,16 +6594,16 @@
         <v>2024</v>
       </c>
       <c r="I108" s="7" t="n">
-        <v>39.57031445002134</v>
+        <v>124.1273684115909</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>843439511.4083691</v>
+        <v>5293720951.314375</v>
       </c>
       <c r="K108" s="10" t="n">
         <v>102</v>
       </c>
       <c r="L108" s="10" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="M108" s="6" t="inlineStr">
         <is>
@@ -6623,28 +6623,28 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>7769819</v>
+        <v>1358282</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>LAO</t>
+          <t>CYP</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>2123.97909415109</v>
+        <v>38674.29296875</v>
       </c>
       <c r="G109" s="8" t="n">
         <v>2026</v>
@@ -6653,16 +6653,16 @@
         <v>2024</v>
       </c>
       <c r="I109" s="7" t="n">
-        <v>106.1989547075545</v>
+        <v>3867.429296874999</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>825146656.0668964</v>
+        <v>5253059600.217968</v>
       </c>
       <c r="K109" s="10" t="n">
         <v>103</v>
       </c>
       <c r="L109" s="10" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="N109" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O109" s="6" t="inlineStr">
@@ -6682,28 +6682,28 @@
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
-        <v>2127400</v>
+        <v>1368333</v>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>TTO</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.778</v>
+        <v>0.333</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>34301.0318686594</v>
+        <v>18733.4110406494</v>
       </c>
       <c r="G110" s="8" t="n">
         <v>2026</v>
@@ -6712,16 +6712,16 @@
         <v>2024</v>
       </c>
       <c r="I110" s="7" t="n">
-        <v>381.122576318438</v>
+        <v>3746.68220812988</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>810800168.8598449</v>
+        <v>5126708905.896983</v>
       </c>
       <c r="K110" s="10" t="n">
         <v>104</v>
       </c>
       <c r="L110" s="10" t="n">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="M110" s="6" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="N110" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O110" s="6" t="inlineStr">
@@ -6741,28 +6741,28 @@
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>401283</v>
+        <v>21314956</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>BHS</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>39455.4466548546</v>
+        <v>1187.10943350064</v>
       </c>
       <c r="G111" s="8" t="n">
         <v>2026</v>
@@ -6771,16 +6771,16 @@
         <v>2024</v>
       </c>
       <c r="I111" s="7" t="n">
-        <v>1972.77233274273</v>
+        <v>237.421886700128</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>791640000.000001</v>
+        <v>5060637068.450214</v>
       </c>
       <c r="K111" s="10" t="n">
         <v>105</v>
       </c>
       <c r="L111" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M111" s="6" t="inlineStr">
         <is>
@@ -6800,28 +6800,28 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
-        <v>6332961</v>
+        <v>7769819</v>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>LAO</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Congo Republic</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F112" s="7" t="n">
-        <v>2482.2489948456</v>
+        <v>2123.97909415109</v>
       </c>
       <c r="G112" s="8" t="n">
         <v>2026</v>
@@ -6830,10 +6830,10 @@
         <v>2024</v>
       </c>
       <c r="I112" s="7" t="n">
-        <v>124.11244974228</v>
+        <v>637.193728245327</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>785999303.8323194</v>
+        <v>4950879936.401378</v>
       </c>
       <c r="K112" s="10" t="n">
         <v>106</v>
@@ -6859,28 +6859,28 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>31964956</v>
+        <v>3164253</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>MDG</t>
+          <t>BIH</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0.111</v>
+        <v>0.444</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>544.987501003384</v>
+        <v>9358.78768951134</v>
       </c>
       <c r="G113" s="8" t="n">
         <v>2026</v>
@@ -6889,16 +6889,16 @@
         <v>2024</v>
       </c>
       <c r="I113" s="7" t="n">
-        <v>24.22166671126151</v>
+        <v>1559.79794825189</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>774244510.6721388</v>
+        <v>4935595337.149887</v>
       </c>
       <c r="K113" s="10" t="n">
         <v>107</v>
       </c>
       <c r="L113" s="10" t="n">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="M113" s="6" t="inlineStr">
         <is>
@@ -6918,28 +6918,28 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
-        <v>462721</v>
+        <v>401283</v>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>BRN</t>
+          <t>BHS</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>Brunei Darussalam</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F114" s="7" t="n">
-        <v>33153.4738913513</v>
+        <v>39455.4466548546</v>
       </c>
       <c r="G114" s="8" t="n">
         <v>2026</v>
@@ -6948,10 +6948,10 @@
         <v>2024</v>
       </c>
       <c r="I114" s="7" t="n">
-        <v>1657.673694567565</v>
+        <v>11836.63399645638</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>767040429.6239983</v>
+        <v>4749840000.000006</v>
       </c>
       <c r="K114" s="10" t="n">
         <v>108</v>
@@ -6977,28 +6977,28 @@
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>2839175</v>
+        <v>6332961</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>JAM</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Congo Republic</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>7753.8006955432</v>
+        <v>2482.2489948456</v>
       </c>
       <c r="G115" s="8" t="n">
         <v>2026</v>
@@ -7007,16 +7007,16 @@
         <v>2024</v>
       </c>
       <c r="I115" s="7" t="n">
-        <v>258.4600231847734</v>
+        <v>744.67469845368</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>733813236.325629</v>
+        <v>4715995822.993916</v>
       </c>
       <c r="K115" s="10" t="n">
         <v>109</v>
       </c>
       <c r="L115" s="10" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="M115" s="6" t="inlineStr">
         <is>
@@ -7036,28 +7036,28 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
-        <v>3033500</v>
+        <v>462721</v>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>BRN</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Brunei Darussalam</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F116" s="7" t="n">
-        <v>8556.21406956719</v>
+        <v>33153.4738913513</v>
       </c>
       <c r="G116" s="8" t="n">
         <v>2026</v>
@@ -7066,16 +7066,16 @@
         <v>2024</v>
       </c>
       <c r="I116" s="7" t="n">
-        <v>237.6726130435331</v>
+        <v>9946.042167405389</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>720979871.6675576</v>
+        <v>4602242577.743989</v>
       </c>
       <c r="K116" s="10" t="n">
         <v>110</v>
       </c>
       <c r="L116" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M116" s="6" t="inlineStr">
         <is>
@@ -7095,28 +7095,28 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>14256567</v>
+        <v>2377128</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>999.65456165547</v>
+        <v>11377.7757431099</v>
       </c>
       <c r="G117" s="8" t="n">
         <v>2026</v>
@@ -7125,16 +7125,16 @@
         <v>2024</v>
       </c>
       <c r="I117" s="7" t="n">
-        <v>49.98272808277351</v>
+        <v>1896.295957184983</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>712582111.754842</v>
+        <v>4507738216.111225</v>
       </c>
       <c r="K117" s="10" t="n">
         <v>111</v>
       </c>
       <c r="L117" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M117" s="6" t="inlineStr">
         <is>
@@ -7154,28 +7154,28 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
-        <v>10590927</v>
+        <v>3033500</v>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>TJK</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F118" s="7" t="n">
-        <v>1341.20229027672</v>
+        <v>8556.21406956719</v>
       </c>
       <c r="G118" s="8" t="n">
         <v>2026</v>
@@ -7184,16 +7184,16 @@
         <v>2024</v>
       </c>
       <c r="I118" s="7" t="n">
-        <v>67.06011451383601</v>
+        <v>1426.035678261198</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>710228777.4276778</v>
+        <v>4325879230.005344</v>
       </c>
       <c r="K118" s="10" t="n">
         <v>112</v>
       </c>
       <c r="L118" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M118" s="6" t="inlineStr">
         <is>
@@ -7213,28 +7213,28 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>5805962</v>
+        <v>14256567</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>LBN</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>3477.72489842684</v>
+        <v>999.65456165547</v>
       </c>
       <c r="G119" s="8" t="n">
         <v>2026</v>
@@ -7243,16 +7243,16 @@
         <v>2024</v>
       </c>
       <c r="I119" s="7" t="n">
-        <v>115.9241632808947</v>
+        <v>299.896368496641</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>673051286.8906699</v>
+        <v>4275492670.529052</v>
       </c>
       <c r="K119" s="10" t="n">
         <v>113</v>
       </c>
       <c r="L119" s="10" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
@@ -7272,28 +7272,28 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
-        <v>27032412</v>
+        <v>10590927</v>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>TJK</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F120" s="7" t="n">
-        <v>735.270255787226</v>
+        <v>1341.20229027672</v>
       </c>
       <c r="G120" s="8" t="n">
         <v>2026</v>
@@ -7302,16 +7302,16 @@
         <v>2024</v>
       </c>
       <c r="I120" s="7" t="n">
-        <v>24.50900852624087</v>
+        <v>402.360687083016</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>662537616.1928561</v>
+        <v>4261372664.566065</v>
       </c>
       <c r="K120" s="10" t="n">
         <v>114</v>
       </c>
       <c r="L120" s="10" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="M120" s="6" t="inlineStr">
         <is>
@@ -7331,28 +7331,28 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>3164253</v>
+        <v>831087</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>BIH</t>
+          <t>GUY</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0.556</v>
+        <v>0.444</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>9358.78768951134</v>
+        <v>29675.2443873316</v>
       </c>
       <c r="G121" s="8" t="n">
         <v>2026</v>
@@ -7361,16 +7361,16 @@
         <v>2024</v>
       </c>
       <c r="I121" s="7" t="n">
-        <v>207.9730597669187</v>
+        <v>4945.874064555266</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>658079378.2866517</v>
+        <v>4110451638.689043</v>
       </c>
       <c r="K121" s="10" t="n">
         <v>115</v>
       </c>
       <c r="L121" s="10" t="n">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="M121" s="6" t="inlineStr">
         <is>
@@ -7390,28 +7390,28 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
-        <v>2521139</v>
+        <v>7221868</v>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>KGZ</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="F122" s="7" t="n">
-        <v>7695.75319445165</v>
+        <v>2420.18542283831</v>
       </c>
       <c r="G122" s="8" t="n">
         <v>2026</v>
@@ -7420,16 +7420,16 @@
         <v>2024</v>
       </c>
       <c r="I122" s="7" t="n">
-        <v>256.5251064817217</v>
+        <v>564.7099319956056</v>
       </c>
       <c r="J122" s="5" t="n">
-        <v>646735450.4302214</v>
+        <v>4078260587.161241</v>
       </c>
       <c r="K122" s="10" t="n">
         <v>116</v>
       </c>
       <c r="L122" s="10" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="M122" s="6" t="inlineStr">
         <is>
@@ -7449,28 +7449,28 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>1892516</v>
+        <v>31964956</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>MDG</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>6745.40013244916</v>
+        <v>544.987501003384</v>
       </c>
       <c r="G123" s="8" t="n">
         <v>2026</v>
@@ -7479,16 +7479,16 @@
         <v>2024</v>
       </c>
       <c r="I123" s="7" t="n">
-        <v>337.270006622458</v>
+        <v>127.1637502341229</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>638288883.8531078</v>
+        <v>4064783681.028729</v>
       </c>
       <c r="K123" s="10" t="n">
         <v>117</v>
       </c>
       <c r="L123" s="10" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="M123" s="6" t="inlineStr">
         <is>
@@ -7508,28 +7508,28 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
-        <v>2377128</v>
+        <v>5805962</v>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.556</v>
+        <v>0.333</v>
       </c>
       <c r="F124" s="7" t="n">
-        <v>11377.7757431099</v>
+        <v>3477.72489842684</v>
       </c>
       <c r="G124" s="8" t="n">
         <v>2026</v>
@@ -7538,16 +7538,16 @@
         <v>2024</v>
       </c>
       <c r="I124" s="7" t="n">
-        <v>252.8394609579978</v>
+        <v>695.544979685368</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>601031762.1481633</v>
+        <v>4038307721.344019</v>
       </c>
       <c r="K124" s="10" t="n">
         <v>118</v>
       </c>
       <c r="L124" s="10" t="n">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="M124" s="6" t="inlineStr">
         <is>
@@ -7567,28 +7567,28 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>1358282</v>
+        <v>27032412</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>CYP</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0.778</v>
+        <v>0.333</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>38674.29296875</v>
+        <v>735.270255787226</v>
       </c>
       <c r="G125" s="8" t="n">
         <v>2026</v>
@@ -7597,16 +7597,16 @@
         <v>2024</v>
       </c>
       <c r="I125" s="7" t="n">
-        <v>429.7143663194447</v>
+        <v>147.0540511574452</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>583673288.9131079</v>
+        <v>3975225697.157135</v>
       </c>
       <c r="K125" s="10" t="n">
         <v>119</v>
       </c>
       <c r="L125" s="10" t="n">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="M125" s="6" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="N125" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O125" s="6" t="inlineStr">
@@ -7626,28 +7626,28 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
-        <v>7221868</v>
+        <v>3524788</v>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>KGZ</t>
+          <t>MNG</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F126" s="7" t="n">
-        <v>2420.18542283831</v>
+        <v>6750.6301157724</v>
       </c>
       <c r="G126" s="8" t="n">
         <v>2026</v>
@@ -7656,16 +7656,16 @@
         <v>2024</v>
       </c>
       <c r="I126" s="7" t="n">
-        <v>80.67284742794368</v>
+        <v>1125.1050192954</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>582608655.3087487</v>
+        <v>3965756670.752194</v>
       </c>
       <c r="K126" s="10" t="n">
         <v>120</v>
       </c>
       <c r="L126" s="10" t="n">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="M126" s="6" t="inlineStr">
         <is>
@@ -7685,28 +7685,28 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>1245779</v>
+        <v>2521139</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0.222</v>
+        <v>0.333</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>11990.7798944837</v>
+        <v>7695.75319445165</v>
       </c>
       <c r="G127" s="8" t="n">
         <v>2026</v>
@@ -7715,16 +7715,16 @@
         <v>2024</v>
       </c>
       <c r="I127" s="7" t="n">
-        <v>466.3081070076994</v>
+        <v>1539.15063889033</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>580916847.2399448</v>
+        <v>3880412702.581328</v>
       </c>
       <c r="K127" s="10" t="n">
         <v>121</v>
       </c>
       <c r="L127" s="10" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="M127" s="6" t="inlineStr">
         <is>
@@ -7744,16 +7744,16 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="n">
-        <v>2538952</v>
+        <v>1892516</v>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F128" s="7" t="n">
-        <v>8230.043114511511</v>
+        <v>6745.40013244916</v>
       </c>
       <c r="G128" s="8" t="n">
         <v>2026</v>
@@ -7774,16 +7774,16 @@
         <v>2024</v>
       </c>
       <c r="I128" s="7" t="n">
-        <v>228.6123087364309</v>
+        <v>2023.620039734748</v>
       </c>
       <c r="J128" s="5" t="n">
-        <v>580435678.4909786</v>
+        <v>3829733303.118646</v>
       </c>
       <c r="K128" s="10" t="n">
         <v>122</v>
       </c>
       <c r="L128" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M128" s="6" t="inlineStr">
         <is>
@@ -7803,28 +7803,28 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>1824359</v>
+        <v>2839175</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>JAM</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>9291.85661671864</v>
+        <v>7753.8006955432</v>
       </c>
       <c r="G129" s="8" t="n">
         <v>2026</v>
@@ -7833,16 +7833,16 @@
         <v>2024</v>
       </c>
       <c r="I129" s="7" t="n">
-        <v>309.7285538906214</v>
+        <v>1292.300115923867</v>
       </c>
       <c r="J129" s="5" t="n">
-        <v>565056074.8473402</v>
+        <v>3669066181.628144</v>
       </c>
       <c r="K129" s="10" t="n">
         <v>123</v>
       </c>
       <c r="L129" s="10" t="n">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="M129" s="6" t="inlineStr">
         <is>
@@ -7862,28 +7862,28 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>38631</v>
+        <v>14462724</v>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F130" s="7" t="n">
-        <v>288001.433369041</v>
+        <v>1485.38018885134</v>
       </c>
       <c r="G130" s="8" t="n">
         <v>2026</v>
@@ -7892,16 +7892,16 @@
         <v>2024</v>
       </c>
       <c r="I130" s="7" t="n">
-        <v>14400.07166845205</v>
+        <v>247.5633648085567</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>556289168.6239712</v>
+        <v>3580440617.737468</v>
       </c>
       <c r="K130" s="10" t="n">
         <v>124</v>
       </c>
       <c r="L130" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M130" s="6" t="inlineStr">
         <is>
@@ -7921,28 +7921,28 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>831087</v>
+        <v>1245779</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>GUY</t>
+          <t>MUS</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0.556</v>
+        <v>0.222</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>29675.2443873316</v>
+        <v>11990.7798944837</v>
       </c>
       <c r="G131" s="8" t="n">
         <v>2026</v>
@@ -7951,16 +7951,16 @@
         <v>2024</v>
       </c>
       <c r="I131" s="7" t="n">
-        <v>659.4498752740355</v>
+        <v>2797.848642046197</v>
       </c>
       <c r="J131" s="5" t="n">
-        <v>548060218.4918724</v>
+        <v>3485501083.439669</v>
       </c>
       <c r="K131" s="10" t="n">
         <v>125</v>
       </c>
       <c r="L131" s="10" t="n">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="M131" s="6" t="inlineStr">
         <is>
@@ -7980,28 +7980,28 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
-        <v>9515236</v>
+        <v>2538952</v>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F132" s="7" t="n">
-        <v>1119.38160509429</v>
+        <v>8230.043114511511</v>
       </c>
       <c r="G132" s="8" t="n">
         <v>2026</v>
@@ -8010,16 +8010,16 @@
         <v>2024</v>
       </c>
       <c r="I132" s="7" t="n">
-        <v>55.96908025471451</v>
+        <v>1371.673852418585</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>532559007.3265486</v>
+        <v>3482614070.945871</v>
       </c>
       <c r="K132" s="10" t="n">
         <v>126</v>
       </c>
       <c r="L132" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M132" s="6" t="inlineStr">
         <is>
@@ -8039,28 +8039,28 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>19009151</v>
+        <v>1824359</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>629.538899449007</v>
+        <v>9291.85661671864</v>
       </c>
       <c r="G133" s="8" t="n">
         <v>2026</v>
@@ -8069,16 +8069,16 @@
         <v>2024</v>
       </c>
       <c r="I133" s="7" t="n">
-        <v>27.97950664217809</v>
+        <v>1858.371323343728</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>531866666.6666662</v>
+        <v>3390336449.084041</v>
       </c>
       <c r="K133" s="10" t="n">
         <v>127</v>
       </c>
       <c r="L133" s="10" t="n">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="M133" s="6" t="inlineStr">
         <is>
@@ -8098,28 +8098,28 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>5129910</v>
+        <v>38631</v>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>CRI</t>
+          <t>MCO</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="F134" s="7" t="n">
-        <v>18587.1532203482</v>
+        <v>288001.433369041</v>
       </c>
       <c r="G134" s="8" t="n">
         <v>2026</v>
@@ -8128,16 +8128,16 @@
         <v>2024</v>
       </c>
       <c r="I134" s="7" t="n">
-        <v>103.2619623352678</v>
+        <v>86400.4300107123</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>529724573.2033138</v>
+        <v>3337735011.743827</v>
       </c>
       <c r="K134" s="10" t="n">
         <v>128</v>
       </c>
       <c r="L134" s="10" t="n">
-        <v>174</v>
+        <v>1</v>
       </c>
       <c r="M134" s="6" t="inlineStr">
         <is>
@@ -8157,28 +8157,28 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>3524788</v>
+        <v>9515236</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>MNG</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>6750.6301157724</v>
+        <v>1119.38160509429</v>
       </c>
       <c r="G135" s="8" t="n">
         <v>2026</v>
@@ -8187,16 +8187,16 @@
         <v>2024</v>
       </c>
       <c r="I135" s="7" t="n">
-        <v>150.01400257272</v>
+        <v>335.814481528287</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>528767556.1002926</v>
+        <v>3195354043.959291</v>
       </c>
       <c r="K135" s="10" t="n">
         <v>129</v>
       </c>
       <c r="L135" s="10" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
@@ -8216,28 +8216,28 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="n">
-        <v>5169395</v>
+        <v>19009151</v>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
         <v>0.111</v>
       </c>
       <c r="F136" s="7" t="n">
-        <v>2110.12036938187</v>
+        <v>629.538899449007</v>
       </c>
       <c r="G136" s="8" t="n">
         <v>2026</v>
@@ -8246,16 +8246,16 @@
         <v>2024</v>
       </c>
       <c r="I136" s="7" t="n">
-        <v>93.78312752808313</v>
+        <v>167.8770398530685</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>484802030.5280353</v>
+        <v>3191199999.999998</v>
       </c>
       <c r="K136" s="10" t="n">
         <v>130</v>
       </c>
       <c r="L136" s="10" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M136" s="6" t="inlineStr">
         <is>
@@ -8275,28 +8275,28 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>14462724</v>
+        <v>5129910</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>CRI</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0.556</v>
+        <v>0.889</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>1485.38018885134</v>
+        <v>18587.1532203482</v>
       </c>
       <c r="G137" s="8" t="n">
         <v>2026</v>
@@ -8305,16 +8305,16 @@
         <v>2024</v>
       </c>
       <c r="I137" s="7" t="n">
-        <v>33.00844864114089</v>
+        <v>619.5717740116069</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>477392082.3649958</v>
+        <v>3178347439.219882</v>
       </c>
       <c r="K137" s="10" t="n">
         <v>131</v>
       </c>
       <c r="L137" s="10" t="n">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M137" s="6" t="inlineStr">
         <is>
@@ -8334,28 +8334,28 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
-        <v>40450</v>
+        <v>3386588</v>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>LIE</t>
+          <t>URY</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Liechtenstein</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="F138" s="7" t="n">
-        <v>206780.590353385</v>
+        <v>23906.5133029408</v>
       </c>
       <c r="G138" s="8" t="n">
         <v>2026</v>
@@ -8364,16 +8364,16 @@
         <v>2024</v>
       </c>
       <c r="I138" s="7" t="n">
-        <v>10339.02951766925</v>
+        <v>796.8837767646936</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>418213743.9897212</v>
+        <v>2698717035.78599</v>
       </c>
       <c r="K138" s="10" t="n">
         <v>132</v>
       </c>
       <c r="L138" s="10" t="n">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="M138" s="6" t="inlineStr">
         <is>
@@ -8393,28 +8393,28 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>21655286</v>
+        <v>5169395</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>522.5703936425469</v>
+        <v>2110.12036938187</v>
       </c>
       <c r="G139" s="8" t="n">
         <v>2026</v>
@@ -8423,16 +8423,16 @@
         <v>2024</v>
       </c>
       <c r="I139" s="7" t="n">
-        <v>17.41901312141824</v>
+        <v>492.3614195224364</v>
       </c>
       <c r="J139" s="5" t="n">
-        <v>377213710.9820646</v>
+        <v>2545210660.272185</v>
       </c>
       <c r="K139" s="10" t="n">
         <v>133</v>
       </c>
       <c r="L139" s="10" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="M139" s="6" t="inlineStr">
         <is>
@@ -8452,28 +8452,28 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
-        <v>3030131</v>
+        <v>40450</v>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>LIE</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Liechtenstein</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>4413.12752211572</v>
+        <v>206780.590353385</v>
       </c>
       <c r="G140" s="8" t="n">
         <v>2026</v>
@@ -8482,16 +8482,16 @@
         <v>2024</v>
       </c>
       <c r="I140" s="7" t="n">
-        <v>98.06950049146046</v>
+        <v>62034.17710601549</v>
       </c>
       <c r="J140" s="5" t="n">
-        <v>297163433.5936896</v>
+        <v>2509282463.938327</v>
       </c>
       <c r="K140" s="10" t="n">
         <v>134</v>
       </c>
       <c r="L140" s="10" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="M140" s="6" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="F141" s="7" t="n">
         <v>43898.5781808597</v>
@@ -8541,16 +8541,16 @@
         <v>2024</v>
       </c>
       <c r="I141" s="7" t="n">
-        <v>487.7619797873303</v>
+        <v>4389.857818085969</v>
       </c>
       <c r="J141" s="5" t="n">
-        <v>277461938.9160835</v>
+        <v>2497157450.24475</v>
       </c>
       <c r="K141" s="10" t="n">
         <v>135</v>
       </c>
       <c r="L141" s="10" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M141" s="6" t="inlineStr">
         <is>
@@ -8570,28 +8570,28 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="n">
-        <v>527799</v>
+        <v>21655286</v>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>MDV</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
         <v>0.333</v>
       </c>
       <c r="F142" s="7" t="n">
-        <v>13379.3513577224</v>
+        <v>522.5703936425469</v>
       </c>
       <c r="G142" s="8" t="n">
         <v>2026</v>
@@ -8600,16 +8600,16 @@
         <v>2024</v>
       </c>
       <c r="I142" s="7" t="n">
-        <v>445.9783785907468</v>
+        <v>104.5140787285094</v>
       </c>
       <c r="J142" s="5" t="n">
-        <v>235386942.2418176</v>
+        <v>2263282265.892387</v>
       </c>
       <c r="K142" s="10" t="n">
         <v>136</v>
       </c>
       <c r="L142" s="10" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M142" s="6" t="inlineStr">
         <is>
@@ -8629,28 +8629,28 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>8642022</v>
+        <v>2402306</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="F143" s="7" t="n">
-        <v>806.654650417726</v>
+        <v>7576.19589413326</v>
       </c>
       <c r="G143" s="8" t="n">
         <v>2026</v>
@@ -8659,16 +8659,16 @@
         <v>2024</v>
       </c>
       <c r="I143" s="7" t="n">
-        <v>26.88848834725754</v>
+        <v>757.6195894133258</v>
       </c>
       <c r="J143" s="5" t="n">
-        <v>232370907.8437433</v>
+        <v>1820034085.365169</v>
       </c>
       <c r="K143" s="10" t="n">
         <v>137</v>
       </c>
       <c r="L143" s="10" t="n">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="M143" s="6" t="inlineStr">
         <is>
@@ -8688,28 +8688,28 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
-        <v>2402306</v>
+        <v>3030131</v>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0.778</v>
+        <v>0.556</v>
       </c>
       <c r="F144" s="7" t="n">
-        <v>7576.19589413326</v>
+        <v>4413.12752211572</v>
       </c>
       <c r="G144" s="8" t="n">
         <v>2026</v>
@@ -8718,16 +8718,16 @@
         <v>2024</v>
       </c>
       <c r="I144" s="7" t="n">
-        <v>84.17995437925848</v>
+        <v>588.4170029487627</v>
       </c>
       <c r="J144" s="5" t="n">
-        <v>202226009.4850189</v>
+        <v>1782980601.562137</v>
       </c>
       <c r="K144" s="10" t="n">
         <v>138</v>
       </c>
       <c r="L144" s="10" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="M144" s="6" t="inlineStr">
         <is>
@@ -8747,28 +8747,28 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>81938</v>
+        <v>527799</v>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>AND</t>
+          <t>MDV</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F145" s="7" t="n">
-        <v>49303.6491674336</v>
+        <v>13379.3513577224</v>
       </c>
       <c r="G145" s="8" t="n">
         <v>2026</v>
@@ -8777,16 +8777,16 @@
         <v>2024</v>
       </c>
       <c r="I145" s="7" t="n">
-        <v>2465.18245837168</v>
+        <v>2675.87027154448</v>
       </c>
       <c r="J145" s="5" t="n">
-        <v>201992120.2740587</v>
+        <v>1412321653.450905</v>
       </c>
       <c r="K145" s="10" t="n">
         <v>139</v>
       </c>
       <c r="L145" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M145" s="6" t="inlineStr">
         <is>
@@ -8806,28 +8806,28 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="n">
-        <v>1242822</v>
+        <v>8642022</v>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0.222</v>
+        <v>0.333</v>
       </c>
       <c r="F146" s="7" t="n">
-        <v>3909.55892378182</v>
+        <v>806.654650417726</v>
       </c>
       <c r="G146" s="8" t="n">
         <v>2026</v>
@@ -8836,16 +8836,16 @@
         <v>2024</v>
       </c>
       <c r="I146" s="7" t="n">
-        <v>152.0384025915152</v>
+        <v>161.3309300835452</v>
       </c>
       <c r="J146" s="5" t="n">
-        <v>188956671.5855921</v>
+        <v>1394225447.062459</v>
       </c>
       <c r="K146" s="10" t="n">
         <v>140</v>
       </c>
       <c r="L146" s="10" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="M146" s="6" t="inlineStr">
         <is>
@@ -8865,28 +8865,28 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>386506</v>
+        <v>1242822</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0.889</v>
+        <v>0.111</v>
       </c>
       <c r="F147" s="7" t="n">
-        <v>86040.5309851288</v>
+        <v>3909.55892378182</v>
       </c>
       <c r="G147" s="8" t="n">
         <v>2026</v>
@@ -8895,16 +8895,16 @@
         <v>2024</v>
       </c>
       <c r="I147" s="7" t="n">
-        <v>478.0029499173825</v>
+        <v>1042.549046341819</v>
       </c>
       <c r="J147" s="5" t="n">
-        <v>184751008.1607678</v>
+        <v>1295702890.872632</v>
       </c>
       <c r="K147" s="10" t="n">
         <v>141</v>
       </c>
       <c r="L147" s="10" t="n">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="M147" s="6" t="inlineStr">
         <is>
@@ -8924,28 +8924,28 @@
     </row>
     <row r="148">
       <c r="A148" s="5" t="n">
-        <v>1168722</v>
+        <v>81938</v>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>AND</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F148" s="7" t="n">
-        <v>3552.72335079222</v>
+        <v>49303.6491674336</v>
       </c>
       <c r="G148" s="8" t="n">
         <v>2026</v>
@@ -8954,16 +8954,16 @@
         <v>2024</v>
       </c>
       <c r="I148" s="7" t="n">
-        <v>138.1614636419197</v>
+        <v>14791.09475023008</v>
       </c>
       <c r="J148" s="5" t="n">
-        <v>161472342.1105117</v>
+        <v>1211952721.644352</v>
       </c>
       <c r="K148" s="10" t="n">
         <v>142</v>
       </c>
       <c r="L148" s="10" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="M148" s="6" t="inlineStr">
         <is>
@@ -8983,28 +8983,28 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>417072</v>
+        <v>386506</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="F149" s="7" t="n">
-        <v>7681.24400583113</v>
+        <v>86040.5309851288</v>
       </c>
       <c r="G149" s="8" t="n">
         <v>2026</v>
@@ -9013,16 +9013,16 @@
         <v>2024</v>
       </c>
       <c r="I149" s="7" t="n">
-        <v>384.0622002915566</v>
+        <v>2868.017699504295</v>
       </c>
       <c r="J149" s="5" t="n">
-        <v>160181590.0000001</v>
+        <v>1108506048.964607</v>
       </c>
       <c r="K149" s="10" t="n">
         <v>143</v>
       </c>
       <c r="L149" s="10" t="n">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="M149" s="6" t="inlineStr">
         <is>
@@ -9042,28 +9042,28 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="n">
-        <v>5612817</v>
+        <v>1168722</v>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0.333</v>
+        <v>0.111</v>
       </c>
       <c r="F150" s="7" t="n">
-        <v>851.497723870206</v>
+        <v>3552.72335079222</v>
       </c>
       <c r="G150" s="8" t="n">
         <v>2026</v>
@@ -9072,16 +9072,16 @@
         <v>2024</v>
       </c>
       <c r="I150" s="7" t="n">
-        <v>28.3832574623402</v>
+        <v>947.392893544592</v>
       </c>
       <c r="J150" s="5" t="n">
-        <v>159310030</v>
+        <v>1107238917.329223</v>
       </c>
       <c r="K150" s="10" t="n">
         <v>144</v>
       </c>
       <c r="L150" s="10" t="n">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="M150" s="6" t="inlineStr">
         <is>
@@ -9101,28 +9101,28 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>14047786</v>
+        <v>623525</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>MNE</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="F151" s="7" t="n">
-        <v>219.424830882698</v>
+        <v>13263.3281277699</v>
       </c>
       <c r="G151" s="8" t="n">
         <v>2026</v>
@@ -9131,16 +9131,16 @@
         <v>2024</v>
       </c>
       <c r="I151" s="7" t="n">
-        <v>10.9712415441349</v>
+        <v>1768.44375036932</v>
       </c>
       <c r="J151" s="5" t="n">
-        <v>154121653.3663166</v>
+        <v>1102668889.44903</v>
       </c>
       <c r="K151" s="10" t="n">
         <v>145</v>
       </c>
       <c r="L151" s="10" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="M151" s="6" t="inlineStr">
         <is>
@@ -9160,28 +9160,28 @@
     </row>
     <row r="152">
       <c r="A152" s="5" t="n">
-        <v>623525</v>
+        <v>928784</v>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>MNE</t>
+          <t>FJI</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Fiji</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Melanesia</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>0.667</v>
+        <v>0.444</v>
       </c>
       <c r="F152" s="7" t="n">
-        <v>13263.3281277699</v>
+        <v>6425.74151715712</v>
       </c>
       <c r="G152" s="8" t="n">
         <v>2026</v>
@@ -9190,16 +9190,16 @@
         <v>2024</v>
       </c>
       <c r="I152" s="7" t="n">
-        <v>221.0554687961651</v>
+        <v>1070.956919526187</v>
       </c>
       <c r="J152" s="5" t="n">
-        <v>137833611.1811288</v>
+        <v>994687651.5452096</v>
       </c>
       <c r="K152" s="10" t="n">
         <v>146</v>
       </c>
       <c r="L152" s="10" t="n">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="M152" s="6" t="inlineStr">
         <is>
@@ -9219,28 +9219,28 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>928784</v>
+        <v>417072</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>FJI</t>
+          <t>BLZ</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Fiji</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="F153" s="7" t="n">
-        <v>6425.74151715712</v>
+        <v>7681.24400583113</v>
       </c>
       <c r="G153" s="8" t="n">
         <v>2026</v>
@@ -9249,16 +9249,16 @@
         <v>2024</v>
       </c>
       <c r="I153" s="7" t="n">
-        <v>142.7942559368249</v>
+        <v>2304.373201749339</v>
       </c>
       <c r="J153" s="5" t="n">
-        <v>132625020.206028</v>
+        <v>961089540.0000002</v>
       </c>
       <c r="K153" s="10" t="n">
         <v>147</v>
       </c>
       <c r="L153" s="10" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
@@ -9278,28 +9278,28 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
-        <v>179744</v>
+        <v>5612817</v>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>St. Lucia</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F154" s="7" t="n">
-        <v>14181.6303351598</v>
+        <v>851.497723870206</v>
       </c>
       <c r="G154" s="8" t="n">
         <v>2026</v>
@@ -9308,16 +9308,16 @@
         <v>2024</v>
       </c>
       <c r="I154" s="7" t="n">
-        <v>709.08151675799</v>
+        <v>170.2995447740412</v>
       </c>
       <c r="J154" s="5" t="n">
-        <v>127453148.1481482</v>
+        <v>955860179.9999996</v>
       </c>
       <c r="K154" s="10" t="n">
         <v>148</v>
       </c>
       <c r="L154" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M154" s="6" t="inlineStr">
         <is>
@@ -9337,28 +9337,28 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>5330690</v>
+        <v>14047786</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F155" s="7" t="n">
-        <v>516.160999996036</v>
+        <v>219.424830882698</v>
       </c>
       <c r="G155" s="8" t="n">
         <v>2026</v>
@@ -9367,16 +9367,16 @@
         <v>2024</v>
       </c>
       <c r="I155" s="7" t="n">
-        <v>22.94048888871271</v>
+        <v>65.82744926480939</v>
       </c>
       <c r="J155" s="5" t="n">
-        <v>122288634.714172</v>
+        <v>924729920.1978996</v>
       </c>
       <c r="K155" s="10" t="n">
         <v>149</v>
       </c>
       <c r="L155" s="10" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="M155" s="6" t="inlineStr">
         <is>
@@ -9396,16 +9396,16 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="n">
-        <v>93772</v>
+        <v>179744</v>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>Antigua and Barbuda</t>
+          <t>St. Lucia</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
@@ -9417,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="F156" s="7" t="n">
-        <v>23542.4526945578</v>
+        <v>14181.6303351598</v>
       </c>
       <c r="G156" s="8" t="n">
         <v>2026</v>
@@ -9426,10 +9426,10 @@
         <v>2024</v>
       </c>
       <c r="I156" s="7" t="n">
-        <v>1177.12263472789</v>
+        <v>4254.489100547939</v>
       </c>
       <c r="J156" s="5" t="n">
-        <v>110381143.7037037</v>
+        <v>764718888.8888888</v>
       </c>
       <c r="K156" s="10" t="n">
         <v>150</v>
@@ -9455,28 +9455,28 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>33977</v>
+        <v>282467</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>BRB</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="F157" s="7" t="n">
-        <v>59879.7173015651</v>
+        <v>26544.8707282621</v>
       </c>
       <c r="G157" s="8" t="n">
         <v>2026</v>
@@ -9485,16 +9485,16 @@
         <v>2024</v>
       </c>
       <c r="I157" s="7" t="n">
-        <v>2993.985865078255</v>
+        <v>2654.48707282621</v>
       </c>
       <c r="J157" s="5" t="n">
-        <v>101726657.7377639</v>
+        <v>749805000.0000012</v>
       </c>
       <c r="K157" s="10" t="n">
         <v>151</v>
       </c>
       <c r="L157" s="10" t="n">
-        <v>1</v>
+        <v>161</v>
       </c>
       <c r="M157" s="6" t="inlineStr">
         <is>
@@ -9514,28 +9514,28 @@
     </row>
     <row r="158">
       <c r="A158" s="5" t="n">
-        <v>791524</v>
+        <v>634431</v>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>BTN</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F158" s="7" t="n">
-        <v>3831.32535494609</v>
+        <v>6961.78955961526</v>
       </c>
       <c r="G158" s="8" t="n">
         <v>2026</v>
@@ -9544,16 +9544,16 @@
         <v>2024</v>
       </c>
       <c r="I158" s="7" t="n">
-        <v>127.7108451648697</v>
+        <v>1160.298259935877</v>
       </c>
       <c r="J158" s="5" t="n">
-        <v>101086199.0082783</v>
+        <v>736129185.3493781</v>
       </c>
       <c r="K158" s="10" t="n">
         <v>152</v>
       </c>
       <c r="L158" s="10" t="n">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="M158" s="6" t="inlineStr">
         <is>
@@ -9573,28 +9573,28 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>2201352</v>
+        <v>5330690</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
         <v>0.111</v>
       </c>
       <c r="F159" s="7" t="n">
-        <v>1007.74151728028</v>
+        <v>516.160999996036</v>
       </c>
       <c r="G159" s="8" t="n">
         <v>2026</v>
@@ -9603,16 +9603,16 @@
         <v>2024</v>
       </c>
       <c r="I159" s="7" t="n">
-        <v>44.78851187912356</v>
+        <v>137.6429333322763</v>
       </c>
       <c r="J159" s="5" t="n">
-        <v>98595280.2021324</v>
+        <v>733731808.2850318</v>
       </c>
       <c r="K159" s="10" t="n">
         <v>153</v>
       </c>
       <c r="L159" s="10" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M159" s="6" t="inlineStr">
         <is>
@@ -9632,28 +9632,28 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
-        <v>634431</v>
+        <v>93772</v>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Antigua and Barbuda</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="F160" s="7" t="n">
-        <v>6961.78955961526</v>
+        <v>23542.4526945578</v>
       </c>
       <c r="G160" s="8" t="n">
         <v>2026</v>
@@ -9662,16 +9662,16 @@
         <v>2024</v>
       </c>
       <c r="I160" s="7" t="n">
-        <v>154.7064346581169</v>
+        <v>7062.73580836734</v>
       </c>
       <c r="J160" s="5" t="n">
-        <v>98150558.04658377</v>
+        <v>662286862.2222222</v>
       </c>
       <c r="K160" s="10" t="n">
         <v>154</v>
       </c>
       <c r="L160" s="10" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="M160" s="6" t="inlineStr">
         <is>
@@ -9691,28 +9691,28 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>282467</v>
+        <v>33977</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>BRB</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="F161" s="7" t="n">
-        <v>26544.8707282621</v>
+        <v>59879.7173015651</v>
       </c>
       <c r="G161" s="8" t="n">
         <v>2026</v>
@@ -9721,16 +9721,16 @@
         <v>2024</v>
       </c>
       <c r="I161" s="7" t="n">
-        <v>294.9430080918012</v>
+        <v>17963.91519046953</v>
       </c>
       <c r="J161" s="5" t="n">
-        <v>83311666.66666682</v>
+        <v>610359946.4265832</v>
       </c>
       <c r="K161" s="10" t="n">
         <v>155</v>
       </c>
       <c r="L161" s="10" t="n">
-        <v>162</v>
+        <v>1</v>
       </c>
       <c r="M161" s="6" t="inlineStr">
         <is>
@@ -9750,28 +9750,28 @@
     </row>
     <row r="162">
       <c r="A162" s="5" t="n">
-        <v>2337423</v>
+        <v>791524</v>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>LSO</t>
+          <t>BTN</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
         <v>0.333</v>
       </c>
       <c r="F162" s="7" t="n">
-        <v>971.9077182482901</v>
+        <v>3831.32535494609</v>
       </c>
       <c r="G162" s="8" t="n">
         <v>2026</v>
@@ -9780,16 +9780,16 @@
         <v>2024</v>
       </c>
       <c r="I162" s="7" t="n">
-        <v>32.39692394160967</v>
+        <v>766.2650709892181</v>
       </c>
       <c r="J162" s="5" t="n">
-        <v>75725315.15036911</v>
+        <v>606517194.0496699</v>
       </c>
       <c r="K162" s="10" t="n">
         <v>156</v>
       </c>
       <c r="L162" s="10" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M162" s="6" t="inlineStr">
         <is>
@@ -9809,28 +9809,28 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
-        <v>117207</v>
+        <v>2201352</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>GRD</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="F163" s="7" t="n">
-        <v>11705.0902976658</v>
+        <v>1007.74151728028</v>
       </c>
       <c r="G163" s="8" t="n">
         <v>2026</v>
@@ -9839,16 +9839,16 @@
         <v>2024</v>
       </c>
       <c r="I163" s="7" t="n">
-        <v>585.25451488329</v>
+        <v>235.1396873653987</v>
       </c>
       <c r="J163" s="5" t="n">
-        <v>68595925.92592576</v>
+        <v>517625221.0611951</v>
       </c>
       <c r="K163" s="10" t="n">
         <v>157</v>
       </c>
       <c r="L163" s="10" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="M163" s="6" t="inlineStr">
         <is>
@@ -9868,28 +9868,28 @@
     </row>
     <row r="164">
       <c r="A164" s="5" t="n">
-        <v>866628</v>
+        <v>2337423</v>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>LSO</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="F164" s="7" t="n">
-        <v>1662.75663312504</v>
+        <v>971.9077182482901</v>
       </c>
       <c r="G164" s="8" t="n">
         <v>2026</v>
@@ -9898,16 +9898,16 @@
         <v>2024</v>
       </c>
       <c r="I164" s="7" t="n">
-        <v>73.90029480555734</v>
+        <v>194.381543649658</v>
       </c>
       <c r="J164" s="5" t="n">
-        <v>64044064.68675055</v>
+        <v>454351890.9022146</v>
       </c>
       <c r="K164" s="10" t="n">
         <v>158</v>
       </c>
       <c r="L164" s="10" t="n">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="M164" s="6" t="inlineStr">
         <is>
@@ -9927,28 +9927,28 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>218019</v>
+        <v>117207</v>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>GRD</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>Samoa</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F165" s="7" t="n">
-        <v>5392.87761915762</v>
+        <v>11705.0902976658</v>
       </c>
       <c r="G165" s="8" t="n">
         <v>2026</v>
@@ -9957,10 +9957,10 @@
         <v>2024</v>
       </c>
       <c r="I165" s="7" t="n">
-        <v>269.643880957881</v>
+        <v>3511.52708929974</v>
       </c>
       <c r="J165" s="5" t="n">
-        <v>58787489.28255625</v>
+        <v>411575555.5555546</v>
       </c>
       <c r="K165" s="10" t="n">
         <v>159</v>
@@ -9986,28 +9986,28 @@
     </row>
     <row r="166">
       <c r="A166" s="5" t="n">
-        <v>100616</v>
+        <v>2759988</v>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>VCT</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>St. Vincent and the Grenadines</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F166" s="7" t="n">
-        <v>11501.2265187188</v>
+        <v>871.340291776294</v>
       </c>
       <c r="G166" s="8" t="n">
         <v>2026</v>
@@ -10016,16 +10016,16 @@
         <v>2024</v>
       </c>
       <c r="I166" s="7" t="n">
-        <v>575.0613259359401</v>
+        <v>145.2233819627156</v>
       </c>
       <c r="J166" s="5" t="n">
-        <v>57860370.37037054</v>
+        <v>400814791.5365117</v>
       </c>
       <c r="K166" s="10" t="n">
         <v>160</v>
       </c>
       <c r="L166" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M166" s="6" t="inlineStr">
         <is>
@@ -10045,28 +10045,28 @@
     </row>
     <row r="167">
       <c r="A167" s="5" t="n">
-        <v>46843</v>
+        <v>866628</v>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>KNA</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>St. Kitts and Nevis</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F167" s="7" t="n">
-        <v>23960.6534357084</v>
+        <v>1662.75663312504</v>
       </c>
       <c r="G167" s="8" t="n">
         <v>2026</v>
@@ -10075,16 +10075,16 @@
         <v>2024</v>
       </c>
       <c r="I167" s="7" t="n">
-        <v>1198.03267178542</v>
+        <v>443.401768833344</v>
       </c>
       <c r="J167" s="5" t="n">
-        <v>56119444.44444443</v>
+        <v>384264388.1205032</v>
       </c>
       <c r="K167" s="10" t="n">
         <v>161</v>
       </c>
       <c r="L167" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M167" s="6" t="inlineStr">
         <is>
@@ -10104,16 +10104,16 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>2759988</v>
+        <v>524877</v>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>CPV</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
@@ -10125,7 +10125,7 @@
         <v>0.556</v>
       </c>
       <c r="F168" s="7" t="n">
-        <v>871.340291776294</v>
+        <v>5192.48157325878</v>
       </c>
       <c r="G168" s="8" t="n">
         <v>2026</v>
@@ -10134,16 +10134,16 @@
         <v>2024</v>
       </c>
       <c r="I168" s="7" t="n">
-        <v>19.36311759502875</v>
+        <v>692.330876434504</v>
       </c>
       <c r="J168" s="5" t="n">
-        <v>53441972.20486822</v>
+        <v>363388553.4303132</v>
       </c>
       <c r="K168" s="10" t="n">
         <v>162</v>
       </c>
       <c r="L168" s="10" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="M168" s="6" t="inlineStr">
         <is>
@@ -10163,28 +10163,28 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>819198</v>
+        <v>218019</v>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>Solomon Islands</t>
+          <t>Samoa</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Polynesia</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F169" s="7" t="n">
-        <v>1933.55538435227</v>
+        <v>5392.87761915762</v>
       </c>
       <c r="G169" s="8" t="n">
         <v>2026</v>
@@ -10193,16 +10193,16 @@
         <v>2024</v>
       </c>
       <c r="I169" s="7" t="n">
-        <v>64.45184614507568</v>
+        <v>1617.863285747286</v>
       </c>
       <c r="J169" s="5" t="n">
-        <v>52798823.45835371</v>
+        <v>352724935.6953375</v>
       </c>
       <c r="K169" s="10" t="n">
         <v>163</v>
       </c>
       <c r="L169" s="10" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="M169" s="6" t="inlineStr">
         <is>
@@ -10222,28 +10222,28 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>524877</v>
+        <v>100616</v>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>CPV</t>
+          <t>VCT</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>St. Vincent and the Grenadines</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="F170" s="7" t="n">
-        <v>5192.48157325878</v>
+        <v>11501.2265187188</v>
       </c>
       <c r="G170" s="8" t="n">
         <v>2026</v>
@@ -10252,16 +10252,16 @@
         <v>2024</v>
       </c>
       <c r="I170" s="7" t="n">
-        <v>86.54135955431302</v>
+        <v>3450.36795561564</v>
       </c>
       <c r="J170" s="5" t="n">
-        <v>45423569.17878915</v>
+        <v>347162222.2222232</v>
       </c>
       <c r="K170" s="10" t="n">
         <v>164</v>
       </c>
       <c r="L170" s="10" t="n">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="M170" s="6" t="inlineStr">
         <is>
@@ -10281,16 +10281,16 @@
     </row>
     <row r="171">
       <c r="A171" s="5" t="n">
-        <v>66205</v>
+        <v>46843</v>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>DMA</t>
+          <t>KNA</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>St. Kitts and Nevis</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
@@ -10302,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="F171" s="7" t="n">
-        <v>10405.2787777582</v>
+        <v>23960.6534357084</v>
       </c>
       <c r="G171" s="8" t="n">
         <v>2026</v>
@@ -10311,10 +10311,10 @@
         <v>2024</v>
       </c>
       <c r="I171" s="7" t="n">
-        <v>520.2639388879101</v>
+        <v>7188.196030712519</v>
       </c>
       <c r="J171" s="5" t="n">
-        <v>34444074.07407408</v>
+        <v>336716666.6666665</v>
       </c>
       <c r="K171" s="10" t="n">
         <v>165</v>
@@ -10340,28 +10340,28 @@
     </row>
     <row r="172">
       <c r="A172" s="5" t="n">
-        <v>1400638</v>
+        <v>819198</v>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>Timor-Leste</t>
+          <t>Solomon Islands</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Melanesia</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="F172" s="7" t="n">
-        <v>1331.9705130185</v>
+        <v>1933.55538435227</v>
       </c>
       <c r="G172" s="8" t="n">
         <v>2026</v>
@@ -10370,16 +10370,16 @@
         <v>2024</v>
       </c>
       <c r="I172" s="7" t="n">
-        <v>22.19950855030834</v>
+        <v>386.711076870454</v>
       </c>
       <c r="J172" s="5" t="n">
-        <v>31093475.25688677</v>
+        <v>316792940.7501222</v>
       </c>
       <c r="K172" s="10" t="n">
         <v>166</v>
       </c>
       <c r="L172" s="10" t="n">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="M172" s="6" t="inlineStr">
         <is>
@@ -10399,28 +10399,28 @@
     </row>
     <row r="173">
       <c r="A173" s="5" t="n">
-        <v>104175</v>
+        <v>1400638</v>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>TON</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>Tonga</t>
+          <t>Timor-Leste</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="F173" s="7" t="n">
-        <v>5651.59373063157</v>
+        <v>1331.9705130185</v>
       </c>
       <c r="G173" s="8" t="n">
         <v>2026</v>
@@ -10429,16 +10429,16 @@
         <v>2024</v>
       </c>
       <c r="I173" s="7" t="n">
-        <v>282.5796865315785</v>
+        <v>177.5960684024667</v>
       </c>
       <c r="J173" s="5" t="n">
-        <v>29437738.84442719</v>
+        <v>248747802.0550941</v>
       </c>
       <c r="K173" s="10" t="n">
         <v>167</v>
       </c>
       <c r="L173" s="10" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="M173" s="6" t="inlineStr">
         <is>
@@ -10458,28 +10458,28 @@
     </row>
     <row r="174">
       <c r="A174" s="5" t="n">
-        <v>327777</v>
+        <v>66205</v>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>VUT</t>
+          <t>DMA</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>Vanuatu</t>
+          <t>Dominica</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="F174" s="7" t="n">
-        <v>3410.77023167097</v>
+        <v>10405.2787777582</v>
       </c>
       <c r="G174" s="8" t="n">
         <v>2026</v>
@@ -10488,16 +10488,16 @@
         <v>2024</v>
       </c>
       <c r="I174" s="7" t="n">
-        <v>75.79489403713268</v>
+        <v>3121.58363332746</v>
       </c>
       <c r="J174" s="5" t="n">
-        <v>24843822.98280924</v>
+        <v>206664444.4444445</v>
       </c>
       <c r="K174" s="10" t="n">
         <v>168</v>
       </c>
       <c r="L174" s="10" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="M174" s="6" t="inlineStr">
         <is>
@@ -10517,28 +10517,28 @@
     </row>
     <row r="175">
       <c r="A175" s="5" t="n">
-        <v>113160</v>
+        <v>327777</v>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>FSM</t>
+          <t>VUT</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>Micronesia, Fed. Sts.</t>
+          <t>Vanuatu</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Melanesia</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F175" s="7" t="n">
-        <v>4166.00476748564</v>
+        <v>3410.77023167097</v>
       </c>
       <c r="G175" s="8" t="n">
         <v>2026</v>
@@ -10547,16 +10547,16 @@
         <v>2024</v>
       </c>
       <c r="I175" s="7" t="n">
-        <v>208.300238374282</v>
+        <v>568.4617052784949</v>
       </c>
       <c r="J175" s="5" t="n">
-        <v>23571254.97443375</v>
+        <v>186328672.3710693</v>
       </c>
       <c r="K175" s="10" t="n">
         <v>169</v>
       </c>
       <c r="L175" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M175" s="6" t="inlineStr">
         <is>
@@ -10576,28 +10576,28 @@
     </row>
     <row r="176">
       <c r="A176" s="5" t="n">
-        <v>235536</v>
+        <v>104175</v>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>TON</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>Sao Tome and Principe</t>
+          <t>Tonga</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Polynesia</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F176" s="7" t="n">
-        <v>3490.56883486557</v>
+        <v>5651.59373063157</v>
       </c>
       <c r="G176" s="8" t="n">
         <v>2026</v>
@@ -10606,16 +10606,16 @@
         <v>2024</v>
       </c>
       <c r="I176" s="7" t="n">
-        <v>96.96024541293251</v>
+        <v>1695.478119189471</v>
       </c>
       <c r="J176" s="5" t="n">
-        <v>22837628.36358047</v>
+        <v>176626433.0665632</v>
       </c>
       <c r="K176" s="10" t="n">
         <v>170</v>
       </c>
       <c r="L176" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M176" s="6" t="inlineStr">
         <is>
@@ -10635,16 +10635,16 @@
     </row>
     <row r="177">
       <c r="A177" s="5" t="n">
-        <v>37548</v>
+        <v>113160</v>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>MHL</t>
+          <t>FSM</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>Marshall Islands</t>
+          <t>Micronesia, Fed. Sts.</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
@@ -10656,7 +10656,7 @@
         <v>0</v>
       </c>
       <c r="F177" s="7" t="n">
-        <v>7726.33668877794</v>
+        <v>4166.00476748564</v>
       </c>
       <c r="G177" s="8" t="n">
         <v>2026</v>
@@ -10665,10 +10665,10 @@
         <v>2024</v>
       </c>
       <c r="I177" s="7" t="n">
-        <v>386.316834438897</v>
+        <v>1249.801430245692</v>
       </c>
       <c r="J177" s="5" t="n">
-        <v>14505424.49951171</v>
+        <v>141427529.8466025</v>
       </c>
       <c r="K177" s="10" t="n">
         <v>171</v>
@@ -10694,28 +10694,28 @@
     </row>
     <row r="178">
       <c r="A178" s="5" t="n">
-        <v>17695</v>
+        <v>235536</v>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>Palau</t>
+          <t>Sao Tome and Principe</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F178" s="7" t="n">
-        <v>15610.8231931032</v>
+        <v>3490.56883486557</v>
       </c>
       <c r="G178" s="8" t="n">
         <v>2026</v>
@@ -10724,16 +10724,16 @@
         <v>2024</v>
       </c>
       <c r="I178" s="7" t="n">
-        <v>780.5411596551601</v>
+        <v>581.7614724775949</v>
       </c>
       <c r="J178" s="5" t="n">
-        <v>13811675.82009806</v>
+        <v>137025770.1814828</v>
       </c>
       <c r="K178" s="10" t="n">
         <v>172</v>
       </c>
       <c r="L178" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M178" s="6" t="inlineStr">
         <is>
@@ -10753,16 +10753,16 @@
     </row>
     <row r="179">
       <c r="A179" s="5" t="n">
-        <v>134518</v>
+        <v>37548</v>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>KIR</t>
+          <t>MHL</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>Kiribati</t>
+          <t>Marshall Islands</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
@@ -10771,10 +10771,10 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F179" s="7" t="n">
-        <v>2288.63471423684</v>
+        <v>7726.33668877794</v>
       </c>
       <c r="G179" s="8" t="n">
         <v>2026</v>
@@ -10783,16 +10783,16 @@
         <v>2024</v>
       </c>
       <c r="I179" s="7" t="n">
-        <v>101.7170984105262</v>
+        <v>2317.901006633382</v>
       </c>
       <c r="J179" s="5" t="n">
-        <v>13682780.64398717</v>
+        <v>87032546.99707024</v>
       </c>
       <c r="K179" s="10" t="n">
         <v>173</v>
       </c>
       <c r="L179" s="10" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="M179" s="6" t="inlineStr">
         <is>
@@ -10812,28 +10812,28 @@
     </row>
     <row r="180">
       <c r="A180" s="5" t="n">
-        <v>121354</v>
+        <v>17695</v>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>SYC</t>
+          <t>PLW</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Palau</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Micronesia</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="F180" s="7" t="n">
-        <v>17858.8226383978</v>
+        <v>15610.8231931032</v>
       </c>
       <c r="G180" s="8" t="n">
         <v>2026</v>
@@ -10842,16 +10842,16 @@
         <v>2024</v>
       </c>
       <c r="I180" s="7" t="n">
-        <v>99.21568132443227</v>
+        <v>4683.24695793096</v>
       </c>
       <c r="J180" s="5" t="n">
-        <v>12040219.79144515</v>
+        <v>82870054.92058833</v>
       </c>
       <c r="K180" s="10" t="n">
         <v>174</v>
       </c>
       <c r="L180" s="10" t="n">
-        <v>174</v>
+        <v>1</v>
       </c>
       <c r="M180" s="6" t="inlineStr">
         <is>
@@ -10871,28 +10871,28 @@
     </row>
     <row r="181">
       <c r="A181" s="5" t="n">
-        <v>11947</v>
+        <v>134518</v>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>NRU</t>
+          <t>KIR</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>Nauru</t>
+          <t>Kiribati</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Micronesia</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F181" s="7" t="n">
-        <v>13609.158837552</v>
+        <v>2288.63471423684</v>
       </c>
       <c r="G181" s="8" t="n">
         <v>2026</v>
@@ -10901,16 +10901,16 @@
         <v>2024</v>
       </c>
       <c r="I181" s="7" t="n">
-        <v>680.4579418776001</v>
+        <v>610.3025904631573</v>
       </c>
       <c r="J181" s="5" t="n">
-        <v>8129431.031611688</v>
+        <v>82096683.863923</v>
       </c>
       <c r="K181" s="10" t="n">
         <v>175</v>
       </c>
       <c r="L181" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M181" s="6" t="inlineStr">
         <is>
@@ -10930,28 +10930,28 @@
     </row>
     <row r="182">
       <c r="A182" s="5" t="n">
-        <v>9646</v>
+        <v>121354</v>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>TUV</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="F182" s="7" t="n">
-        <v>6344.7750188689</v>
+        <v>17858.8226383978</v>
       </c>
       <c r="G182" s="8" t="n">
         <v>2026</v>
@@ -10960,16 +10960,16 @@
         <v>2024</v>
       </c>
       <c r="I182" s="7" t="n">
-        <v>317.238750943445</v>
+        <v>595.2940879465935</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>3060084.99160047</v>
+        <v>72241318.74867092</v>
       </c>
       <c r="K182" s="10" t="n">
         <v>176</v>
       </c>
       <c r="L182" s="10" t="n">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="M182" s="6" t="inlineStr">
         <is>
@@ -10989,28 +10989,28 @@
     </row>
     <row r="183">
       <c r="A183" s="5" t="n">
-        <v>5572279</v>
+        <v>11947</v>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>NRU</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Nauru</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Polynesia</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F183" s="7" t="n">
-        <v>86785.4334489176</v>
+        <v>13609.158837552</v>
       </c>
       <c r="G183" s="8" t="n">
         <v>2026</v>
@@ -11019,16 +11019,16 @@
         <v>2024</v>
       </c>
       <c r="I183" s="7" t="n">
-        <v>0</v>
+        <v>4082.7476512656</v>
       </c>
       <c r="J183" s="5" t="n">
-        <v>0</v>
+        <v>48776586.18967012</v>
       </c>
       <c r="K183" s="10" t="n">
         <v>177</v>
       </c>
       <c r="L183" s="10" t="n">
-        <v>183</v>
+        <v>1</v>
       </c>
       <c r="M183" s="6" t="inlineStr">
         <is>
@@ -11048,46 +11048,46 @@
     </row>
     <row r="184">
       <c r="A184" s="5" t="n">
-        <v>677012</v>
+        <v>9646</v>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>TUV</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Polynesia</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="7" t="n">
+        <v>6344.7750188689</v>
+      </c>
+      <c r="G184" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H184" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="I184" s="7" t="n">
+        <v>1903.43250566067</v>
+      </c>
+      <c r="J184" s="5" t="n">
+        <v>18360509.94960282</v>
+      </c>
+      <c r="K184" s="10" t="n">
+        <v>178</v>
+      </c>
+      <c r="L184" s="10" t="n">
         <v>1</v>
-      </c>
-      <c r="F184" s="7" t="n">
-        <v>137781.681659123</v>
-      </c>
-      <c r="G184" s="8" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H184" s="9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="I184" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J184" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K184" s="10" t="n">
-        <v>177</v>
-      </c>
-      <c r="L184" s="10" t="n">
-        <v>183</v>
       </c>
       <c r="M184" s="6" t="inlineStr">
         <is>
@@ -11107,16 +11107,16 @@
     </row>
     <row r="185">
       <c r="A185" s="5" t="n">
-        <v>5395790</v>
+        <v>1372341</v>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
@@ -11128,7 +11128,7 @@
         <v>1</v>
       </c>
       <c r="F185" s="7" t="n">
-        <v>112894.953240805</v>
+        <v>31428.3547816104</v>
       </c>
       <c r="G185" s="8" t="n">
         <v>2026</v>
@@ -11143,10 +11143,10 @@
         <v>0</v>
       </c>
       <c r="K185" s="10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L185" s="10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M185" s="6" t="inlineStr">
         <is>
@@ -11202,10 +11202,10 @@
         <v>0</v>
       </c>
       <c r="K186" s="10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L186" s="10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M186" s="6" t="inlineStr">
         <is>
@@ -11225,16 +11225,16 @@
     </row>
     <row r="187">
       <c r="A187" s="5" t="n">
-        <v>5976992</v>
+        <v>10569709</v>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
@@ -11246,7 +11246,7 @@
         <v>1</v>
       </c>
       <c r="F187" s="7" t="n">
-        <v>71026.4832271897</v>
+        <v>57117.4877440616</v>
       </c>
       <c r="G187" s="8" t="n">
         <v>2026</v>
@@ -11261,10 +11261,10 @@
         <v>0</v>
       </c>
       <c r="K187" s="10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L187" s="10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M187" s="6" t="inlineStr">
         <is>
@@ -11284,28 +11284,28 @@
     </row>
     <row r="188">
       <c r="A188" s="5" t="n">
-        <v>19764771</v>
+        <v>677012</v>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F188" s="7" t="n">
-        <v>16709.8893972307</v>
+        <v>137781.681659123</v>
       </c>
       <c r="G188" s="8" t="n">
         <v>2026</v>
@@ -11320,10 +11320,10 @@
         <v>0</v>
       </c>
       <c r="K188" s="10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L188" s="10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M188" s="6" t="inlineStr">
         <is>
@@ -11343,16 +11343,16 @@
     </row>
     <row r="189">
       <c r="A189" s="5" t="n">
-        <v>1372341</v>
+        <v>5976992</v>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
@@ -11364,7 +11364,7 @@
         <v>1</v>
       </c>
       <c r="F189" s="7" t="n">
-        <v>31428.3547816104</v>
+        <v>71026.4832271897</v>
       </c>
       <c r="G189" s="8" t="n">
         <v>2026</v>
@@ -11379,10 +11379,10 @@
         <v>0</v>
       </c>
       <c r="K189" s="10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L189" s="10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M189" s="6" t="inlineStr">
         <is>
@@ -11402,16 +11402,16 @@
     </row>
     <row r="190">
       <c r="A190" s="5" t="n">
-        <v>5619911</v>
+        <v>5395790</v>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
@@ -11423,7 +11423,7 @@
         <v>1</v>
       </c>
       <c r="F190" s="7" t="n">
-        <v>53149.7671934051</v>
+        <v>112894.953240805</v>
       </c>
       <c r="G190" s="8" t="n">
         <v>2026</v>
@@ -11438,10 +11438,10 @@
         <v>0</v>
       </c>
       <c r="K190" s="10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L190" s="10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M190" s="6" t="inlineStr">
         <is>
@@ -11461,28 +11461,28 @@
     </row>
     <row r="191">
       <c r="A191" s="5" t="n">
-        <v>11858610</v>
+        <v>5572279</v>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F191" s="7" t="n">
-        <v>56614.5679499036</v>
+        <v>86785.4334489176</v>
       </c>
       <c r="G191" s="8" t="n">
         <v>2026</v>
@@ -11497,10 +11497,10 @@
         <v>0</v>
       </c>
       <c r="K191" s="10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L191" s="10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M191" s="6" t="inlineStr">
         <is>
@@ -11520,28 +11520,28 @@
     </row>
     <row r="192">
       <c r="A192" s="5" t="n">
-        <v>10569709</v>
+        <v>11858610</v>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F192" s="7" t="n">
-        <v>57117.4877440616</v>
+        <v>56614.5679499036</v>
       </c>
       <c r="G192" s="8" t="n">
         <v>2026</v>
@@ -11556,10 +11556,10 @@
         <v>0</v>
       </c>
       <c r="K192" s="10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L192" s="10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M192" s="6" t="inlineStr">
         <is>
@@ -11579,28 +11579,28 @@
     </row>
     <row r="193">
       <c r="A193" s="5" t="n">
-        <v>3386588</v>
+        <v>5619911</v>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>URY</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F193" s="7" t="n">
-        <v>23906.5133029408</v>
+        <v>53149.7671934051</v>
       </c>
       <c r="G193" s="8" t="n">
         <v>2026</v>
@@ -11615,10 +11615,10 @@
         <v>0</v>
       </c>
       <c r="K193" s="10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L193" s="10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M193" s="6" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F194" s="7" t="n"/>
       <c r="G194" s="8" t="n">
@@ -11669,7 +11669,7 @@
       <c r="J194" s="5" t="n"/>
       <c r="K194" s="10" t="n"/>
       <c r="L194" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M194" s="6" t="inlineStr">
         <is>
@@ -11952,9 +11952,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A202:O202"/>
-    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/atlas/rtl_di_atlas_un_members_2026.xlsx
+++ b/outputs/atlas/rtl_di_atlas_un_members_2026.xlsx
@@ -522,7 +522,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Countries: 193 | With GDP: 187 | Est. global deficit: $18,762,377,508,353 | Avg R: 0.326</t>
+          <t>Countries: 193 | With GDP: 187 | Est. global capital exclusions: $17,490,547,087,096 | Avg R: 0.326</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Total annual deficit (US$)</t>
+          <t>Total annual capital exclusions (US$)</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -635,10 +635,10 @@
         <v>2024</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>3990.94444631604</v>
+        <v>3325.7870385967</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>5623140951248.143</v>
+        <v>4685950792706.785</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>2024</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>718.596748959896</v>
+        <v>673.6844521499025</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1042637742362.155</v>
+        <v>977472883464.5205</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>3</v>
@@ -782,28 +782,28 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>143533851</v>
+        <v>123975371</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.111</v>
+        <v>0.556</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>14889.0185546875</v>
+        <v>32487.0778047567</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>2026</v>
@@ -812,16 +812,16 @@
         <v>2024</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>3970.404947916667</v>
+        <v>4331.61037396756</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>569887512203.9336</v>
+        <v>537013003140.077</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>4</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -841,28 +841,28 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>123975371</v>
+        <v>143533851</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.556</v>
+        <v>0.111</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>32487.0778047567</v>
+        <v>14889.0185546875</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>2026</v>
@@ -871,16 +871,16 @@
         <v>2024</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>4331.61037396756</v>
+        <v>3722.254638671875</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>537013003140.077</v>
+        <v>534269542691.1877</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>5</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -1077,28 +1077,28 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>35300280</v>
+        <v>211998573</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>SAU</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>35121.6628687742</v>
+        <v>10310.5488778166</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>2026</v>
@@ -1107,16 +1107,16 @@
         <v>2024</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>10536.49886063226</v>
+        <v>1718.424812969433</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>371941359999.9997</v>
+        <v>364303608157.3118</v>
       </c>
       <c r="K15" s="10" t="n">
         <v>9</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1136,28 +1136,28 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>211998573</v>
+        <v>58952704</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.444</v>
+        <v>0.556</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>10310.5488778166</v>
+        <v>40385.3413957669</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>2026</v>
@@ -1166,16 +1166,16 @@
         <v>2024</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1718.424812969433</v>
+        <v>5384.712186102253</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>364303608157.3118</v>
+        <v>317443343632.4791</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>10</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1195,28 +1195,28 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>58952704</v>
+        <v>85518661</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.556</v>
+        <v>0.222</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>40385.3413957669</v>
+        <v>15892.7157287241</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>2026</v>
@@ -1225,16 +1225,16 @@
         <v>2024</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>5384.712186102253</v>
+        <v>3708.30033670229</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>317443343632.4791</v>
+        <v>317128879380.629</v>
       </c>
       <c r="K17" s="10" t="n">
         <v>11</v>
       </c>
       <c r="L17" s="10" t="n">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>85518661</v>
+        <v>35300280</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>SAU</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>15892.7157287241</v>
+        <v>35121.6628687742</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>2026</v>
@@ -1284,16 +1284,16 @@
         <v>2024</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>3708.30033670229</v>
+        <v>8780.415717193549</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>317128879380.629</v>
+        <v>309951133333.3331</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>12</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
         <v>2024</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>13406.26827919565</v>
+        <v>12568.37651174592</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>147286625822.5551</v>
+        <v>138081211708.6454</v>
       </c>
       <c r="K24" s="10" t="n">
         <v>18</v>
@@ -1667,28 +1667,28 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>91567738</v>
+        <v>71668011</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>IRN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>5190.16959024821</v>
+        <v>7346.62022142185</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>2026</v>
@@ -1697,16 +1697,16 @@
         <v>2024</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1557.050877074463</v>
+        <v>1836.655055355463</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>142575626764.6246</v>
+        <v>131629414710.4209</v>
       </c>
       <c r="K25" s="10" t="n">
         <v>19</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
@@ -1726,28 +1726,28 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>71668011</v>
+        <v>36559233</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.111</v>
+        <v>0.556</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>7346.62022142185</v>
+        <v>25103.565661423</v>
       </c>
       <c r="G26" s="8" t="n">
         <v>2026</v>
@@ -1756,16 +1756,16 @@
         <v>2024</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1959.098725712493</v>
+        <v>3347.142088189733</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>140404709024.449</v>
+        <v>122368947486.235</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>20</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
@@ -1785,28 +1785,28 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>173562364</v>
+        <v>100987686</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>BGD</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>2593.41611680774</v>
+        <v>4717.29028732449</v>
       </c>
       <c r="G27" s="8" t="n">
         <v>2026</v>
@@ -1815,16 +1815,16 @@
         <v>2024</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>778.0248350423219</v>
+        <v>1179.322571831123</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>135035829620.6554</v>
+        <v>119097057576.7939</v>
       </c>
       <c r="K27" s="10" t="n">
         <v>21</v>
       </c>
       <c r="L27" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
@@ -1844,28 +1844,28 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>100987686</v>
+        <v>91567738</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>IRN</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>4717.29028732449</v>
+        <v>5190.16959024821</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>2026</v>
@@ -1874,16 +1874,16 @@
         <v>2024</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1257.944076619864</v>
+        <v>1297.542397562052</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>127036861415.2468</v>
+        <v>118813022303.8539</v>
       </c>
       <c r="K28" s="10" t="n">
         <v>22</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -1903,28 +1903,28 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>36559233</v>
+        <v>27196812</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Australia and New Zealand</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.556</v>
+        <v>0.778</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>25103.565661423</v>
+        <v>64603.9856308464</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>2026</v>
@@ -1933,16 +1933,16 @@
         <v>2024</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>3347.142088189733</v>
+        <v>4306.932375389762</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>122368947486.235</v>
+        <v>117134830110.1888</v>
       </c>
       <c r="K29" s="10" t="n">
         <v>23</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -1962,28 +1962,28 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>27196812</v>
+        <v>173562364</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>BGD</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Australia and New Zealand</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>64603.9856308464</v>
+        <v>2593.41611680774</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>2026</v>
@@ -1992,16 +1992,16 @@
         <v>2024</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>4306.932375389762</v>
+        <v>648.354029201935</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>117134830110.1888</v>
+        <v>112529858017.2129</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>24</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2021,28 +2021,28 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>251269164</v>
+        <v>9974400</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>PAK</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1478.77277977996</v>
+        <v>54176.6844383302</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>2026</v>
@@ -2051,16 +2051,16 @@
         <v>2024</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>443.631833933988</v>
+        <v>10835.33688766604</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>111471000036.38</v>
+        <v>108075984252.3362</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>25</v>
       </c>
       <c r="L31" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2080,28 +2080,28 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>9974400</v>
+        <v>45696159</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>54176.6844383302</v>
+        <v>13969.7836603737</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>2026</v>
@@ -2110,16 +2110,16 @@
         <v>2024</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>10835.33688766604</v>
+        <v>2328.29727672895</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>108075984252.3362</v>
+        <v>106394242556.6731</v>
       </c>
       <c r="K32" s="10" t="n">
         <v>26</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2139,28 +2139,28 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>45696159</v>
+        <v>116538258</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.444</v>
+        <v>0.111</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>13969.7836603737</v>
+        <v>3338.47371395895</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>2026</v>
@@ -2169,16 +2169,16 @@
         <v>2024</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>2328.29727672895</v>
+        <v>834.6184284897375</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>106394242556.6731</v>
+        <v>97264977750.89159</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>27</v>
       </c>
       <c r="L33" s="10" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2198,28 +2198,28 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>116538258</v>
+        <v>251269164</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>PAK</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>3338.47371395895</v>
+        <v>1478.77277977996</v>
       </c>
       <c r="G34" s="8" t="n">
         <v>2026</v>
@@ -2228,16 +2228,16 @@
         <v>2024</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>890.25965705572</v>
+        <v>369.69319494499</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>103749309600.951</v>
+        <v>92892500030.31667</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>28</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2316,28 +2316,28 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>46042015</v>
+        <v>17993485</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>IRQ</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>0.778</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>6073.61032342708</v>
+        <v>67520.4218956281</v>
       </c>
       <c r="G36" s="8" t="n">
         <v>2026</v>
@@ -2346,16 +2346,16 @@
         <v>2024</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1822.083097028124</v>
+        <v>4501.361459708542</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>83892377284.61534</v>
+        <v>80995179904.84375</v>
       </c>
       <c r="K36" s="10" t="n">
         <v>30</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2375,28 +2375,28 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>17993485</v>
+        <v>20592571</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.778</v>
+        <v>0.111</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>67520.4218956281</v>
+        <v>14154.6324958076</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>2026</v>
@@ -2405,16 +2405,16 @@
         <v>2024</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>4501.361459708542</v>
+        <v>3538.6581239519</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>80995179904.84375</v>
+        <v>72870068662.2063</v>
       </c>
       <c r="K37" s="10" t="n">
         <v>31</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2434,28 +2434,28 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>20592571</v>
+        <v>35557673</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.111</v>
+        <v>0.444</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>14154.6324958076</v>
+        <v>11874.4273684245</v>
       </c>
       <c r="G38" s="8" t="n">
         <v>2026</v>
@@ -2464,16 +2464,16 @@
         <v>2024</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>3774.568665548693</v>
+        <v>1979.07122807075</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>77728073239.68672</v>
+        <v>70371167571.44815</v>
       </c>
       <c r="K38" s="10" t="n">
         <v>32</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2493,28 +2493,28 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>46814308</v>
+        <v>46042015</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>IRQ</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>5752.99076651465</v>
+        <v>6073.61032342708</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>2026</v>
@@ -2523,16 +2523,16 @@
         <v>2024</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1534.130871070573</v>
+        <v>1518.40258085677</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>71819275110.60611</v>
+        <v>69910314403.84612</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>33</v>
       </c>
       <c r="L39" s="10" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2552,28 +2552,28 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>35557673</v>
+        <v>52886363</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
         <v>0.444</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>11874.4273684245</v>
+        <v>7919.20886825345</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>2026</v>
@@ -2582,10 +2582,10 @@
         <v>2024</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1979.07122807075</v>
+        <v>1319.868144708908</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>70371167571.44815</v>
+        <v>69803025813.21185</v>
       </c>
       <c r="K40" s="10" t="n">
         <v>34</v>
@@ -2611,28 +2611,28 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>52886363</v>
+        <v>46814308</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.444</v>
+        <v>0.111</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>7919.20886825345</v>
+        <v>5752.99076651465</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>2026</v>
@@ -2641,16 +2641,16 @@
         <v>2024</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1319.868144708908</v>
+        <v>1438.247691628663</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>69803025813.21185</v>
+        <v>67330570416.19323</v>
       </c>
       <c r="K41" s="10" t="n">
         <v>35</v>
       </c>
       <c r="L41" s="10" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -3172,10 +3172,10 @@
         <v>2024</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>302.3687458179173</v>
+        <v>283.4706992042975</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>39930746120.79639</v>
+        <v>37435074488.24661</v>
       </c>
       <c r="K50" s="10" t="n">
         <v>44</v>
@@ -3201,28 +3201,28 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>28405543</v>
+        <v>10405134</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>4217.59102643391</v>
+        <v>24626.1481858973</v>
       </c>
       <c r="G51" s="8" t="n">
         <v>2026</v>
@@ -3231,16 +3231,16 @@
         <v>2024</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>1265.277307930173</v>
+        <v>3283.486424786307</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>35940888977.33477</v>
+        <v>34165116237.08244</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>45</v>
       </c>
       <c r="L51" s="10" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3260,28 +3260,28 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
-        <v>10405134</v>
+        <v>4897263</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>KWT</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.556</v>
+        <v>0.333</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>24626.1481858973</v>
+        <v>32717.7186631255</v>
       </c>
       <c r="G52" s="8" t="n">
         <v>2026</v>
@@ -3290,16 +3290,16 @@
         <v>2024</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>3283.486424786307</v>
+        <v>6543.5437326251</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>34165116237.08244</v>
+        <v>32045454610.6668</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>46</v>
       </c>
       <c r="L52" s="10" t="n">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3319,28 +3319,28 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>4897263</v>
+        <v>9005582</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>KWT</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.333</v>
+        <v>0.889</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>32717.7186631255</v>
+        <v>103998.186685604</v>
       </c>
       <c r="G53" s="8" t="n">
         <v>2026</v>
@@ -3349,16 +3349,16 @@
         <v>2024</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>6543.5437326251</v>
+        <v>3466.606222853468</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>32045454610.6668</v>
+        <v>31218806601.61718</v>
       </c>
       <c r="K53" s="10" t="n">
         <v>47</v>
       </c>
       <c r="L53" s="10" t="n">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3378,28 +3378,28 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
-        <v>9005582</v>
+        <v>28405543</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>103998.186685604</v>
+        <v>4217.59102643391</v>
       </c>
       <c r="G54" s="8" t="n">
         <v>2026</v>
@@ -3408,16 +3408,16 @@
         <v>2024</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>3466.606222853468</v>
+        <v>1054.397756608477</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>31218806601.61718</v>
+        <v>29950740814.44564</v>
       </c>
       <c r="K54" s="10" t="n">
         <v>48</v>
       </c>
       <c r="L54" s="10" t="n">
-        <v>176</v>
+        <v>1</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3850,28 +3850,28 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
-        <v>9132629</v>
+        <v>10694681</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>0.778</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>8317.633999137919</v>
+        <v>29292.242104753</v>
       </c>
       <c r="G62" s="8" t="n">
         <v>2026</v>
@@ -3880,16 +3880,16 @@
         <v>2024</v>
       </c>
       <c r="I62" s="7" t="n">
-        <v>2495.290199741376</v>
+        <v>1952.816140316867</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>22788559641.57388</v>
+        <v>20884745672.34014</v>
       </c>
       <c r="K62" s="10" t="n">
         <v>56</v>
       </c>
       <c r="L62" s="10" t="n">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -3909,28 +3909,28 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>10202830</v>
+        <v>11427557</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>AZE</t>
+          <t>DOM</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>7283.8499076179</v>
+        <v>10875.6618443092</v>
       </c>
       <c r="G63" s="8" t="n">
         <v>2026</v>
@@ -3939,16 +3939,16 @@
         <v>2024</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>2185.15497228537</v>
+        <v>1812.610307384866</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>22294764705.88234</v>
+        <v>20713707606.42808</v>
       </c>
       <c r="K63" s="10" t="n">
         <v>57</v>
       </c>
       <c r="L63" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -3968,28 +3968,28 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
-        <v>54500091</v>
+        <v>37885849</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>MMR</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>1359.05001560107</v>
+        <v>2665.87444776753</v>
       </c>
       <c r="G64" s="8" t="n">
         <v>2026</v>
@@ -3998,16 +3998,16 @@
         <v>2024</v>
       </c>
       <c r="I64" s="7" t="n">
-        <v>407.715004680321</v>
+        <v>533.174889553506</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>22220504857.14292</v>
+        <v>20199783356.21581</v>
       </c>
       <c r="K64" s="10" t="n">
         <v>58</v>
       </c>
       <c r="L64" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4027,28 +4027,28 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>10694681</v>
+        <v>21916000</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>LKA</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0.778</v>
+        <v>0.333</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>29292.242104753</v>
+        <v>4515.56787322732</v>
       </c>
       <c r="G65" s="8" t="n">
         <v>2026</v>
@@ -4057,16 +4057,16 @@
         <v>2024</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>1952.816140316867</v>
+        <v>903.113574645464</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>20884745672.34014</v>
+        <v>19792637101.92999</v>
       </c>
       <c r="K65" s="10" t="n">
         <v>59</v>
       </c>
       <c r="L65" s="10" t="n">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4086,28 +4086,28 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>11427557</v>
+        <v>9132629</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>10875.6618443092</v>
+        <v>8317.633999137919</v>
       </c>
       <c r="G66" s="8" t="n">
         <v>2026</v>
@@ -4116,16 +4116,16 @@
         <v>2024</v>
       </c>
       <c r="I66" s="7" t="n">
-        <v>1812.610307384866</v>
+        <v>2079.40849978448</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>20713707606.42808</v>
+        <v>18990466367.97823</v>
       </c>
       <c r="K66" s="10" t="n">
         <v>60</v>
       </c>
       <c r="L66" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4145,28 +4145,28 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>37885849</v>
+        <v>6441421</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>2665.87444776753</v>
+        <v>17596.0173663521</v>
       </c>
       <c r="G67" s="8" t="n">
         <v>2026</v>
@@ -4175,16 +4175,16 @@
         <v>2024</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>533.174889553506</v>
+        <v>2932.669561058683</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>20199783356.21581</v>
+        <v>18890559296.66418</v>
       </c>
       <c r="K67" s="10" t="n">
         <v>61</v>
       </c>
       <c r="L67" s="10" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4204,28 +4204,28 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
-        <v>21916000</v>
+        <v>5422069</v>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>LKA</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0.333</v>
+        <v>0.556</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>4515.56787322732</v>
+        <v>25992.6748502048</v>
       </c>
       <c r="G68" s="8" t="n">
         <v>2026</v>
@@ -4234,16 +4234,16 @@
         <v>2024</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>903.113574645464</v>
+        <v>3465.689980027306</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>19792637101.92999</v>
+        <v>18791210204.31668</v>
       </c>
       <c r="K68" s="10" t="n">
         <v>62</v>
       </c>
       <c r="L68" s="10" t="n">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4263,28 +4263,28 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>109276265</v>
+        <v>10202830</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>649.383338556725</v>
+        <v>7283.8499076179</v>
       </c>
       <c r="G69" s="8" t="n">
         <v>2026</v>
@@ -4293,16 +4293,16 @@
         <v>2024</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>173.1688902817933</v>
+        <v>1820.962476904475</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>18923249544.18917</v>
+        <v>18578970588.23528</v>
       </c>
       <c r="K69" s="10" t="n">
         <v>63</v>
       </c>
       <c r="L69" s="10" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4322,28 +4322,28 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
-        <v>6441421</v>
+        <v>54500091</v>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>MMR</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>17596.0173663521</v>
+        <v>1359.05001560107</v>
       </c>
       <c r="G70" s="8" t="n">
         <v>2026</v>
@@ -4352,16 +4352,16 @@
         <v>2024</v>
       </c>
       <c r="I70" s="7" t="n">
-        <v>2932.669561058683</v>
+        <v>339.7625039002675</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>18890559296.66418</v>
+        <v>18517087380.95243</v>
       </c>
       <c r="K70" s="10" t="n">
         <v>64</v>
       </c>
       <c r="L70" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4381,28 +4381,28 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>5422069</v>
+        <v>109276265</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0.556</v>
+        <v>0.111</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>25992.6748502048</v>
+        <v>649.383338556725</v>
       </c>
       <c r="G71" s="8" t="n">
         <v>2026</v>
@@ -4411,16 +4411,16 @@
         <v>2024</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>3465.689980027306</v>
+        <v>162.3458346391812</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>18791210204.31668</v>
+        <v>17740546447.67735</v>
       </c>
       <c r="K71" s="10" t="n">
         <v>65</v>
       </c>
       <c r="L71" s="10" t="n">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4499,28 +4499,28 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>7494498</v>
+        <v>6586476</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>TKM</t>
+          <t>SRB</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>6856.65802730208</v>
+        <v>13679.2065983557</v>
       </c>
       <c r="G73" s="8" t="n">
         <v>2026</v>
@@ -4529,16 +4529,16 @@
         <v>2024</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>2056.997408190624</v>
+        <v>2279.867766392616</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>15416162961.68981</v>
+        <v>15016294326.51857</v>
       </c>
       <c r="K73" s="10" t="n">
         <v>67</v>
       </c>
       <c r="L73" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -4558,28 +4558,28 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
-        <v>6586476</v>
+        <v>68560157</v>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>SRB</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
         <v>0.444</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>13679.2065983557</v>
+        <v>1186.71691894531</v>
       </c>
       <c r="G74" s="8" t="n">
         <v>2026</v>
@@ -4588,10 +4588,10 @@
         <v>2024</v>
       </c>
       <c r="I74" s="7" t="n">
-        <v>2279.867766392616</v>
+        <v>197.7861531575517</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>15016294326.51857</v>
+        <v>13560249712.90779</v>
       </c>
       <c r="K74" s="10" t="n">
         <v>68</v>
@@ -4617,28 +4617,28 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>50448963</v>
+        <v>50015092</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>984.607666015625</v>
+        <v>1077.91278452817</v>
       </c>
       <c r="G75" s="8" t="n">
         <v>2026</v>
@@ -4647,16 +4647,16 @@
         <v>2024</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>295.3822998046875</v>
+        <v>269.4781961320425</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>14901730713.70159</v>
+        <v>13477976771.53815</v>
       </c>
       <c r="K75" s="10" t="n">
         <v>69</v>
       </c>
       <c r="L75" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4676,28 +4676,28 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
-        <v>7381023</v>
+        <v>29123744</v>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>6569.16408678648</v>
+        <v>1830.00833684727</v>
       </c>
       <c r="G76" s="8" t="n">
         <v>2026</v>
@@ -4706,16 +4706,16 @@
         <v>2024</v>
       </c>
       <c r="I76" s="7" t="n">
-        <v>1970.749226035944</v>
+        <v>457.5020842118175</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>14546145364.6035</v>
+        <v>13324173580.05141</v>
       </c>
       <c r="K76" s="10" t="n">
         <v>70</v>
       </c>
       <c r="L76" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4735,28 +4735,28 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>50015092</v>
+        <v>7494498</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TKM</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>1077.91278452817</v>
+        <v>6856.65802730208</v>
       </c>
       <c r="G77" s="8" t="n">
         <v>2026</v>
@@ -4765,16 +4765,16 @@
         <v>2024</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>287.443409207512</v>
+        <v>1714.16450682552</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>14376508556.30736</v>
+        <v>12846802468.07485</v>
       </c>
       <c r="K77" s="10" t="n">
         <v>71</v>
       </c>
       <c r="L77" s="10" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -4794,28 +4794,28 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
-        <v>29123744</v>
+        <v>12413315</v>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0.111</v>
+        <v>0.222</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>1830.00833684727</v>
+        <v>4421.16609889999</v>
       </c>
       <c r="G78" s="8" t="n">
         <v>2026</v>
@@ -4824,16 +4824,16 @@
         <v>2024</v>
       </c>
       <c r="I78" s="7" t="n">
-        <v>488.002223159272</v>
+        <v>1031.605423076664</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>14212451818.72151</v>
+        <v>12805643072.35891</v>
       </c>
       <c r="K78" s="10" t="n">
         <v>72</v>
       </c>
       <c r="L78" s="10" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -4853,28 +4853,28 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>1588670</v>
+        <v>50448963</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>BHR</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>29653.5682731534</v>
+        <v>984.607666015625</v>
       </c>
       <c r="G79" s="8" t="n">
         <v>2026</v>
@@ -4883,10 +4883,10 @@
         <v>2024</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>8896.070481946019</v>
+        <v>246.1519165039062</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>14132920292.55318</v>
+        <v>12418108928.08466</v>
       </c>
       <c r="K79" s="10" t="n">
         <v>73</v>
@@ -4912,28 +4912,28 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
-        <v>17638801</v>
+        <v>7381023</v>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>KHM</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>2627.87969756224</v>
+        <v>6569.16408678648</v>
       </c>
       <c r="G80" s="8" t="n">
         <v>2026</v>
@@ -4942,10 +4942,10 @@
         <v>2024</v>
       </c>
       <c r="I80" s="7" t="n">
-        <v>788.3639092686719</v>
+        <v>1642.29102169662</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>13905794111.17216</v>
+        <v>12121787803.83625</v>
       </c>
       <c r="K80" s="10" t="n">
         <v>74</v>
@@ -4971,28 +4971,28 @@
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>68560157</v>
+        <v>1588670</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>BHR</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>1186.71691894531</v>
+        <v>29653.5682731534</v>
       </c>
       <c r="G81" s="8" t="n">
         <v>2026</v>
@@ -5001,16 +5001,16 @@
         <v>2024</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>197.7861531575517</v>
+        <v>7413.39206828835</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>13560249712.90779</v>
+        <v>11777433577.12765</v>
       </c>
       <c r="K81" s="10" t="n">
         <v>75</v>
       </c>
       <c r="L81" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -5030,28 +5030,28 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>12413315</v>
+        <v>17638801</v>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>KHM</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>4421.16609889999</v>
+        <v>2627.87969756224</v>
       </c>
       <c r="G82" s="8" t="n">
         <v>2026</v>
@@ -5060,16 +5060,16 @@
         <v>2024</v>
       </c>
       <c r="I82" s="7" t="n">
-        <v>1031.605423076664</v>
+        <v>656.96992439056</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>12805643072.35891</v>
+        <v>11588161759.31013</v>
       </c>
       <c r="K82" s="10" t="n">
         <v>76</v>
       </c>
       <c r="L82" s="10" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5207,28 +5207,28 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>16634373</v>
+        <v>19764771</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>ZWE</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0.111</v>
+        <v>0.889</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>2497.20332208763</v>
+        <v>16709.8893972307</v>
       </c>
       <c r="G85" s="8" t="n">
         <v>2026</v>
@@ -5237,16 +5237,16 @@
         <v>2024</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>665.9208858900347</v>
+        <v>556.9963132410236</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>11077176404.38527</v>
+        <v>11008904579.0531</v>
       </c>
       <c r="K85" s="10" t="n">
         <v>79</v>
       </c>
       <c r="L85" s="10" t="n">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5266,28 +5266,28 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
-        <v>19764771</v>
+        <v>34427414</v>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0.889</v>
+        <v>0.556</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>16709.8893972307</v>
+        <v>2390.77237652715</v>
       </c>
       <c r="G86" s="8" t="n">
         <v>2026</v>
@@ -5296,16 +5296,16 @@
         <v>2024</v>
       </c>
       <c r="I86" s="7" t="n">
-        <v>556.9963132410236</v>
+        <v>318.76965020362</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>11008904579.0531</v>
+        <v>10974414718.19521</v>
       </c>
       <c r="K86" s="10" t="n">
         <v>80</v>
       </c>
       <c r="L86" s="10" t="n">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5325,28 +5325,28 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>34427414</v>
+        <v>11552876</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>JOR</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0.556</v>
+        <v>0.333</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>2390.77237652715</v>
+        <v>4618.09592498567</v>
       </c>
       <c r="G87" s="8" t="n">
         <v>2026</v>
@@ -5355,16 +5355,16 @@
         <v>2024</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>318.76965020362</v>
+        <v>923.619184997134</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>10974414718.19521</v>
+        <v>10670457915.49295</v>
       </c>
       <c r="K87" s="10" t="n">
         <v>81</v>
       </c>
       <c r="L87" s="10" t="n">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
@@ -5384,28 +5384,28 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
-        <v>11552876</v>
+        <v>16634373</v>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>JOR</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0.333</v>
+        <v>0.111</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>4618.09592498567</v>
+        <v>2497.20332208763</v>
       </c>
       <c r="G88" s="8" t="n">
         <v>2026</v>
@@ -5414,16 +5414,16 @@
         <v>2024</v>
       </c>
       <c r="I88" s="7" t="n">
-        <v>923.619184997134</v>
+        <v>624.3008305219075</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>10670457915.49295</v>
+        <v>10384852879.11119</v>
       </c>
       <c r="K88" s="10" t="n">
         <v>82</v>
       </c>
       <c r="L88" s="10" t="n">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -5443,28 +5443,28 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>6338193</v>
+        <v>3866200</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>5579.65969165029</v>
+        <v>24050.4397933135</v>
       </c>
       <c r="G89" s="8" t="n">
         <v>2026</v>
@@ -5473,16 +5473,16 @@
         <v>2024</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>1673.897907495087</v>
+        <v>2405.043979331349</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>10609488000.00001</v>
+        <v>9298381032.890863</v>
       </c>
       <c r="K89" s="10" t="n">
         <v>83</v>
       </c>
       <c r="L89" s="10" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
@@ -5502,28 +5502,28 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
-        <v>3866200</v>
+        <v>6929153</v>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>24050.4397933135</v>
+        <v>6416.09708970845</v>
       </c>
       <c r="G90" s="8" t="n">
         <v>2026</v>
@@ -5532,16 +5532,16 @@
         <v>2024</v>
       </c>
       <c r="I90" s="7" t="n">
-        <v>2405.043979331349</v>
+        <v>1283.21941794169</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>9298381032.890863</v>
+        <v>8891623679.488916</v>
       </c>
       <c r="K90" s="10" t="n">
         <v>84</v>
       </c>
       <c r="L90" s="10" t="n">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
@@ -5561,28 +5561,28 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>6929153</v>
+        <v>6338193</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>6416.09708970845</v>
+        <v>5579.65969165029</v>
       </c>
       <c r="G91" s="8" t="n">
         <v>2026</v>
@@ -5591,16 +5591,16 @@
         <v>2024</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>1283.21941794169</v>
+        <v>1394.914922912573</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>8891623679.488916</v>
+        <v>8841240000.000008</v>
       </c>
       <c r="K91" s="10" t="n">
         <v>85</v>
       </c>
       <c r="L91" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -5915,28 +5915,28 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>14754785</v>
+        <v>2127400</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>1694.95375862193</v>
+        <v>34301.0318686594</v>
       </c>
       <c r="G97" s="8" t="n">
         <v>2026</v>
@@ -5945,16 +5945,16 @@
         <v>2024</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>508.486127586579</v>
+        <v>3430.103186865939</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>7502603488.022542</v>
+        <v>7297201519.738598</v>
       </c>
       <c r="K97" s="10" t="n">
         <v>91</v>
       </c>
       <c r="L97" s="10" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="N97" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O97" s="6" t="inlineStr">
@@ -5974,28 +5974,28 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
-        <v>2127400</v>
+        <v>10576502</v>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Melanesia</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>34301.0318686594</v>
+        <v>3006.70564478923</v>
       </c>
       <c r="G98" s="8" t="n">
         <v>2026</v>
@@ -6004,16 +6004,16 @@
         <v>2024</v>
       </c>
       <c r="I98" s="7" t="n">
-        <v>3430.103186865939</v>
+        <v>601.3411289578461</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>7297201519.738598</v>
+        <v>6360085653.104917</v>
       </c>
       <c r="K98" s="10" t="n">
         <v>92</v>
       </c>
       <c r="L98" s="10" t="n">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="N98" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O98" s="6" t="inlineStr">
@@ -6033,28 +6033,28 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>34631766</v>
+        <v>14754785</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>656.776824637306</v>
+        <v>1694.95375862193</v>
       </c>
       <c r="G99" s="8" t="n">
         <v>2026</v>
@@ -6063,10 +6063,10 @@
         <v>2024</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>197.0330473911918</v>
+        <v>423.7384396554825</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>6823602391.518665</v>
+        <v>6252169573.352118</v>
       </c>
       <c r="K99" s="10" t="n">
         <v>93</v>
@@ -6092,28 +6092,28 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
-        <v>10576502</v>
+        <v>11772557</v>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>HTI</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>3006.70564478923</v>
+        <v>2142.62330526788</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>2026</v>
@@ -6122,16 +6122,16 @@
         <v>2024</v>
       </c>
       <c r="I100" s="7" t="n">
-        <v>601.3411289578461</v>
+        <v>499.9454378958387</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>6360085653.104917</v>
+        <v>5885636164.518721</v>
       </c>
       <c r="K100" s="10" t="n">
         <v>94</v>
       </c>
       <c r="L100" s="10" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -6181,10 +6181,10 @@
         <v>2024</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>261.8647066050883</v>
+        <v>245.4981624422703</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>6166594627.472477</v>
+        <v>5781182463.255447</v>
       </c>
       <c r="K101" s="10" t="n">
         <v>95</v>
@@ -6210,28 +6210,28 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
-        <v>6916140</v>
+        <v>3699557</v>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>NIC</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>2847.53966339498</v>
+        <v>9241.491223137131</v>
       </c>
       <c r="G102" s="8" t="n">
         <v>2026</v>
@@ -6240,16 +6240,16 @@
         <v>2024</v>
       </c>
       <c r="I102" s="7" t="n">
-        <v>854.261899018494</v>
+        <v>1540.248537189522</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>5908194890.277767</v>
+        <v>5698237257.499256</v>
       </c>
       <c r="K102" s="10" t="n">
         <v>96</v>
       </c>
       <c r="L102" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6269,28 +6269,28 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>11772557</v>
+        <v>34631766</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>HTI</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>2142.62330526788</v>
+        <v>656.776824637306</v>
       </c>
       <c r="G103" s="8" t="n">
         <v>2026</v>
@@ -6299,16 +6299,16 @@
         <v>2024</v>
       </c>
       <c r="I103" s="7" t="n">
-        <v>499.9454378958387</v>
+        <v>164.1942061593265</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>5885636164.518721</v>
+        <v>5686335326.265554</v>
       </c>
       <c r="K103" s="10" t="n">
         <v>97</v>
       </c>
       <c r="L103" s="10" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6328,28 +6328,28 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
-        <v>20299123</v>
+        <v>18501984</v>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>TCD</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>961.55975562506</v>
+        <v>1773.21829923448</v>
       </c>
       <c r="G104" s="8" t="n">
         <v>2026</v>
@@ -6358,16 +6358,16 @@
         <v>2024</v>
       </c>
       <c r="I104" s="7" t="n">
-        <v>288.467926687518</v>
+        <v>295.5363832057466</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>5855645925.384911</v>
+        <v>5468009433.490593</v>
       </c>
       <c r="K104" s="10" t="n">
         <v>98</v>
       </c>
       <c r="L104" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
@@ -6387,28 +6387,28 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>3699557</v>
+        <v>24478595</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0.444</v>
+        <v>0.333</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>9241.491223137131</v>
+        <v>1094.61949265799</v>
       </c>
       <c r="G105" s="8" t="n">
         <v>2026</v>
@@ -6417,16 +6417,16 @@
         <v>2024</v>
       </c>
       <c r="I105" s="7" t="n">
-        <v>1540.248537189522</v>
+        <v>218.923898531598</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>5698237257.499256</v>
+        <v>5358949447.976082</v>
       </c>
       <c r="K105" s="10" t="n">
         <v>99</v>
       </c>
       <c r="L105" s="10" t="n">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="M105" s="6" t="inlineStr">
         <is>
@@ -6446,28 +6446,28 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
-        <v>18501984</v>
+        <v>1358282</v>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>CYP</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.444</v>
+        <v>0.667</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>1773.21829923448</v>
+        <v>38674.29296875</v>
       </c>
       <c r="G106" s="8" t="n">
         <v>2026</v>
@@ -6476,16 +6476,16 @@
         <v>2024</v>
       </c>
       <c r="I106" s="7" t="n">
-        <v>295.5363832057466</v>
+        <v>3867.429296874999</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>5468009433.490593</v>
+        <v>5253059600.217968</v>
       </c>
       <c r="K106" s="10" t="n">
         <v>100</v>
       </c>
       <c r="L106" s="10" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="M106" s="6" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="N106" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O106" s="6" t="inlineStr">
@@ -6505,28 +6505,28 @@
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>24478595</v>
+        <v>1368333</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>TTO</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
         <v>0.333</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>1094.61949265799</v>
+        <v>18733.4110406494</v>
       </c>
       <c r="G107" s="8" t="n">
         <v>2026</v>
@@ -6535,10 +6535,10 @@
         <v>2024</v>
       </c>
       <c r="I107" s="7" t="n">
-        <v>218.923898531598</v>
+        <v>3746.68220812988</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>5358949447.976082</v>
+        <v>5126708905.896983</v>
       </c>
       <c r="K107" s="10" t="n">
         <v>101</v>
@@ -6564,28 +6564,28 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
-        <v>42647492</v>
+        <v>21314956</v>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>413.757894705303</v>
+        <v>1187.10943350064</v>
       </c>
       <c r="G108" s="8" t="n">
         <v>2026</v>
@@ -6594,16 +6594,16 @@
         <v>2024</v>
       </c>
       <c r="I108" s="7" t="n">
-        <v>124.1273684115909</v>
+        <v>237.421886700128</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>5293720951.314375</v>
+        <v>5060637068.450214</v>
       </c>
       <c r="K108" s="10" t="n">
         <v>102</v>
       </c>
       <c r="L108" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M108" s="6" t="inlineStr">
         <is>
@@ -6623,28 +6623,28 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>1358282</v>
+        <v>3164253</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>CYP</t>
+          <t>BIH</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0.667</v>
+        <v>0.444</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>38674.29296875</v>
+        <v>9358.78768951134</v>
       </c>
       <c r="G109" s="8" t="n">
         <v>2026</v>
@@ -6653,16 +6653,16 @@
         <v>2024</v>
       </c>
       <c r="I109" s="7" t="n">
-        <v>3867.429296874999</v>
+        <v>1559.79794825189</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>5253059600.217968</v>
+        <v>4935595337.149887</v>
       </c>
       <c r="K109" s="10" t="n">
         <v>103</v>
       </c>
       <c r="L109" s="10" t="n">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="N109" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O109" s="6" t="inlineStr">
@@ -6682,28 +6682,28 @@
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
-        <v>1368333</v>
+        <v>6916140</v>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>TTO</t>
+          <t>NIC</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>18733.4110406494</v>
+        <v>2847.53966339498</v>
       </c>
       <c r="G110" s="8" t="n">
         <v>2026</v>
@@ -6712,16 +6712,16 @@
         <v>2024</v>
       </c>
       <c r="I110" s="7" t="n">
-        <v>3746.68220812988</v>
+        <v>711.884915848745</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>5126708905.896983</v>
+        <v>4923495741.898139</v>
       </c>
       <c r="K110" s="10" t="n">
         <v>104</v>
       </c>
       <c r="L110" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M110" s="6" t="inlineStr">
         <is>
@@ -6741,28 +6741,28 @@
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>21314956</v>
+        <v>20299123</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>TCD</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>1187.10943350064</v>
+        <v>961.55975562506</v>
       </c>
       <c r="G111" s="8" t="n">
         <v>2026</v>
@@ -6771,16 +6771,16 @@
         <v>2024</v>
       </c>
       <c r="I111" s="7" t="n">
-        <v>237.421886700128</v>
+        <v>240.389938906265</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>5060637068.450214</v>
+        <v>4879704937.820759</v>
       </c>
       <c r="K111" s="10" t="n">
         <v>105</v>
       </c>
       <c r="L111" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M111" s="6" t="inlineStr">
         <is>
@@ -6800,28 +6800,28 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
-        <v>7769819</v>
+        <v>2377128</v>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>LAO</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F112" s="7" t="n">
-        <v>2123.97909415109</v>
+        <v>11377.7757431099</v>
       </c>
       <c r="G112" s="8" t="n">
         <v>2026</v>
@@ -6830,16 +6830,16 @@
         <v>2024</v>
       </c>
       <c r="I112" s="7" t="n">
-        <v>637.193728245327</v>
+        <v>1896.295957184983</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>4950879936.401378</v>
+        <v>4507738216.111225</v>
       </c>
       <c r="K112" s="10" t="n">
         <v>106</v>
       </c>
       <c r="L112" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M112" s="6" t="inlineStr">
         <is>
@@ -6859,28 +6859,28 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>3164253</v>
+        <v>42647492</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>BIH</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>9358.78768951134</v>
+        <v>413.757894705303</v>
       </c>
       <c r="G113" s="8" t="n">
         <v>2026</v>
@@ -6889,16 +6889,16 @@
         <v>2024</v>
       </c>
       <c r="I113" s="7" t="n">
-        <v>1559.79794825189</v>
+        <v>103.4394736763257</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>4935595337.149887</v>
+        <v>4411434126.095313</v>
       </c>
       <c r="K113" s="10" t="n">
         <v>107</v>
       </c>
       <c r="L113" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M113" s="6" t="inlineStr">
         <is>
@@ -6918,28 +6918,28 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
-        <v>401283</v>
+        <v>3033500</v>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>BHS</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F114" s="7" t="n">
-        <v>39455.4466548546</v>
+        <v>8556.21406956719</v>
       </c>
       <c r="G114" s="8" t="n">
         <v>2026</v>
@@ -6948,16 +6948,16 @@
         <v>2024</v>
       </c>
       <c r="I114" s="7" t="n">
-        <v>11836.63399645638</v>
+        <v>1426.035678261198</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>4749840000.000006</v>
+        <v>4325879230.005344</v>
       </c>
       <c r="K114" s="10" t="n">
         <v>108</v>
       </c>
       <c r="L114" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M114" s="6" t="inlineStr">
         <is>
@@ -6977,28 +6977,28 @@
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>6332961</v>
+        <v>7769819</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>LAO</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Congo Republic</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>2482.2489948456</v>
+        <v>2123.97909415109</v>
       </c>
       <c r="G115" s="8" t="n">
         <v>2026</v>
@@ -7007,10 +7007,10 @@
         <v>2024</v>
       </c>
       <c r="I115" s="7" t="n">
-        <v>744.67469845368</v>
+        <v>530.9947735377725</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>4715995822.993916</v>
+        <v>4125733280.334482</v>
       </c>
       <c r="K115" s="10" t="n">
         <v>109</v>
@@ -7036,28 +7036,28 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
-        <v>462721</v>
+        <v>831087</v>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>BRN</t>
+          <t>GUY</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Brunei Darussalam</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F116" s="7" t="n">
-        <v>33153.4738913513</v>
+        <v>29675.2443873316</v>
       </c>
       <c r="G116" s="8" t="n">
         <v>2026</v>
@@ -7066,16 +7066,16 @@
         <v>2024</v>
       </c>
       <c r="I116" s="7" t="n">
-        <v>9946.042167405389</v>
+        <v>4945.874064555266</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>4602242577.743989</v>
+        <v>4110451638.689043</v>
       </c>
       <c r="K116" s="10" t="n">
         <v>110</v>
       </c>
       <c r="L116" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M116" s="6" t="inlineStr">
         <is>
@@ -7095,28 +7095,28 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>2377128</v>
+        <v>7221868</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>KGZ</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0.444</v>
+        <v>0.222</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>11377.7757431099</v>
+        <v>2420.18542283831</v>
       </c>
       <c r="G117" s="8" t="n">
         <v>2026</v>
@@ -7125,16 +7125,16 @@
         <v>2024</v>
       </c>
       <c r="I117" s="7" t="n">
-        <v>1896.295957184983</v>
+        <v>564.7099319956056</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>4507738216.111225</v>
+        <v>4078260587.161241</v>
       </c>
       <c r="K117" s="10" t="n">
         <v>111</v>
       </c>
       <c r="L117" s="10" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="M117" s="6" t="inlineStr">
         <is>
@@ -7154,28 +7154,28 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
-        <v>3033500</v>
+        <v>31964956</v>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>MDG</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0.444</v>
+        <v>0.222</v>
       </c>
       <c r="F118" s="7" t="n">
-        <v>8556.21406956719</v>
+        <v>544.987501003384</v>
       </c>
       <c r="G118" s="8" t="n">
         <v>2026</v>
@@ -7184,16 +7184,16 @@
         <v>2024</v>
       </c>
       <c r="I118" s="7" t="n">
-        <v>1426.035678261198</v>
+        <v>127.1637502341229</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>4325879230.005344</v>
+        <v>4064783681.028729</v>
       </c>
       <c r="K118" s="10" t="n">
         <v>112</v>
       </c>
       <c r="L118" s="10" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="M118" s="6" t="inlineStr">
         <is>
@@ -7213,28 +7213,28 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>14256567</v>
+        <v>5805962</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>999.65456165547</v>
+        <v>3477.72489842684</v>
       </c>
       <c r="G119" s="8" t="n">
         <v>2026</v>
@@ -7243,16 +7243,16 @@
         <v>2024</v>
       </c>
       <c r="I119" s="7" t="n">
-        <v>299.896368496641</v>
+        <v>695.544979685368</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>4275492670.529052</v>
+        <v>4038307721.344019</v>
       </c>
       <c r="K119" s="10" t="n">
         <v>113</v>
       </c>
       <c r="L119" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
@@ -7272,28 +7272,28 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
-        <v>10590927</v>
+        <v>27032412</v>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>TJK</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F120" s="7" t="n">
-        <v>1341.20229027672</v>
+        <v>735.270255787226</v>
       </c>
       <c r="G120" s="8" t="n">
         <v>2026</v>
@@ -7302,16 +7302,16 @@
         <v>2024</v>
       </c>
       <c r="I120" s="7" t="n">
-        <v>402.360687083016</v>
+        <v>147.0540511574452</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>4261372664.566065</v>
+        <v>3975225697.157135</v>
       </c>
       <c r="K120" s="10" t="n">
         <v>114</v>
       </c>
       <c r="L120" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M120" s="6" t="inlineStr">
         <is>
@@ -7331,28 +7331,28 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>831087</v>
+        <v>3524788</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>GUY</t>
+          <t>MNG</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
         <v>0.444</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>29675.2443873316</v>
+        <v>6750.6301157724</v>
       </c>
       <c r="G121" s="8" t="n">
         <v>2026</v>
@@ -7361,10 +7361,10 @@
         <v>2024</v>
       </c>
       <c r="I121" s="7" t="n">
-        <v>4945.874064555266</v>
+        <v>1125.1050192954</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>4110451638.689043</v>
+        <v>3965756670.752194</v>
       </c>
       <c r="K121" s="10" t="n">
         <v>115</v>
@@ -7390,28 +7390,28 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
-        <v>7221868</v>
+        <v>401283</v>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>KGZ</t>
+          <t>BHS</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F122" s="7" t="n">
-        <v>2420.18542283831</v>
+        <v>39455.4466548546</v>
       </c>
       <c r="G122" s="8" t="n">
         <v>2026</v>
@@ -7420,16 +7420,16 @@
         <v>2024</v>
       </c>
       <c r="I122" s="7" t="n">
-        <v>564.7099319956056</v>
+        <v>9863.861663713649</v>
       </c>
       <c r="J122" s="5" t="n">
-        <v>4078260587.161241</v>
+        <v>3958200000.000004</v>
       </c>
       <c r="K122" s="10" t="n">
         <v>116</v>
       </c>
       <c r="L122" s="10" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="M122" s="6" t="inlineStr">
         <is>
@@ -7449,28 +7449,28 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>31964956</v>
+        <v>6332961</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>MDG</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Congo Republic</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>544.987501003384</v>
+        <v>2482.2489948456</v>
       </c>
       <c r="G123" s="8" t="n">
         <v>2026</v>
@@ -7479,16 +7479,16 @@
         <v>2024</v>
       </c>
       <c r="I123" s="7" t="n">
-        <v>127.1637502341229</v>
+        <v>620.5622487114</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>4064783681.028729</v>
+        <v>3929996519.161596</v>
       </c>
       <c r="K123" s="10" t="n">
         <v>117</v>
       </c>
       <c r="L123" s="10" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="M123" s="6" t="inlineStr">
         <is>
@@ -7508,28 +7508,28 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
-        <v>5805962</v>
+        <v>2521139</v>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>LBN</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
         <v>0.333</v>
       </c>
       <c r="F124" s="7" t="n">
-        <v>3477.72489842684</v>
+        <v>7695.75319445165</v>
       </c>
       <c r="G124" s="8" t="n">
         <v>2026</v>
@@ -7538,10 +7538,10 @@
         <v>2024</v>
       </c>
       <c r="I124" s="7" t="n">
-        <v>695.544979685368</v>
+        <v>1539.15063889033</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>4038307721.344019</v>
+        <v>3880412702.581328</v>
       </c>
       <c r="K124" s="10" t="n">
         <v>118</v>
@@ -7567,28 +7567,28 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>27032412</v>
+        <v>462721</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>BRN</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Brunei Darussalam</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>735.270255787226</v>
+        <v>33153.4738913513</v>
       </c>
       <c r="G125" s="8" t="n">
         <v>2026</v>
@@ -7597,16 +7597,16 @@
         <v>2024</v>
       </c>
       <c r="I125" s="7" t="n">
-        <v>147.0540511574452</v>
+        <v>8288.368472837825</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>3975225697.157135</v>
+        <v>3835202148.119991</v>
       </c>
       <c r="K125" s="10" t="n">
         <v>119</v>
       </c>
       <c r="L125" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M125" s="6" t="inlineStr">
         <is>
@@ -7626,28 +7626,28 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
-        <v>3524788</v>
+        <v>2839175</v>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>MNG</t>
+          <t>JAM</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
         <v>0.444</v>
       </c>
       <c r="F126" s="7" t="n">
-        <v>6750.6301157724</v>
+        <v>7753.8006955432</v>
       </c>
       <c r="G126" s="8" t="n">
         <v>2026</v>
@@ -7656,10 +7656,10 @@
         <v>2024</v>
       </c>
       <c r="I126" s="7" t="n">
-        <v>1125.1050192954</v>
+        <v>1292.300115923867</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>3965756670.752194</v>
+        <v>3669066181.628144</v>
       </c>
       <c r="K126" s="10" t="n">
         <v>120</v>
@@ -7685,28 +7685,28 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>2521139</v>
+        <v>14462724</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0.333</v>
+        <v>0.444</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>7695.75319445165</v>
+        <v>1485.38018885134</v>
       </c>
       <c r="G127" s="8" t="n">
         <v>2026</v>
@@ -7715,16 +7715,16 @@
         <v>2024</v>
       </c>
       <c r="I127" s="7" t="n">
-        <v>1539.15063889033</v>
+        <v>247.5633648085567</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>3880412702.581328</v>
+        <v>3580440617.737468</v>
       </c>
       <c r="K127" s="10" t="n">
         <v>121</v>
       </c>
       <c r="L127" s="10" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="M127" s="6" t="inlineStr">
         <is>
@@ -7744,28 +7744,28 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="n">
-        <v>1892516</v>
+        <v>14256567</v>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F128" s="7" t="n">
-        <v>6745.40013244916</v>
+        <v>999.65456165547</v>
       </c>
       <c r="G128" s="8" t="n">
         <v>2026</v>
@@ -7774,10 +7774,10 @@
         <v>2024</v>
       </c>
       <c r="I128" s="7" t="n">
-        <v>2023.620039734748</v>
+        <v>249.9136404138675</v>
       </c>
       <c r="J128" s="5" t="n">
-        <v>3829733303.118646</v>
+        <v>3562910558.77421</v>
       </c>
       <c r="K128" s="10" t="n">
         <v>122</v>
@@ -7803,28 +7803,28 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>2839175</v>
+        <v>10590927</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>JAM</t>
+          <t>TJK</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>7753.8006955432</v>
+        <v>1341.20229027672</v>
       </c>
       <c r="G129" s="8" t="n">
         <v>2026</v>
@@ -7833,16 +7833,16 @@
         <v>2024</v>
       </c>
       <c r="I129" s="7" t="n">
-        <v>1292.300115923867</v>
+        <v>335.30057256918</v>
       </c>
       <c r="J129" s="5" t="n">
-        <v>3669066181.628144</v>
+        <v>3551143887.138388</v>
       </c>
       <c r="K129" s="10" t="n">
         <v>123</v>
       </c>
       <c r="L129" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M129" s="6" t="inlineStr">
         <is>
@@ -7862,28 +7862,28 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>14462724</v>
+        <v>1245779</v>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>MUS</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.444</v>
+        <v>0.222</v>
       </c>
       <c r="F130" s="7" t="n">
-        <v>1485.38018885134</v>
+        <v>11990.7798944837</v>
       </c>
       <c r="G130" s="8" t="n">
         <v>2026</v>
@@ -7892,16 +7892,16 @@
         <v>2024</v>
       </c>
       <c r="I130" s="7" t="n">
-        <v>247.5633648085567</v>
+        <v>2797.848642046197</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>3580440617.737468</v>
+        <v>3485501083.439669</v>
       </c>
       <c r="K130" s="10" t="n">
         <v>124</v>
       </c>
       <c r="L130" s="10" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="M130" s="6" t="inlineStr">
         <is>
@@ -7921,28 +7921,28 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>1245779</v>
+        <v>2538952</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0.222</v>
+        <v>0.444</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>11990.7798944837</v>
+        <v>8230.043114511511</v>
       </c>
       <c r="G131" s="8" t="n">
         <v>2026</v>
@@ -7951,16 +7951,16 @@
         <v>2024</v>
       </c>
       <c r="I131" s="7" t="n">
-        <v>2797.848642046197</v>
+        <v>1371.673852418585</v>
       </c>
       <c r="J131" s="5" t="n">
-        <v>3485501083.439669</v>
+        <v>3482614070.945871</v>
       </c>
       <c r="K131" s="10" t="n">
         <v>125</v>
       </c>
       <c r="L131" s="10" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="M131" s="6" t="inlineStr">
         <is>
@@ -7980,28 +7980,28 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
-        <v>2538952</v>
+        <v>1824359</v>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0.444</v>
+        <v>0.333</v>
       </c>
       <c r="F132" s="7" t="n">
-        <v>8230.043114511511</v>
+        <v>9291.85661671864</v>
       </c>
       <c r="G132" s="8" t="n">
         <v>2026</v>
@@ -8010,16 +8010,16 @@
         <v>2024</v>
       </c>
       <c r="I132" s="7" t="n">
-        <v>1371.673852418585</v>
+        <v>1858.371323343728</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>3482614070.945871</v>
+        <v>3390336449.084041</v>
       </c>
       <c r="K132" s="10" t="n">
         <v>126</v>
       </c>
       <c r="L132" s="10" t="n">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="M132" s="6" t="inlineStr">
         <is>
@@ -8039,28 +8039,28 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>1824359</v>
+        <v>1892516</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>9291.85661671864</v>
+        <v>6745.40013244916</v>
       </c>
       <c r="G133" s="8" t="n">
         <v>2026</v>
@@ -8069,16 +8069,16 @@
         <v>2024</v>
       </c>
       <c r="I133" s="7" t="n">
-        <v>1858.371323343728</v>
+        <v>1686.35003311229</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>3390336449.084041</v>
+        <v>3191444419.265539</v>
       </c>
       <c r="K133" s="10" t="n">
         <v>127</v>
       </c>
       <c r="L133" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M133" s="6" t="inlineStr">
         <is>
@@ -8098,28 +8098,28 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>38631</v>
+        <v>5129910</v>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>CRI</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="F134" s="7" t="n">
-        <v>288001.433369041</v>
+        <v>18587.1532203482</v>
       </c>
       <c r="G134" s="8" t="n">
         <v>2026</v>
@@ -8128,16 +8128,16 @@
         <v>2024</v>
       </c>
       <c r="I134" s="7" t="n">
-        <v>86400.4300107123</v>
+        <v>619.5717740116069</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>3337735011.743827</v>
+        <v>3178347439.219882</v>
       </c>
       <c r="K134" s="10" t="n">
         <v>128</v>
       </c>
       <c r="L134" s="10" t="n">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="M134" s="6" t="inlineStr">
         <is>
@@ -8157,28 +8157,28 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>9515236</v>
+        <v>19009151</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>1119.38160509429</v>
+        <v>629.538899449007</v>
       </c>
       <c r="G135" s="8" t="n">
         <v>2026</v>
@@ -8187,16 +8187,16 @@
         <v>2024</v>
       </c>
       <c r="I135" s="7" t="n">
-        <v>335.814481528287</v>
+        <v>157.3847248622517</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>3195354043.959291</v>
+        <v>2991749999.999998</v>
       </c>
       <c r="K135" s="10" t="n">
         <v>129</v>
       </c>
       <c r="L135" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
@@ -8216,28 +8216,28 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="n">
-        <v>19009151</v>
+        <v>38631</v>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>MCO</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F136" s="7" t="n">
-        <v>629.538899449007</v>
+        <v>288001.433369041</v>
       </c>
       <c r="G136" s="8" t="n">
         <v>2026</v>
@@ -8246,16 +8246,16 @@
         <v>2024</v>
       </c>
       <c r="I136" s="7" t="n">
-        <v>167.8770398530685</v>
+        <v>72000.35834226025</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>3191199999.999998</v>
+        <v>2781445843.119856</v>
       </c>
       <c r="K136" s="10" t="n">
         <v>130</v>
       </c>
       <c r="L136" s="10" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="M136" s="6" t="inlineStr">
         <is>
@@ -8275,28 +8275,28 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>5129910</v>
+        <v>3386588</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>CRI</t>
+          <t>URY</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
         <v>0.889</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>18587.1532203482</v>
+        <v>23906.5133029408</v>
       </c>
       <c r="G137" s="8" t="n">
         <v>2026</v>
@@ -8305,10 +8305,10 @@
         <v>2024</v>
       </c>
       <c r="I137" s="7" t="n">
-        <v>619.5717740116069</v>
+        <v>796.8837767646936</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>3178347439.219882</v>
+        <v>2698717035.78599</v>
       </c>
       <c r="K137" s="10" t="n">
         <v>131</v>
@@ -8334,28 +8334,28 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
-        <v>3386588</v>
+        <v>9515236</v>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>URY</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="F138" s="7" t="n">
-        <v>23906.5133029408</v>
+        <v>1119.38160509429</v>
       </c>
       <c r="G138" s="8" t="n">
         <v>2026</v>
@@ -8364,16 +8364,16 @@
         <v>2024</v>
       </c>
       <c r="I138" s="7" t="n">
-        <v>796.8837767646936</v>
+        <v>279.8454012735725</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>2698717035.78599</v>
+        <v>2662795036.632743</v>
       </c>
       <c r="K138" s="10" t="n">
         <v>132</v>
       </c>
       <c r="L138" s="10" t="n">
-        <v>176</v>
+        <v>1</v>
       </c>
       <c r="M138" s="6" t="inlineStr">
         <is>
@@ -8452,28 +8452,28 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
-        <v>40450</v>
+        <v>568847</v>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>LIE</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Liechtenstein</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>206780.590353385</v>
+        <v>43898.5781808597</v>
       </c>
       <c r="G140" s="8" t="n">
         <v>2026</v>
@@ -8482,16 +8482,16 @@
         <v>2024</v>
       </c>
       <c r="I140" s="7" t="n">
-        <v>62034.17710601549</v>
+        <v>4389.857818085969</v>
       </c>
       <c r="J140" s="5" t="n">
-        <v>2509282463.938327</v>
+        <v>2497157450.24475</v>
       </c>
       <c r="K140" s="10" t="n">
         <v>134</v>
       </c>
       <c r="L140" s="10" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="M140" s="6" t="inlineStr">
         <is>
@@ -8511,28 +8511,28 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>568847</v>
+        <v>21655286</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="F141" s="7" t="n">
-        <v>43898.5781808597</v>
+        <v>522.5703936425469</v>
       </c>
       <c r="G141" s="8" t="n">
         <v>2026</v>
@@ -8541,16 +8541,16 @@
         <v>2024</v>
       </c>
       <c r="I141" s="7" t="n">
-        <v>4389.857818085969</v>
+        <v>104.5140787285094</v>
       </c>
       <c r="J141" s="5" t="n">
-        <v>2497157450.24475</v>
+        <v>2263282265.892387</v>
       </c>
       <c r="K141" s="10" t="n">
         <v>135</v>
       </c>
       <c r="L141" s="10" t="n">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="M141" s="6" t="inlineStr">
         <is>
@@ -8570,28 +8570,28 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="n">
-        <v>21655286</v>
+        <v>40450</v>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>LIE</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Liechtenstein</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F142" s="7" t="n">
-        <v>522.5703936425469</v>
+        <v>206780.590353385</v>
       </c>
       <c r="G142" s="8" t="n">
         <v>2026</v>
@@ -8600,16 +8600,16 @@
         <v>2024</v>
       </c>
       <c r="I142" s="7" t="n">
-        <v>104.5140787285094</v>
+        <v>51695.14758834625</v>
       </c>
       <c r="J142" s="5" t="n">
-        <v>2263282265.892387</v>
+        <v>2091068719.948606</v>
       </c>
       <c r="K142" s="10" t="n">
         <v>136</v>
       </c>
       <c r="L142" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M142" s="6" t="inlineStr">
         <is>
@@ -8895,10 +8895,10 @@
         <v>2024</v>
       </c>
       <c r="I147" s="7" t="n">
-        <v>1042.549046341819</v>
+        <v>977.389730945455</v>
       </c>
       <c r="J147" s="5" t="n">
-        <v>1295702890.872632</v>
+        <v>1214721460.193092</v>
       </c>
       <c r="K147" s="10" t="n">
         <v>141</v>
@@ -8924,28 +8924,28 @@
     </row>
     <row r="148">
       <c r="A148" s="5" t="n">
-        <v>81938</v>
+        <v>386506</v>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>AND</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="F148" s="7" t="n">
-        <v>49303.6491674336</v>
+        <v>86040.5309851288</v>
       </c>
       <c r="G148" s="8" t="n">
         <v>2026</v>
@@ -8954,16 +8954,16 @@
         <v>2024</v>
       </c>
       <c r="I148" s="7" t="n">
-        <v>14791.09475023008</v>
+        <v>2868.017699504295</v>
       </c>
       <c r="J148" s="5" t="n">
-        <v>1211952721.644352</v>
+        <v>1108506048.964607</v>
       </c>
       <c r="K148" s="10" t="n">
         <v>142</v>
       </c>
       <c r="L148" s="10" t="n">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="M148" s="6" t="inlineStr">
         <is>
@@ -8983,28 +8983,28 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>386506</v>
+        <v>623525</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>MNE</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0.889</v>
+        <v>0.556</v>
       </c>
       <c r="F149" s="7" t="n">
-        <v>86040.5309851288</v>
+        <v>13263.3281277699</v>
       </c>
       <c r="G149" s="8" t="n">
         <v>2026</v>
@@ -9013,16 +9013,16 @@
         <v>2024</v>
       </c>
       <c r="I149" s="7" t="n">
-        <v>2868.017699504295</v>
+        <v>1768.44375036932</v>
       </c>
       <c r="J149" s="5" t="n">
-        <v>1108506048.964607</v>
+        <v>1102668889.44903</v>
       </c>
       <c r="K149" s="10" t="n">
         <v>143</v>
       </c>
       <c r="L149" s="10" t="n">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="M149" s="6" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>2024</v>
       </c>
       <c r="I150" s="7" t="n">
-        <v>947.392893544592</v>
+        <v>888.180837698055</v>
       </c>
       <c r="J150" s="5" t="n">
-        <v>1107238917.329223</v>
+        <v>1038036484.996146</v>
       </c>
       <c r="K150" s="10" t="n">
         <v>144</v>
@@ -9101,16 +9101,16 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>623525</v>
+        <v>81938</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>MNE</t>
+          <t>AND</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
@@ -9119,10 +9119,10 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="F151" s="7" t="n">
-        <v>13263.3281277699</v>
+        <v>49303.6491674336</v>
       </c>
       <c r="G151" s="8" t="n">
         <v>2026</v>
@@ -9131,16 +9131,16 @@
         <v>2024</v>
       </c>
       <c r="I151" s="7" t="n">
-        <v>1768.44375036932</v>
+        <v>12325.9122918584</v>
       </c>
       <c r="J151" s="5" t="n">
-        <v>1102668889.44903</v>
+        <v>1009960601.370294</v>
       </c>
       <c r="K151" s="10" t="n">
         <v>145</v>
       </c>
       <c r="L151" s="10" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="M151" s="6" t="inlineStr">
         <is>
@@ -9219,28 +9219,28 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>417072</v>
+        <v>5612817</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F153" s="7" t="n">
-        <v>7681.24400583113</v>
+        <v>851.497723870206</v>
       </c>
       <c r="G153" s="8" t="n">
         <v>2026</v>
@@ -9249,16 +9249,16 @@
         <v>2024</v>
       </c>
       <c r="I153" s="7" t="n">
-        <v>2304.373201749339</v>
+        <v>170.2995447740412</v>
       </c>
       <c r="J153" s="5" t="n">
-        <v>961089540.0000002</v>
+        <v>955860179.9999996</v>
       </c>
       <c r="K153" s="10" t="n">
         <v>147</v>
       </c>
       <c r="L153" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
@@ -9278,28 +9278,28 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
-        <v>5612817</v>
+        <v>417072</v>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>BLZ</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F154" s="7" t="n">
-        <v>851.497723870206</v>
+        <v>7681.24400583113</v>
       </c>
       <c r="G154" s="8" t="n">
         <v>2026</v>
@@ -9308,16 +9308,16 @@
         <v>2024</v>
       </c>
       <c r="I154" s="7" t="n">
-        <v>170.2995447740412</v>
+        <v>1920.311001457783</v>
       </c>
       <c r="J154" s="5" t="n">
-        <v>955860179.9999996</v>
+        <v>800907950.0000004</v>
       </c>
       <c r="K154" s="10" t="n">
         <v>148</v>
       </c>
       <c r="L154" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M154" s="6" t="inlineStr">
         <is>
@@ -9367,10 +9367,10 @@
         <v>2024</v>
       </c>
       <c r="I155" s="7" t="n">
-        <v>65.82744926480939</v>
+        <v>54.8562077206745</v>
       </c>
       <c r="J155" s="5" t="n">
-        <v>924729920.1978996</v>
+        <v>770608266.8315831</v>
       </c>
       <c r="K155" s="10" t="n">
         <v>149</v>
@@ -9396,16 +9396,16 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="n">
-        <v>179744</v>
+        <v>282467</v>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>BRB</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>St. Lucia</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
@@ -9414,10 +9414,10 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="F156" s="7" t="n">
-        <v>14181.6303351598</v>
+        <v>26544.8707282621</v>
       </c>
       <c r="G156" s="8" t="n">
         <v>2026</v>
@@ -9426,16 +9426,16 @@
         <v>2024</v>
       </c>
       <c r="I156" s="7" t="n">
-        <v>4254.489100547939</v>
+        <v>2654.48707282621</v>
       </c>
       <c r="J156" s="5" t="n">
-        <v>764718888.8888888</v>
+        <v>749805000.0000012</v>
       </c>
       <c r="K156" s="10" t="n">
         <v>150</v>
       </c>
       <c r="L156" s="10" t="n">
-        <v>1</v>
+        <v>161</v>
       </c>
       <c r="M156" s="6" t="inlineStr">
         <is>
@@ -9455,28 +9455,28 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>282467</v>
+        <v>634431</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>BRB</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0.667</v>
+        <v>0.444</v>
       </c>
       <c r="F157" s="7" t="n">
-        <v>26544.8707282621</v>
+        <v>6961.78955961526</v>
       </c>
       <c r="G157" s="8" t="n">
         <v>2026</v>
@@ -9485,16 +9485,16 @@
         <v>2024</v>
       </c>
       <c r="I157" s="7" t="n">
-        <v>2654.48707282621</v>
+        <v>1160.298259935877</v>
       </c>
       <c r="J157" s="5" t="n">
-        <v>749805000.0000012</v>
+        <v>736129185.3493781</v>
       </c>
       <c r="K157" s="10" t="n">
         <v>151</v>
       </c>
       <c r="L157" s="10" t="n">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="M157" s="6" t="inlineStr">
         <is>
@@ -9514,28 +9514,28 @@
     </row>
     <row r="158">
       <c r="A158" s="5" t="n">
-        <v>634431</v>
+        <v>5330690</v>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0.444</v>
+        <v>0.111</v>
       </c>
       <c r="F158" s="7" t="n">
-        <v>6961.78955961526</v>
+        <v>516.160999996036</v>
       </c>
       <c r="G158" s="8" t="n">
         <v>2026</v>
@@ -9544,16 +9544,16 @@
         <v>2024</v>
       </c>
       <c r="I158" s="7" t="n">
-        <v>1160.298259935877</v>
+        <v>129.040249999009</v>
       </c>
       <c r="J158" s="5" t="n">
-        <v>736129185.3493781</v>
+        <v>687873570.2672173</v>
       </c>
       <c r="K158" s="10" t="n">
         <v>152</v>
       </c>
       <c r="L158" s="10" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="M158" s="6" t="inlineStr">
         <is>
@@ -9573,28 +9573,28 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>5330690</v>
+        <v>179744</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>St. Lucia</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F159" s="7" t="n">
-        <v>516.160999996036</v>
+        <v>14181.6303351598</v>
       </c>
       <c r="G159" s="8" t="n">
         <v>2026</v>
@@ -9603,16 +9603,16 @@
         <v>2024</v>
       </c>
       <c r="I159" s="7" t="n">
-        <v>137.6429333322763</v>
+        <v>3545.40758378995</v>
       </c>
       <c r="J159" s="5" t="n">
-        <v>733731808.2850318</v>
+        <v>637265740.7407408</v>
       </c>
       <c r="K159" s="10" t="n">
         <v>153</v>
       </c>
       <c r="L159" s="10" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="M159" s="6" t="inlineStr">
         <is>
@@ -9632,28 +9632,28 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
-        <v>93772</v>
+        <v>791524</v>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>BTN</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>Antigua and Barbuda</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F160" s="7" t="n">
-        <v>23542.4526945578</v>
+        <v>3831.32535494609</v>
       </c>
       <c r="G160" s="8" t="n">
         <v>2026</v>
@@ -9662,16 +9662,16 @@
         <v>2024</v>
       </c>
       <c r="I160" s="7" t="n">
-        <v>7062.73580836734</v>
+        <v>766.2650709892181</v>
       </c>
       <c r="J160" s="5" t="n">
-        <v>662286862.2222222</v>
+        <v>606517194.0496699</v>
       </c>
       <c r="K160" s="10" t="n">
         <v>154</v>
       </c>
       <c r="L160" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M160" s="6" t="inlineStr">
         <is>
@@ -9691,28 +9691,28 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>33977</v>
+        <v>93772</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Antigua and Barbuda</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F161" s="7" t="n">
-        <v>59879.7173015651</v>
+        <v>23542.4526945578</v>
       </c>
       <c r="G161" s="8" t="n">
         <v>2026</v>
@@ -9721,10 +9721,10 @@
         <v>2024</v>
       </c>
       <c r="I161" s="7" t="n">
-        <v>17963.91519046953</v>
+        <v>5885.61317363945</v>
       </c>
       <c r="J161" s="5" t="n">
-        <v>610359946.4265832</v>
+        <v>551905718.5185184</v>
       </c>
       <c r="K161" s="10" t="n">
         <v>155</v>
@@ -9750,28 +9750,28 @@
     </row>
     <row r="162">
       <c r="A162" s="5" t="n">
-        <v>791524</v>
+        <v>2201352</v>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>BTN</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="F162" s="7" t="n">
-        <v>3831.32535494609</v>
+        <v>1007.74151728028</v>
       </c>
       <c r="G162" s="8" t="n">
         <v>2026</v>
@@ -9780,16 +9780,16 @@
         <v>2024</v>
       </c>
       <c r="I162" s="7" t="n">
-        <v>766.2650709892181</v>
+        <v>235.1396873653987</v>
       </c>
       <c r="J162" s="5" t="n">
-        <v>606517194.0496699</v>
+        <v>517625221.0611951</v>
       </c>
       <c r="K162" s="10" t="n">
         <v>156</v>
       </c>
       <c r="L162" s="10" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="M162" s="6" t="inlineStr">
         <is>
@@ -9809,28 +9809,28 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
-        <v>2201352</v>
+        <v>33977</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F163" s="7" t="n">
-        <v>1007.74151728028</v>
+        <v>59879.7173015651</v>
       </c>
       <c r="G163" s="8" t="n">
         <v>2026</v>
@@ -9839,16 +9839,16 @@
         <v>2024</v>
       </c>
       <c r="I163" s="7" t="n">
-        <v>235.1396873653987</v>
+        <v>14969.92932539127</v>
       </c>
       <c r="J163" s="5" t="n">
-        <v>517625221.0611951</v>
+        <v>508633288.6888193</v>
       </c>
       <c r="K163" s="10" t="n">
         <v>157</v>
       </c>
       <c r="L163" s="10" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="M163" s="6" t="inlineStr">
         <is>
@@ -9927,28 +9927,28 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>117207</v>
+        <v>2759988</v>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>GRD</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F165" s="7" t="n">
-        <v>11705.0902976658</v>
+        <v>871.340291776294</v>
       </c>
       <c r="G165" s="8" t="n">
         <v>2026</v>
@@ -9957,16 +9957,16 @@
         <v>2024</v>
       </c>
       <c r="I165" s="7" t="n">
-        <v>3511.52708929974</v>
+        <v>145.2233819627156</v>
       </c>
       <c r="J165" s="5" t="n">
-        <v>411575555.5555546</v>
+        <v>400814791.5365117</v>
       </c>
       <c r="K165" s="10" t="n">
         <v>159</v>
       </c>
       <c r="L165" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M165" s="6" t="inlineStr">
         <is>
@@ -9986,16 +9986,16 @@
     </row>
     <row r="166">
       <c r="A166" s="5" t="n">
-        <v>2759988</v>
+        <v>524877</v>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>CPV</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
@@ -10004,10 +10004,10 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>0.444</v>
+        <v>0.556</v>
       </c>
       <c r="F166" s="7" t="n">
-        <v>871.340291776294</v>
+        <v>5192.48157325878</v>
       </c>
       <c r="G166" s="8" t="n">
         <v>2026</v>
@@ -10016,16 +10016,16 @@
         <v>2024</v>
       </c>
       <c r="I166" s="7" t="n">
-        <v>145.2233819627156</v>
+        <v>692.330876434504</v>
       </c>
       <c r="J166" s="5" t="n">
-        <v>400814791.5365117</v>
+        <v>363388553.4303132</v>
       </c>
       <c r="K166" s="10" t="n">
         <v>160</v>
       </c>
       <c r="L166" s="10" t="n">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="M166" s="6" t="inlineStr">
         <is>
@@ -10075,10 +10075,10 @@
         <v>2024</v>
       </c>
       <c r="I167" s="7" t="n">
-        <v>443.401768833344</v>
+        <v>415.68915828126</v>
       </c>
       <c r="J167" s="5" t="n">
-        <v>384264388.1205032</v>
+        <v>360247863.8629718</v>
       </c>
       <c r="K167" s="10" t="n">
         <v>161</v>
@@ -10104,28 +10104,28 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>524877</v>
+        <v>117207</v>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>CPV</t>
+          <t>GRD</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="F168" s="7" t="n">
-        <v>5192.48157325878</v>
+        <v>11705.0902976658</v>
       </c>
       <c r="G168" s="8" t="n">
         <v>2026</v>
@@ -10134,16 +10134,16 @@
         <v>2024</v>
       </c>
       <c r="I168" s="7" t="n">
-        <v>692.330876434504</v>
+        <v>2926.27257441645</v>
       </c>
       <c r="J168" s="5" t="n">
-        <v>363388553.4303132</v>
+        <v>342979629.6296288</v>
       </c>
       <c r="K168" s="10" t="n">
         <v>162</v>
       </c>
       <c r="L168" s="10" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="M168" s="6" t="inlineStr">
         <is>
@@ -10163,28 +10163,28 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>218019</v>
+        <v>819198</v>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>Samoa</t>
+          <t>Solomon Islands</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Melanesia</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F169" s="7" t="n">
-        <v>5392.87761915762</v>
+        <v>1933.55538435227</v>
       </c>
       <c r="G169" s="8" t="n">
         <v>2026</v>
@@ -10193,16 +10193,16 @@
         <v>2024</v>
       </c>
       <c r="I169" s="7" t="n">
-        <v>1617.863285747286</v>
+        <v>386.711076870454</v>
       </c>
       <c r="J169" s="5" t="n">
-        <v>352724935.6953375</v>
+        <v>316792940.7501222</v>
       </c>
       <c r="K169" s="10" t="n">
         <v>163</v>
       </c>
       <c r="L169" s="10" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="M169" s="6" t="inlineStr">
         <is>
@@ -10222,28 +10222,28 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>100616</v>
+        <v>218019</v>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>VCT</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>St. Vincent and the Grenadines</t>
+          <t>Samoa</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Polynesia</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F170" s="7" t="n">
-        <v>11501.2265187188</v>
+        <v>5392.87761915762</v>
       </c>
       <c r="G170" s="8" t="n">
         <v>2026</v>
@@ -10252,10 +10252,10 @@
         <v>2024</v>
       </c>
       <c r="I170" s="7" t="n">
-        <v>3450.36795561564</v>
+        <v>1348.219404789405</v>
       </c>
       <c r="J170" s="5" t="n">
-        <v>347162222.2222232</v>
+        <v>293937446.4127813</v>
       </c>
       <c r="K170" s="10" t="n">
         <v>164</v>
@@ -10281,16 +10281,16 @@
     </row>
     <row r="171">
       <c r="A171" s="5" t="n">
-        <v>46843</v>
+        <v>100616</v>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>KNA</t>
+          <t>VCT</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>St. Kitts and Nevis</t>
+          <t>St. Vincent and the Grenadines</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
@@ -10302,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="F171" s="7" t="n">
-        <v>23960.6534357084</v>
+        <v>11501.2265187188</v>
       </c>
       <c r="G171" s="8" t="n">
         <v>2026</v>
@@ -10311,10 +10311,10 @@
         <v>2024</v>
       </c>
       <c r="I171" s="7" t="n">
-        <v>7188.196030712519</v>
+        <v>2875.3066296797</v>
       </c>
       <c r="J171" s="5" t="n">
-        <v>336716666.6666665</v>
+        <v>289301851.8518527</v>
       </c>
       <c r="K171" s="10" t="n">
         <v>165</v>
@@ -10340,28 +10340,28 @@
     </row>
     <row r="172">
       <c r="A172" s="5" t="n">
-        <v>819198</v>
+        <v>46843</v>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>KNA</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>Solomon Islands</t>
+          <t>St. Kitts and Nevis</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F172" s="7" t="n">
-        <v>1933.55538435227</v>
+        <v>23960.6534357084</v>
       </c>
       <c r="G172" s="8" t="n">
         <v>2026</v>
@@ -10370,16 +10370,16 @@
         <v>2024</v>
       </c>
       <c r="I172" s="7" t="n">
-        <v>386.711076870454</v>
+        <v>5990.1633589271</v>
       </c>
       <c r="J172" s="5" t="n">
-        <v>316792940.7501222</v>
+        <v>280597222.2222221</v>
       </c>
       <c r="K172" s="10" t="n">
         <v>166</v>
       </c>
       <c r="L172" s="10" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M172" s="6" t="inlineStr">
         <is>
@@ -10458,28 +10458,28 @@
     </row>
     <row r="174">
       <c r="A174" s="5" t="n">
-        <v>66205</v>
+        <v>327777</v>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>DMA</t>
+          <t>VUT</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>Vanuatu</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Melanesia</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F174" s="7" t="n">
-        <v>10405.2787777582</v>
+        <v>3410.77023167097</v>
       </c>
       <c r="G174" s="8" t="n">
         <v>2026</v>
@@ -10488,16 +10488,16 @@
         <v>2024</v>
       </c>
       <c r="I174" s="7" t="n">
-        <v>3121.58363332746</v>
+        <v>568.4617052784949</v>
       </c>
       <c r="J174" s="5" t="n">
-        <v>206664444.4444445</v>
+        <v>186328672.3710693</v>
       </c>
       <c r="K174" s="10" t="n">
         <v>168</v>
       </c>
       <c r="L174" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M174" s="6" t="inlineStr">
         <is>
@@ -10517,28 +10517,28 @@
     </row>
     <row r="175">
       <c r="A175" s="5" t="n">
-        <v>327777</v>
+        <v>66205</v>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>VUT</t>
+          <t>DMA</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>Vanuatu</t>
+          <t>Dominica</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F175" s="7" t="n">
-        <v>3410.77023167097</v>
+        <v>10405.2787777582</v>
       </c>
       <c r="G175" s="8" t="n">
         <v>2026</v>
@@ -10547,16 +10547,16 @@
         <v>2024</v>
       </c>
       <c r="I175" s="7" t="n">
-        <v>568.4617052784949</v>
+        <v>2601.31969443955</v>
       </c>
       <c r="J175" s="5" t="n">
-        <v>186328672.3710693</v>
+        <v>172220370.3703704</v>
       </c>
       <c r="K175" s="10" t="n">
         <v>169</v>
       </c>
       <c r="L175" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M175" s="6" t="inlineStr">
         <is>
@@ -10606,10 +10606,10 @@
         <v>2024</v>
       </c>
       <c r="I176" s="7" t="n">
-        <v>1695.478119189471</v>
+        <v>1412.898432657892</v>
       </c>
       <c r="J176" s="5" t="n">
-        <v>176626433.0665632</v>
+        <v>147188694.222136</v>
       </c>
       <c r="K176" s="10" t="n">
         <v>170</v>
@@ -10635,28 +10635,28 @@
     </row>
     <row r="177">
       <c r="A177" s="5" t="n">
-        <v>113160</v>
+        <v>235536</v>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>FSM</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>Micronesia, Fed. Sts.</t>
+          <t>Sao Tome and Principe</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="F177" s="7" t="n">
-        <v>4166.00476748564</v>
+        <v>3490.56883486557</v>
       </c>
       <c r="G177" s="8" t="n">
         <v>2026</v>
@@ -10665,16 +10665,16 @@
         <v>2024</v>
       </c>
       <c r="I177" s="7" t="n">
-        <v>1249.801430245692</v>
+        <v>581.7614724775949</v>
       </c>
       <c r="J177" s="5" t="n">
-        <v>141427529.8466025</v>
+        <v>137025770.1814828</v>
       </c>
       <c r="K177" s="10" t="n">
         <v>171</v>
       </c>
       <c r="L177" s="10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M177" s="6" t="inlineStr">
         <is>
@@ -10694,28 +10694,28 @@
     </row>
     <row r="178">
       <c r="A178" s="5" t="n">
-        <v>235536</v>
+        <v>113160</v>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>FSM</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>Sao Tome and Principe</t>
+          <t>Micronesia, Fed. Sts.</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Micronesia</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F178" s="7" t="n">
-        <v>3490.56883486557</v>
+        <v>4166.00476748564</v>
       </c>
       <c r="G178" s="8" t="n">
         <v>2026</v>
@@ -10724,16 +10724,16 @@
         <v>2024</v>
       </c>
       <c r="I178" s="7" t="n">
-        <v>581.7614724775949</v>
+        <v>1041.50119187141</v>
       </c>
       <c r="J178" s="5" t="n">
-        <v>137025770.1814828</v>
+        <v>117856274.8721687</v>
       </c>
       <c r="K178" s="10" t="n">
         <v>172</v>
       </c>
       <c r="L178" s="10" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M178" s="6" t="inlineStr">
         <is>
@@ -10753,16 +10753,16 @@
     </row>
     <row r="179">
       <c r="A179" s="5" t="n">
-        <v>37548</v>
+        <v>134518</v>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>MHL</t>
+          <t>KIR</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>Marshall Islands</t>
+          <t>Kiribati</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
@@ -10771,10 +10771,10 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F179" s="7" t="n">
-        <v>7726.33668877794</v>
+        <v>2288.63471423684</v>
       </c>
       <c r="G179" s="8" t="n">
         <v>2026</v>
@@ -10783,16 +10783,16 @@
         <v>2024</v>
       </c>
       <c r="I179" s="7" t="n">
-        <v>2317.901006633382</v>
+        <v>572.15867855921</v>
       </c>
       <c r="J179" s="5" t="n">
-        <v>87032546.99707024</v>
+        <v>76965641.12242781</v>
       </c>
       <c r="K179" s="10" t="n">
         <v>173</v>
       </c>
       <c r="L179" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="M179" s="6" t="inlineStr">
         <is>
@@ -10812,16 +10812,16 @@
     </row>
     <row r="180">
       <c r="A180" s="5" t="n">
-        <v>17695</v>
+        <v>37548</v>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>MHL</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>Palau</t>
+          <t>Marshall Islands</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
@@ -10833,7 +10833,7 @@
         <v>0</v>
       </c>
       <c r="F180" s="7" t="n">
-        <v>15610.8231931032</v>
+        <v>7726.33668877794</v>
       </c>
       <c r="G180" s="8" t="n">
         <v>2026</v>
@@ -10842,10 +10842,10 @@
         <v>2024</v>
       </c>
       <c r="I180" s="7" t="n">
-        <v>4683.24695793096</v>
+        <v>1931.584172194485</v>
       </c>
       <c r="J180" s="5" t="n">
-        <v>82870054.92058833</v>
+        <v>72527122.49755852</v>
       </c>
       <c r="K180" s="10" t="n">
         <v>174</v>
@@ -10871,28 +10871,28 @@
     </row>
     <row r="181">
       <c r="A181" s="5" t="n">
-        <v>134518</v>
+        <v>121354</v>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>KIR</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>Kiribati</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>0.111</v>
+        <v>0.889</v>
       </c>
       <c r="F181" s="7" t="n">
-        <v>2288.63471423684</v>
+        <v>17858.8226383978</v>
       </c>
       <c r="G181" s="8" t="n">
         <v>2026</v>
@@ -10901,16 +10901,16 @@
         <v>2024</v>
       </c>
       <c r="I181" s="7" t="n">
-        <v>610.3025904631573</v>
+        <v>595.2940879465935</v>
       </c>
       <c r="J181" s="5" t="n">
-        <v>82096683.863923</v>
+        <v>72241318.74867092</v>
       </c>
       <c r="K181" s="10" t="n">
         <v>175</v>
       </c>
       <c r="L181" s="10" t="n">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="M181" s="6" t="inlineStr">
         <is>
@@ -10930,28 +10930,28 @@
     </row>
     <row r="182">
       <c r="A182" s="5" t="n">
-        <v>121354</v>
+        <v>17695</v>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>SYC</t>
+          <t>PLW</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Palau</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Micronesia</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="F182" s="7" t="n">
-        <v>17858.8226383978</v>
+        <v>15610.8231931032</v>
       </c>
       <c r="G182" s="8" t="n">
         <v>2026</v>
@@ -10960,16 +10960,16 @@
         <v>2024</v>
       </c>
       <c r="I182" s="7" t="n">
-        <v>595.2940879465935</v>
+        <v>3902.7057982758</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>72241318.74867092</v>
+        <v>69058379.10049029</v>
       </c>
       <c r="K182" s="10" t="n">
         <v>176</v>
       </c>
       <c r="L182" s="10" t="n">
-        <v>176</v>
+        <v>1</v>
       </c>
       <c r="M182" s="6" t="inlineStr">
         <is>
@@ -11019,10 +11019,10 @@
         <v>2024</v>
       </c>
       <c r="I183" s="7" t="n">
-        <v>4082.7476512656</v>
+        <v>3402.289709388</v>
       </c>
       <c r="J183" s="5" t="n">
-        <v>48776586.18967012</v>
+        <v>40647155.15805843</v>
       </c>
       <c r="K183" s="10" t="n">
         <v>177</v>
@@ -11078,10 +11078,10 @@
         <v>2024</v>
       </c>
       <c r="I184" s="7" t="n">
-        <v>1903.43250566067</v>
+        <v>1586.193754717225</v>
       </c>
       <c r="J184" s="5" t="n">
-        <v>18360509.94960282</v>
+        <v>15300424.95800235</v>
       </c>
       <c r="K184" s="10" t="n">
         <v>178</v>
@@ -11107,16 +11107,16 @@
     </row>
     <row r="185">
       <c r="A185" s="5" t="n">
-        <v>1372341</v>
+        <v>1866124</v>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
@@ -11128,7 +11128,7 @@
         <v>1</v>
       </c>
       <c r="F185" s="7" t="n">
-        <v>31428.3547816104</v>
+        <v>23409.0845154775</v>
       </c>
       <c r="G185" s="8" t="n">
         <v>2026</v>
@@ -11166,16 +11166,16 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
-        <v>1866124</v>
+        <v>5572279</v>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
@@ -11187,7 +11187,7 @@
         <v>1</v>
       </c>
       <c r="F186" s="7" t="n">
-        <v>23409.0845154775</v>
+        <v>86785.4334489176</v>
       </c>
       <c r="G186" s="8" t="n">
         <v>2026</v>
@@ -11225,16 +11225,16 @@
     </row>
     <row r="187">
       <c r="A187" s="5" t="n">
-        <v>10569709</v>
+        <v>5619911</v>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
@@ -11246,7 +11246,7 @@
         <v>1</v>
       </c>
       <c r="F187" s="7" t="n">
-        <v>57117.4877440616</v>
+        <v>53149.7671934051</v>
       </c>
       <c r="G187" s="8" t="n">
         <v>2026</v>
@@ -11284,28 +11284,28 @@
     </row>
     <row r="188">
       <c r="A188" s="5" t="n">
-        <v>677012</v>
+        <v>10569709</v>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F188" s="7" t="n">
-        <v>137781.681659123</v>
+        <v>57117.4877440616</v>
       </c>
       <c r="G188" s="8" t="n">
         <v>2026</v>
@@ -11343,28 +11343,28 @@
     </row>
     <row r="189">
       <c r="A189" s="5" t="n">
-        <v>5976992</v>
+        <v>11858610</v>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F189" s="7" t="n">
-        <v>71026.4832271897</v>
+        <v>56614.5679499036</v>
       </c>
       <c r="G189" s="8" t="n">
         <v>2026</v>
@@ -11461,28 +11461,28 @@
     </row>
     <row r="191">
       <c r="A191" s="5" t="n">
-        <v>5572279</v>
+        <v>677012</v>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F191" s="7" t="n">
-        <v>86785.4334489176</v>
+        <v>137781.681659123</v>
       </c>
       <c r="G191" s="8" t="n">
         <v>2026</v>
@@ -11520,28 +11520,28 @@
     </row>
     <row r="192">
       <c r="A192" s="5" t="n">
-        <v>11858610</v>
+        <v>5976992</v>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F192" s="7" t="n">
-        <v>56614.5679499036</v>
+        <v>71026.4832271897</v>
       </c>
       <c r="G192" s="8" t="n">
         <v>2026</v>
@@ -11579,16 +11579,16 @@
     </row>
     <row r="193">
       <c r="A193" s="5" t="n">
-        <v>5619911</v>
+        <v>1372341</v>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
@@ -11600,7 +11600,7 @@
         <v>1</v>
       </c>
       <c r="F193" s="7" t="n">
-        <v>53149.7671934051</v>
+        <v>31428.3547816104</v>
       </c>
       <c r="G193" s="8" t="n">
         <v>2026</v>

--- a/outputs/atlas/rtl_di_atlas_un_members_2026.xlsx
+++ b/outputs/atlas/rtl_di_atlas_un_members_2026.xlsx
@@ -11945,7 +11945,7 @@
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>PLACEHOLDER: Full R from 9 RTLP indicators requires V-Dem v16 data (see docs/indicator_crosswalk.md and src/fetch_vdem.py). This demonstrates the equation + pipeline with real WB G0/pop/socio.</t>
+          <t>Canonical RTLDI Atlas output: R is computed from the documented V-Dem + World Bank crosswalk, and capital exclusions use the population-weighted eta with the 25% cap.</t>
         </is>
       </c>
     </row>
